--- a/inasistencias-6A-sistDeCtrolVirtual/Alumnos-6A-SistDeCtrolVirtual.xlsx
+++ b/inasistencias-6A-sistDeCtrolVirtual/Alumnos-6A-SistDeCtrolVirtual.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="asistencia" sheetId="1" state="visible" r:id="rId3"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1888" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1918" uniqueCount="601">
   <si>
     <t xml:space="preserve">nro</t>
   </si>
@@ -332,139 +332,154 @@
     <t xml:space="preserve">fecha limite</t>
   </si>
   <si>
+    <t xml:space="preserve">1-SO gen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-SO hist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-comandos mkdir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4-comandos mv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-git historia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6- git funcionam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7- git estados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8-git comandos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positivos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8+posit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">promedio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valoracion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9-cli-serv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-html bodt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11-table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asistencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repositorio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tp1- index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tp2- presentacion-amigos y comidas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tp-3-login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tp4-buscar y agregar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tp-5-listar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tp-6js</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tp-7Flexbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">se subio 16/9, falta volver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">se subio 30/9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">se subio el 30 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">se subio el 08/4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">se subio el 15/04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hacer carpeta fotos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">se subio el 16/9, tiene mal el nomb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">se subio 19/6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no hace lo que debe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no vuelve, comida preferida no esta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no vuelve peri igual vale el 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Index pedir explicacion, soy tu nombre jajaj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estan vacios las comidas y amigos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">corregir las referencias, faltan las imagenes</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> se subio 10/6, le creo que lo subio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no vuelve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no es un formulario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no corresponde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aprobo Agosto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09/09/2025 un poquito atrasado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09/09/2025 atrasado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/09/2025 atrasado y mal</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
     <t xml:space="preserve">f</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1-SO gen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-SO hist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-comandos mkdir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4-comandos mv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5-git historia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6- git funcionam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7- git estados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8-git comandos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">positivos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8+posit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">promedio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valoracion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9-cli-serv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10-html bodt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11-table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asistencia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OBS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repositorio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tp1- index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tp2- presentacion-amigos y comidas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tp-3-login</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tp4-buscar y agregar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tp-5-listar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tp-6js</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tp-7Flexbox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hacer carpeta fotos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">se subio el 16/9, tiene mal el nomb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">se subio 19/6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no hace lo que debe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no vuelve, comida preferida no esta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no vuelve peri igual vale el 10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Index pedir explicacion, soy tu nombre jajaj</t>
-  </si>
-  <si>
-    <t xml:space="preserve">estan vacios las comidas y amigos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">corregir las referencias, faltan las imagenes</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> se subio 10/6, le creo que lo subio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no vuelve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no es un formulario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no corresponde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aprobo Agosto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09/09/2025 un poquito atrasado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09/09/2025 atrasado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16/09/2025 atrasado y mal</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t xml:space="preserve">16/9 no vuelve</t>
@@ -1965,15 +1980,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2275,17 +2290,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AH32"/>
+  <dimension ref="A1:AJ32"/>
   <sheetFormatPr defaultColWidth="8.8125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="2" min="2" style="1" width="21.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.6"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="1" width="33.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.61"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="1" width="33.13"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="19" min="5" style="1" width="8.69"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="29" min="20" style="0" width="8.81"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="29" min="20" style="1" width="8.81"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="30" min="30" style="1" width="8.8"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="32" min="31" style="0" width="8.81"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="32" min="31" style="1" width="8.81"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2403,14 +2418,17 @@
       <c r="AF2" s="3" t="n">
         <v>45930</v>
       </c>
-      <c r="AG2" s="4" t="n">
+      <c r="AG2" s="3" t="n">
         <v>45944</v>
       </c>
-      <c r="AH2" s="5" t="s">
+      <c r="AH2" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI2" s="4" t="n">
+        <v>45951</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
@@ -2457,7 +2475,7 @@
         <f aca="false">M3+N3/2+O3/4</f>
         <v>5</v>
       </c>
-      <c r="Q3" s="6" t="n">
+      <c r="Q3" s="5" t="n">
         <f aca="false">ROUND(P3*10/$S$2,0)</f>
         <v>8</v>
       </c>
@@ -2470,13 +2488,13 @@
       <c r="X3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Y3" s="7" t="n">
+      <c r="Y3" s="6" t="n">
         <v>0.5625</v>
       </c>
       <c r="Z3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AA3" s="7" t="n">
+      <c r="AA3" s="6" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="AB3" s="1" t="s">
@@ -2485,17 +2503,20 @@
       <c r="AD3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AE3" s="7" t="n">
+      <c r="AE3" s="6" t="n">
         <v>0.570833333333333</v>
       </c>
       <c r="AF3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AG3" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AG3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI3" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
@@ -2542,7 +2563,7 @@
         <f aca="false">M4+N4/2+O4/4</f>
         <v>4</v>
       </c>
-      <c r="Q4" s="6" t="n">
+      <c r="Q4" s="5" t="n">
         <f aca="false">ROUND(P4*10/$S$2,0)</f>
         <v>7</v>
       </c>
@@ -2567,11 +2588,14 @@
       <c r="AF4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AG4" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AG4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI4" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
@@ -2618,7 +2642,7 @@
         <f aca="false">M5+N5/2+O5/4</f>
         <v>5</v>
       </c>
-      <c r="Q5" s="6" t="n">
+      <c r="Q5" s="5" t="n">
         <f aca="false">ROUND(P5*10/$S$2,0)</f>
         <v>8</v>
       </c>
@@ -2628,13 +2652,13 @@
       <c r="V5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="W5" s="7" t="n">
+      <c r="W5" s="6" t="n">
         <v>0.597222222222222</v>
       </c>
       <c r="X5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Y5" s="7" t="n">
+      <c r="Y5" s="6" t="n">
         <v>0.5625</v>
       </c>
       <c r="Z5" s="1" t="s">
@@ -2649,11 +2673,14 @@
       <c r="AF5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AG5" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AG5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI5" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
@@ -2700,18 +2727,18 @@
         <f aca="false">M6+N6/2+O6/4</f>
         <v>2</v>
       </c>
-      <c r="Q6" s="6" t="n">
+      <c r="Q6" s="5" t="n">
         <f aca="false">ROUND(P6*10/$S$2,0)</f>
         <v>3</v>
       </c>
       <c r="T6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="U6" s="7"/>
+      <c r="U6" s="6"/>
       <c r="V6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="W6" s="7" t="n">
+      <c r="W6" s="6" t="n">
         <v>0.548611111111111</v>
       </c>
       <c r="X6" s="1" t="s">
@@ -2723,26 +2750,29 @@
       <c r="AB6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AC6" s="7" t="n">
+      <c r="AC6" s="6" t="n">
         <v>0.597222222222222</v>
       </c>
       <c r="AD6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AE6" s="7" t="n">
+      <c r="AE6" s="6" t="n">
         <v>0.570833333333333</v>
       </c>
       <c r="AF6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AG6" s="5" t="s">
+      <c r="AG6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AH6" s="8" t="n">
+      <c r="AH6" s="6" t="n">
         <v>0.555555555555556</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI6" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
@@ -2789,7 +2819,7 @@
         <f aca="false">M7+N7/2+O7/4</f>
         <v>5</v>
       </c>
-      <c r="Q7" s="6" t="n">
+      <c r="Q7" s="5" t="n">
         <f aca="false">ROUND(P7*10/$S$2,0)</f>
         <v>8</v>
       </c>
@@ -2814,11 +2844,14 @@
       <c r="AF7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AG7" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AG7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI7" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
@@ -2865,7 +2898,7 @@
         <f aca="false">M8+N8/2+O8/4</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="6" t="n">
+      <c r="Q8" s="5" t="n">
         <f aca="false">ROUND(P8*10/$S$2,0)</f>
         <v>0</v>
       </c>
@@ -2878,13 +2911,13 @@
       <c r="X8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Y8" s="7" t="n">
+      <c r="Y8" s="6" t="n">
         <v>0.5625</v>
       </c>
       <c r="Z8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AA8" s="7" t="n">
+      <c r="AA8" s="6" t="n">
         <v>0.583333333333333</v>
       </c>
       <c r="AB8" s="1" t="s">
@@ -2896,11 +2929,14 @@
       <c r="AF8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AG8" s="5" t="s">
+      <c r="AG8" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI8" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
@@ -2947,7 +2983,7 @@
         <f aca="false">M9+N9/2+O9/4</f>
         <v>4</v>
       </c>
-      <c r="Q9" s="6" t="n">
+      <c r="Q9" s="5" t="n">
         <f aca="false">ROUND(P9*10/$S$2,0)</f>
         <v>7</v>
       </c>
@@ -2972,11 +3008,14 @@
       <c r="AF9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AG9" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AG9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI9" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
@@ -2995,7 +3034,7 @@
       <c r="F10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G10" s="6" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="H10" s="1" t="s">
@@ -3026,22 +3065,22 @@
         <f aca="false">M10+N10/2+O10/4</f>
         <v>4.5</v>
       </c>
-      <c r="Q10" s="6" t="n">
+      <c r="Q10" s="5" t="n">
         <f aca="false">ROUND(P10*10/$S$2,0)</f>
         <v>8</v>
       </c>
       <c r="T10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="U10" s="7"/>
+      <c r="U10" s="6"/>
       <c r="V10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="W10" s="7"/>
+      <c r="W10" s="6"/>
       <c r="X10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Y10" s="7" t="n">
+      <c r="Y10" s="6" t="n">
         <v>0.5625</v>
       </c>
       <c r="Z10" s="1" t="s">
@@ -3053,20 +3092,26 @@
       <c r="AD10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AE10" s="7" t="n">
+      <c r="AE10" s="6" t="n">
         <v>0.55</v>
       </c>
       <c r="AF10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AG10" s="5" t="s">
+      <c r="AG10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AH10" s="8" t="n">
+      <c r="AH10" s="6" t="n">
         <v>0.5625</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ10" s="8" t="n">
+        <v>0.555555555555556</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
@@ -3113,7 +3158,7 @@
         <f aca="false">M11+N11/2+O11/4</f>
         <v>6</v>
       </c>
-      <c r="Q11" s="6" t="n">
+      <c r="Q11" s="5" t="n">
         <f aca="false">ROUND(P11*10/$S$2,0)</f>
         <v>10</v>
       </c>
@@ -3138,11 +3183,14 @@
       <c r="AF11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AG11" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AG11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI11" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
@@ -3189,7 +3237,7 @@
         <f aca="false">M12+N12/2+O12/4</f>
         <v>4</v>
       </c>
-      <c r="Q12" s="6" t="n">
+      <c r="Q12" s="5" t="n">
         <f aca="false">ROUND(P12*10/$S$2,0)</f>
         <v>7</v>
       </c>
@@ -3214,11 +3262,14 @@
       <c r="AF12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AG12" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AG12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI12" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
@@ -3249,7 +3300,7 @@
       <c r="K13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L13" s="7" t="n">
+      <c r="L13" s="6" t="n">
         <v>0.614583333333333</v>
       </c>
       <c r="M13" s="1" t="n">
@@ -3268,12 +3319,12 @@
         <f aca="false">M13+N13/2+O13/4</f>
         <v>4.25</v>
       </c>
-      <c r="Q13" s="6" t="n">
+      <c r="Q13" s="5" t="n">
         <f aca="false">ROUND(P13*10/$S$2,0)</f>
         <v>7</v>
       </c>
-      <c r="R13" s="7"/>
-      <c r="S13" s="7"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="6"/>
       <c r="T13" s="1" t="s">
         <v>13</v>
       </c>
@@ -3295,11 +3346,17 @@
       <c r="AF13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AG13" s="5" t="s">
+      <c r="AG13" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI13" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ13" s="8" t="n">
+        <v>0.555555555555556</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
@@ -3318,7 +3375,7 @@
       <c r="F14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="G14" s="6" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="H14" s="1" t="s">
@@ -3333,7 +3390,7 @@
       <c r="K14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L14" s="7" t="n">
+      <c r="L14" s="6" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="M14" s="1" t="n">
@@ -3352,19 +3409,19 @@
         <f aca="false">M14+N14/2+O14/4</f>
         <v>4</v>
       </c>
-      <c r="Q14" s="6" t="n">
+      <c r="Q14" s="5" t="n">
         <f aca="false">ROUND(P14*10/$S$2,0)</f>
         <v>7</v>
       </c>
-      <c r="R14" s="7"/>
-      <c r="S14" s="7"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
       <c r="T14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="V14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="W14" s="7" t="n">
+      <c r="W14" s="6" t="n">
         <v>0.5625</v>
       </c>
       <c r="X14" s="1" t="s">
@@ -3373,7 +3430,7 @@
       <c r="Z14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AA14" s="7" t="n">
+      <c r="AA14" s="6" t="n">
         <v>0.569444444444444</v>
       </c>
       <c r="AB14" s="1" t="s">
@@ -3385,14 +3442,17 @@
       <c r="AF14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AG14" s="5" t="s">
+      <c r="AG14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AH14" s="8" t="n">
+      <c r="AH14" s="6" t="n">
         <v>0.548611111111111</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI14" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
@@ -3443,7 +3503,7 @@
         <f aca="false">ROUND(P15*10/$S$2,0)</f>
         <v>10</v>
       </c>
-      <c r="R15" s="7" t="s">
+      <c r="R15" s="6" t="s">
         <v>53</v>
       </c>
       <c r="T15" s="1" t="s">
@@ -3452,13 +3512,13 @@
       <c r="V15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="W15" s="7" t="n">
+      <c r="W15" s="6" t="n">
         <v>0.597222222222222</v>
       </c>
       <c r="X15" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="Y15" s="7" t="n">
+      <c r="Y15" s="6" t="n">
         <v>0.541666666666667</v>
       </c>
       <c r="Z15" s="1" t="s">
@@ -3473,11 +3533,14 @@
       <c r="AF15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AG15" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AG15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI15" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
@@ -3524,7 +3587,7 @@
         <f aca="false">M16+N16/2+O16/4</f>
         <v>5</v>
       </c>
-      <c r="Q16" s="6" t="n">
+      <c r="Q16" s="5" t="n">
         <f aca="false">ROUND(P16*10/$S$2,0)</f>
         <v>8</v>
       </c>
@@ -3549,11 +3612,14 @@
       <c r="AF16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AG16" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AG16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI16" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
@@ -3600,7 +3666,7 @@
         <f aca="false">M17+N17/2+O17/4</f>
         <v>3</v>
       </c>
-      <c r="Q17" s="6" t="n">
+      <c r="Q17" s="5" t="n">
         <f aca="false">ROUND(P17*10/$S$2,0)</f>
         <v>5</v>
       </c>
@@ -3625,11 +3691,14 @@
       <c r="AF17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AG17" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AG17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI17" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
@@ -3676,7 +3745,7 @@
         <f aca="false">M18+N18/2+O18/4</f>
         <v>5</v>
       </c>
-      <c r="Q18" s="6" t="n">
+      <c r="Q18" s="5" t="n">
         <f aca="false">ROUND(P18*10/$S$2,0)</f>
         <v>8</v>
       </c>
@@ -3686,13 +3755,13 @@
       <c r="V18" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="W18" s="7" t="n">
+      <c r="W18" s="6" t="n">
         <v>0.548611111111111</v>
       </c>
       <c r="X18" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="Y18" s="7" t="n">
+      <c r="Y18" s="6" t="n">
         <v>0.541666666666667</v>
       </c>
       <c r="Z18" s="1" t="s">
@@ -3704,17 +3773,20 @@
       <c r="AD18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AE18" s="7" t="n">
+      <c r="AE18" s="6" t="n">
         <v>0.569444444444444</v>
       </c>
       <c r="AF18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AG18" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AG18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI18" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
@@ -3761,14 +3833,14 @@
         <f aca="false">M19+N19/2+O19/4</f>
         <v>3</v>
       </c>
-      <c r="Q19" s="6" t="n">
+      <c r="Q19" s="5" t="n">
         <f aca="false">ROUND(P19*10/$S$2,0)</f>
         <v>5</v>
       </c>
       <c r="T19" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="U19" s="7" t="n">
+      <c r="U19" s="6" t="n">
         <v>0.611111111111111</v>
       </c>
       <c r="V19" s="1" t="s">
@@ -3780,7 +3852,7 @@
       <c r="Z19" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AA19" s="7" t="n">
+      <c r="AA19" s="6" t="n">
         <v>0.569444444444444</v>
       </c>
       <c r="AB19" s="1" t="s">
@@ -3792,11 +3864,14 @@
       <c r="AF19" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AG19" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AG19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI19" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
@@ -3827,7 +3902,7 @@
       <c r="K20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L20" s="7" t="n">
+      <c r="L20" s="6" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="M20" s="1" t="n">
@@ -3846,19 +3921,19 @@
         <f aca="false">M20+N20/2+O20/4</f>
         <v>3.5</v>
       </c>
-      <c r="Q20" s="6" t="n">
+      <c r="Q20" s="5" t="n">
         <f aca="false">ROUND(P20*10/$S$2,0)</f>
         <v>6</v>
       </c>
-      <c r="R20" s="7"/>
-      <c r="S20" s="7"/>
+      <c r="R20" s="6"/>
+      <c r="S20" s="6"/>
       <c r="T20" s="1" t="s">
         <v>13</v>
       </c>
       <c r="V20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="W20" s="7" t="n">
+      <c r="W20" s="6" t="n">
         <v>0.5625</v>
       </c>
       <c r="X20" s="1" t="s">
@@ -3876,14 +3951,17 @@
       <c r="AF20" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AG20" s="5" t="s">
+      <c r="AG20" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AH20" s="8" t="n">
+      <c r="AH20" s="6" t="n">
         <v>0.555555555555556</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI20" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
@@ -3930,7 +4008,7 @@
         <f aca="false">M21+N21/2+O21/4</f>
         <v>6</v>
       </c>
-      <c r="Q21" s="6" t="n">
+      <c r="Q21" s="5" t="n">
         <f aca="false">ROUND(P21*10/$S$2,0)</f>
         <v>10</v>
       </c>
@@ -3940,7 +4018,7 @@
       <c r="V21" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="W21" s="7"/>
+      <c r="W21" s="6"/>
       <c r="X21" s="1" t="s">
         <v>13</v>
       </c>
@@ -3956,11 +4034,14 @@
       <c r="AF21" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AG21" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AG21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI21" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
@@ -3991,7 +4072,7 @@
       <c r="K22" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L22" s="7" t="n">
+      <c r="L22" s="6" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="M22" s="1" t="n">
@@ -4010,25 +4091,25 @@
         <f aca="false">M22+N22/2+O22/4</f>
         <v>3.5</v>
       </c>
-      <c r="Q22" s="6" t="n">
+      <c r="Q22" s="5" t="n">
         <f aca="false">ROUND(P22*10/$S$2,0)</f>
         <v>6</v>
       </c>
-      <c r="R22" s="7"/>
-      <c r="S22" s="7"/>
+      <c r="R22" s="6"/>
+      <c r="S22" s="6"/>
       <c r="T22" s="1" t="s">
         <v>13</v>
       </c>
       <c r="V22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="W22" s="7" t="n">
+      <c r="W22" s="6" t="n">
         <v>0.5625</v>
       </c>
       <c r="X22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Y22" s="7" t="n">
+      <c r="Y22" s="6" t="n">
         <v>0.5625</v>
       </c>
       <c r="Z22" s="1" t="s">
@@ -4043,11 +4124,14 @@
       <c r="AF22" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AG22" s="5" t="s">
+      <c r="AG22" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI22" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
@@ -4122,11 +4206,14 @@
       <c r="AF23" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AG23" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AG23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI23" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
@@ -4173,7 +4260,7 @@
         <f aca="false">M24+N24/2+O24/4</f>
         <v>5</v>
       </c>
-      <c r="Q24" s="6" t="n">
+      <c r="Q24" s="5" t="n">
         <f aca="false">ROUND(P24*10/$S$2,0)</f>
         <v>8</v>
       </c>
@@ -4198,11 +4285,14 @@
       <c r="AF24" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AG24" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AG24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI24" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
@@ -4249,7 +4339,7 @@
         <f aca="false">M25+N25/2+O25/4</f>
         <v>6</v>
       </c>
-      <c r="Q25" s="6" t="n">
+      <c r="Q25" s="5" t="n">
         <f aca="false">ROUND(P25*10/$S$2,0)</f>
         <v>10</v>
       </c>
@@ -4274,11 +4364,14 @@
       <c r="AF25" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AG25" s="5" t="s">
+      <c r="AG25" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI25" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
@@ -4325,7 +4418,7 @@
         <f aca="false">M26+N26/2+O26/4</f>
         <v>5</v>
       </c>
-      <c r="Q26" s="6" t="n">
+      <c r="Q26" s="5" t="n">
         <f aca="false">ROUND(P26*10/$S$2,0)</f>
         <v>8</v>
       </c>
@@ -4341,7 +4434,7 @@
       <c r="Z26" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AA26" s="7" t="n">
+      <c r="AA26" s="6" t="n">
         <v>0.569444444444444</v>
       </c>
       <c r="AB26" s="1" t="s">
@@ -4353,11 +4446,14 @@
       <c r="AF26" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AG26" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AG26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI26" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
@@ -4404,7 +4500,7 @@
         <f aca="false">M27+N27/2+O27/4</f>
         <v>6</v>
       </c>
-      <c r="Q27" s="6" t="n">
+      <c r="Q27" s="5" t="n">
         <f aca="false">ROUND(P27*10/$S$2,0)</f>
         <v>10</v>
       </c>
@@ -4426,20 +4522,23 @@
       <c r="AD27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AE27" s="7" t="n">
+      <c r="AE27" s="6" t="n">
         <v>0.572916666666667</v>
       </c>
       <c r="AF27" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AG27" s="5" t="s">
+      <c r="AG27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AH27" s="8" t="n">
+      <c r="AH27" s="6" t="n">
         <v>0.604166666666667</v>
       </c>
-    </row>
-    <row r="28" s="1" customFormat="true" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI27" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="n">
         <v>26</v>
       </c>
@@ -4488,7 +4587,7 @@
         <f aca="false">M28+N28/2+O28/4</f>
         <v>3</v>
       </c>
-      <c r="Q28" s="6" t="n">
+      <c r="Q28" s="5" t="n">
         <f aca="false">ROUND(P28*10/$S$2,0)</f>
         <v>5</v>
       </c>
@@ -4501,13 +4600,13 @@
       <c r="V28" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="W28" s="7" t="n">
+      <c r="W28" s="6" t="n">
         <v>0.576388888888889</v>
       </c>
       <c r="X28" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Y28" s="7" t="n">
+      <c r="Y28" s="6" t="n">
         <v>0.583333333333333</v>
       </c>
       <c r="Z28" s="2" t="s">
@@ -4516,13 +4615,13 @@
       <c r="AB28" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AC28" s="7" t="n">
+      <c r="AC28" s="6" t="n">
         <v>0.59375</v>
       </c>
       <c r="AD28" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AE28" s="7" t="n">
+      <c r="AE28" s="6" t="n">
         <v>0.572916666666667</v>
       </c>
       <c r="AF28" s="2" t="s">
@@ -4531,8 +4630,14 @@
       <c r="AG28" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AH28" s="7" t="n">
+      <c r="AH28" s="6" t="n">
         <v>0.583333333333333</v>
+      </c>
+      <c r="AI28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ28" s="6" t="n">
+        <v>0.597222222222222</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4595,6 +4700,11 @@
         <f aca="false">COUNTIF(AG3:AG28,"P")</f>
         <v>16</v>
       </c>
+      <c r="AH29" s="1"/>
+      <c r="AI29" s="1" t="n">
+        <f aca="false">COUNTIF(AI3:AI28,"P")</f>
+        <v>17</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C30" s="1" t="s">
@@ -4628,6 +4738,11 @@
         <f aca="false">COUNTIF(AG3:AG28,"M")</f>
         <v>0</v>
       </c>
+      <c r="AH30" s="1"/>
+      <c r="AI30" s="1" t="n">
+        <f aca="false">COUNTIF(AI3:AI28,"M")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C31" s="1" t="s">
@@ -4661,6 +4776,11 @@
         <f aca="false">COUNTIF(AG3:AG28,"T")</f>
         <v>6</v>
       </c>
+      <c r="AH31" s="1"/>
+      <c r="AI31" s="1" t="n">
+        <f aca="false">COUNTIF(AI3:AI28,"T")</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C32" s="1" t="s">
@@ -4693,6 +4813,11 @@
       <c r="AG32" s="1" t="n">
         <f aca="false">SUM(AG29:AG31)</f>
         <v>22</v>
+      </c>
+      <c r="AH32" s="1"/>
+      <c r="AI32" s="1" t="n">
+        <f aca="false">SUM(AI29:AI31)</f>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -4720,8 +4845,8 @@
   <sheetFormatPr defaultColWidth="9.63671875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
   </cols>
@@ -4731,22 +4856,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4760,10 +4885,10 @@
         <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>9</v>
@@ -4797,10 +4922,10 @@
         <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>10</v>
@@ -4822,10 +4947,10 @@
         <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>6</v>
@@ -4856,10 +4981,10 @@
         <v>27</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>10</v>
@@ -4881,10 +5006,10 @@
         <v>27</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>9</v>
@@ -4895,10 +5020,10 @@
         <v>27</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>9</v>
@@ -4909,10 +5034,10 @@
         <v>27</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>7</v>
@@ -4923,10 +5048,10 @@
         <v>27</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>5</v>
@@ -4937,10 +5062,10 @@
         <v>27</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>4</v>
@@ -4971,10 +5096,10 @@
         <v>33</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -5008,10 +5133,10 @@
         <v>39</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>8</v>
@@ -5045,10 +5170,10 @@
         <v>45</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>9</v>
@@ -5068,10 +5193,10 @@
         <v>48</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>8</v>
@@ -5091,10 +5216,10 @@
         <v>51</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>8</v>
@@ -5116,10 +5241,10 @@
         <v>51</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>7</v>
@@ -5136,10 +5261,10 @@
         <v>55</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>5</v>
@@ -5173,10 +5298,10 @@
         <v>61</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>9</v>
@@ -5196,10 +5321,10 @@
         <v>64</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -5219,10 +5344,10 @@
         <v>67</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>10</v>
@@ -5242,10 +5367,10 @@
         <v>70</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>9</v>
@@ -5279,10 +5404,10 @@
         <v>76</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>8</v>
@@ -5302,10 +5427,10 @@
         <v>80</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>10</v>
@@ -5325,10 +5450,10 @@
         <v>83</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>10</v>
@@ -5348,10 +5473,10 @@
         <v>86</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>10</v>
@@ -5373,10 +5498,10 @@
         <v>86</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>10</v>
@@ -5387,10 +5512,10 @@
         <v>86</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>10</v>
@@ -5401,10 +5526,10 @@
         <v>86</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>10</v>
@@ -5415,10 +5540,10 @@
         <v>86</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>10</v>
@@ -5429,10 +5554,10 @@
         <v>86</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>10</v>
@@ -5443,10 +5568,10 @@
         <v>86</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>10</v>
@@ -5457,10 +5582,10 @@
         <v>86</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="F39" s="1" t="n">
         <v>10</v>
@@ -5471,10 +5596,10 @@
         <v>86</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="F40" s="1" t="n">
         <v>10</v>
@@ -5485,10 +5610,10 @@
         <v>86</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="F41" s="1" t="n">
         <v>10</v>
@@ -5499,10 +5624,10 @@
         <v>86</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="F42" s="1" t="n">
         <v>10</v>
@@ -5513,10 +5638,10 @@
         <v>86</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="F43" s="1" t="n">
         <v>10</v>
@@ -5527,10 +5652,10 @@
         <v>86</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>9</v>
@@ -5541,10 +5666,10 @@
         <v>86</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>7</v>
@@ -5555,10 +5680,10 @@
         <v>86</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="F46" s="1" t="n">
         <v>7</v>
@@ -5575,10 +5700,10 @@
         <v>89</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="F47" s="1" t="n">
         <v>10</v>
@@ -5600,10 +5725,10 @@
         <v>89</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="F48" s="1" t="n">
         <v>3</v>
@@ -5625,7 +5750,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H50" s="1" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="I50" s="1" t="n">
         <f aca="false">COUNTIF(I2:I49,"&gt;0")</f>
@@ -5670,8 +5795,8 @@
   <sheetFormatPr defaultColWidth="9.63671875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
   </cols>
@@ -5681,22 +5806,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5710,10 +5835,10 @@
         <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>7</v>
@@ -5747,10 +5872,10 @@
         <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>9</v>
@@ -5784,10 +5909,10 @@
         <v>27</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>10</v>
@@ -5809,10 +5934,10 @@
         <v>27</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>9</v>
@@ -5823,10 +5948,10 @@
         <v>27</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>2</v>
@@ -5857,10 +5982,10 @@
         <v>33</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>10</v>
@@ -5894,10 +6019,10 @@
         <v>39</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>10</v>
@@ -5931,10 +6056,10 @@
         <v>45</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -5954,10 +6079,10 @@
         <v>48</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -5979,10 +6104,10 @@
         <v>48</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>5</v>
@@ -5999,10 +6124,10 @@
         <v>51</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>8</v>
@@ -6024,10 +6149,10 @@
         <v>51</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>7</v>
@@ -6038,10 +6163,10 @@
         <v>51</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>4</v>
@@ -6052,10 +6177,10 @@
         <v>51</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>4</v>
@@ -6072,10 +6197,10 @@
         <v>55</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>7</v>
@@ -6109,10 +6234,10 @@
         <v>61</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>10</v>
@@ -6132,10 +6257,10 @@
         <v>64</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>8</v>
@@ -6155,10 +6280,10 @@
         <v>67</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -6178,10 +6303,10 @@
         <v>70</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>10</v>
@@ -6215,10 +6340,10 @@
         <v>76</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>8</v>
@@ -6238,10 +6363,10 @@
         <v>80</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>10</v>
@@ -6261,10 +6386,10 @@
         <v>83</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>10</v>
@@ -6284,10 +6409,10 @@
         <v>86</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>10</v>
@@ -6309,10 +6434,10 @@
         <v>86</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>9</v>
@@ -6329,10 +6454,10 @@
         <v>89</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>10</v>
@@ -6354,10 +6479,10 @@
         <v>89</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>3</v>
@@ -6379,7 +6504,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H36" s="1" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="I36" s="1" t="n">
         <f aca="false">COUNTIF(I2:I35,"&gt;0")</f>
@@ -6419,9 +6544,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I41"/>
-  <sheetFormatPr defaultColWidth="9.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.5390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="5.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
@@ -6435,19 +6560,19 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6464,7 +6589,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>7</v>
@@ -6501,7 +6626,7 @@
         <v>19</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>9</v>
@@ -6538,7 +6663,7 @@
         <v>26</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>10</v>
@@ -6561,7 +6686,7 @@
         <v>29</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>9</v>
@@ -6584,7 +6709,7 @@
         <v>32</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>10</v>
@@ -6649,7 +6774,7 @@
         <v>44</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>8</v>
@@ -6686,7 +6811,7 @@
         <v>50</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -6737,7 +6862,7 @@
         <v>60</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>9</v>
@@ -6760,7 +6885,7 @@
         <v>63</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>10</v>
@@ -6783,7 +6908,7 @@
         <v>66</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>10</v>
@@ -6806,7 +6931,7 @@
         <v>69</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>9</v>
@@ -6843,7 +6968,7 @@
         <v>75</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>9</v>
@@ -6866,7 +6991,7 @@
         <v>79</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>10</v>
@@ -6891,7 +7016,7 @@
         <v>79</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>9</v>
@@ -6911,7 +7036,7 @@
         <v>82</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>9</v>
@@ -6936,7 +7061,7 @@
         <v>82</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>9</v>
@@ -6950,7 +7075,7 @@
         <v>82</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>8</v>
@@ -6964,7 +7089,7 @@
         <v>82</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>6</v>
@@ -6978,7 +7103,7 @@
         <v>82</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>6</v>
@@ -6992,7 +7117,7 @@
         <v>82</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>4</v>
@@ -7012,7 +7137,7 @@
         <v>85</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>10</v>
@@ -7037,7 +7162,7 @@
         <v>85</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>10</v>
@@ -7051,7 +7176,7 @@
         <v>85</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>10</v>
@@ -7065,7 +7190,7 @@
         <v>85</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>10</v>
@@ -7079,7 +7204,7 @@
         <v>85</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>9</v>
@@ -7093,7 +7218,7 @@
         <v>85</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>9</v>
@@ -7107,7 +7232,7 @@
         <v>85</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>9</v>
@@ -7121,7 +7246,7 @@
         <v>85</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>9</v>
@@ -7181,10 +7306,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I1048576"/>
-  <sheetFormatPr defaultColWidth="9.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7195,19 +7320,19 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7224,7 +7349,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>10</v>
@@ -7261,7 +7386,7 @@
         <v>19</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>10</v>
@@ -7298,7 +7423,7 @@
         <v>26</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>3</v>
@@ -7323,7 +7448,7 @@
         <v>26</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>9</v>
@@ -7337,7 +7462,7 @@
         <v>26</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>10</v>
@@ -7427,7 +7552,7 @@
         <v>44</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -7464,7 +7589,7 @@
         <v>50</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>10</v>
@@ -7515,7 +7640,7 @@
         <v>60</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>6</v>
@@ -7552,7 +7677,7 @@
         <v>66</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>9</v>
@@ -7575,7 +7700,7 @@
         <v>69</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>9</v>
@@ -7612,7 +7737,7 @@
         <v>75</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>8</v>
@@ -7635,7 +7760,7 @@
         <v>79</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -7658,7 +7783,7 @@
         <v>82</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>10</v>
@@ -7683,7 +7808,7 @@
         <v>82</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>10</v>
@@ -7697,7 +7822,7 @@
         <v>82</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>9</v>
@@ -7711,7 +7836,7 @@
         <v>82</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>9</v>
@@ -7731,7 +7856,7 @@
         <v>85</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>9</v>
@@ -7756,7 +7881,7 @@
         <v>85</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>9</v>
@@ -7770,7 +7895,7 @@
         <v>85</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>10</v>
@@ -7784,7 +7909,7 @@
         <v>85</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>10</v>
@@ -7846,10 +7971,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I40"/>
-  <sheetFormatPr defaultColWidth="9.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.5390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.2"/>
   </cols>
@@ -7862,19 +7987,19 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7891,7 +8016,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>9</v>
@@ -7928,7 +8053,7 @@
         <v>19</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>8</v>
@@ -7965,7 +8090,7 @@
         <v>26</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>8</v>
@@ -7990,7 +8115,7 @@
         <v>26</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>8</v>
@@ -8004,7 +8129,7 @@
         <v>26</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>7</v>
@@ -8018,7 +8143,7 @@
         <v>26</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>2</v>
@@ -8108,7 +8233,7 @@
         <v>44</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>9</v>
@@ -8145,7 +8270,7 @@
         <v>50</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>9</v>
@@ -8196,7 +8321,7 @@
         <v>60</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>7</v>
@@ -8233,7 +8358,7 @@
         <v>66</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>7</v>
@@ -8256,7 +8381,7 @@
         <v>69</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>8</v>
@@ -8293,7 +8418,7 @@
         <v>75</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>8</v>
@@ -8316,7 +8441,7 @@
         <v>79</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>9</v>
@@ -8339,7 +8464,7 @@
         <v>82</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>9</v>
@@ -8364,7 +8489,7 @@
         <v>82</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>9</v>
@@ -8378,7 +8503,7 @@
         <v>82</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>9</v>
@@ -8398,7 +8523,7 @@
         <v>85</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>10</v>
@@ -8423,7 +8548,7 @@
         <v>85</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>10</v>
@@ -8437,7 +8562,7 @@
         <v>85</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>10</v>
@@ -8451,7 +8576,7 @@
         <v>85</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>9</v>
@@ -8465,7 +8590,7 @@
         <v>85</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>9</v>
@@ -8479,7 +8604,7 @@
         <v>85</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>8</v>
@@ -8493,7 +8618,7 @@
         <v>85</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>6</v>
@@ -8507,7 +8632,7 @@
         <v>85</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>6</v>
@@ -8586,7 +8711,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="15.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="40.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="18.97"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="1" width="10.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="1" width="10.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="1" width="22.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="16.41"/>
   </cols>
@@ -8620,8 +8745,8 @@
       <c r="AS1" s="3" t="n">
         <v>45818</v>
       </c>
-      <c r="AT1" s="3" t="s">
-        <v>99</v>
+      <c r="AT1" s="3" t="n">
+        <v>45886</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8632,91 +8757,91 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="R2" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="X2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y2" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="X2" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA2" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z2" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC2" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="AB2" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AD2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE2" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="AF2" s="3" t="n">
         <v>45881</v>
@@ -8725,46 +8850,46 @@
         <v>45874</v>
       </c>
       <c r="AH2" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AI2" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="AI2" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="AJ2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AL2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AN2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AP2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AR2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="AS2" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AT2" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="AT2" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
@@ -8805,30 +8930,30 @@
         <f aca="false">Q3+S3/2</f>
         <v>7</v>
       </c>
-      <c r="U3" s="6" t="n">
+      <c r="U3" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(M3,O3,T3,C3),0)</f>
         <v>8</v>
       </c>
-      <c r="V3" s="6" t="str">
+      <c r="V3" s="5" t="str">
         <f aca="false">IF(U3&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W3" s="6" t="n">
+      <c r="W3" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z3" s="6"/>
-      <c r="AA3" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB3" s="6"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z3" s="5"/>
+      <c r="AA3" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB3" s="5"/>
       <c r="AC3" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AD3" s="6" t="n">
+      <c r="AD3" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(AC3,AA3,Y3,W3,U3),0)</f>
         <v>8</v>
       </c>
@@ -8845,10 +8970,13 @@
         <v>9</v>
       </c>
       <c r="AM3" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="AN3" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="AO3" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AQ3" s="1" t="n">
         <v>1</v>
@@ -8856,8 +8984,11 @@
       <c r="AS3" s="1" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AT3" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
@@ -8898,30 +9029,30 @@
         <f aca="false">Q4+S4/2</f>
         <v>1.5</v>
       </c>
-      <c r="U4" s="6" t="n">
+      <c r="U4" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(M4,O4,T4),0)</f>
         <v>1</v>
       </c>
-      <c r="V4" s="6" t="str">
+      <c r="V4" s="5" t="str">
         <f aca="false">IF(U4&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="W4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="6"/>
-      <c r="AA4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="6"/>
+      <c r="W4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="5"/>
+      <c r="AA4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="5"/>
       <c r="AC4" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AD4" s="6" t="n">
+      <c r="AD4" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(AC4,AA4,Y4,W4,U4),0)</f>
         <v>2</v>
       </c>
@@ -8935,10 +9066,16 @@
         <v>7</v>
       </c>
       <c r="AI4" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="AJ4" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="AK4" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="AL4" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="AM4" s="1" t="n">
         <v>1</v>
@@ -8953,7 +9090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
@@ -8991,30 +9128,30 @@
         <f aca="false">Q5+S5/2</f>
         <v>9.5</v>
       </c>
-      <c r="U5" s="6" t="n">
+      <c r="U5" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(M5,O5,T5),0)</f>
         <v>9</v>
       </c>
-      <c r="V5" s="6" t="str">
+      <c r="V5" s="5" t="str">
         <f aca="false">IF(U5&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W5" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z5" s="6"/>
-      <c r="AA5" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB5" s="6"/>
-      <c r="AC5" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD5" s="6" t="n">
+      <c r="W5" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="X5" s="5"/>
+      <c r="Y5" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z5" s="5"/>
+      <c r="AA5" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB5" s="5"/>
+      <c r="AC5" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD5" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(AC5,AA5,Y5,W5,U5),0)</f>
         <v>9</v>
       </c>
@@ -9025,10 +9162,16 @@
         <v>10</v>
       </c>
       <c r="AI5" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="AJ5" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="AK5" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="AL5" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="AM5" s="1" t="n">
         <v>10</v>
@@ -9043,7 +9186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
@@ -9099,11 +9242,11 @@
         <f aca="false">Q6+S6/2</f>
         <v>13.5</v>
       </c>
-      <c r="U6" s="6" t="n">
+      <c r="U6" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(M6,O6,T6),0)</f>
         <v>8</v>
       </c>
-      <c r="V6" s="6" t="str">
+      <c r="V6" s="5" t="str">
         <f aca="false">IF(U6&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -9125,10 +9268,10 @@
       <c r="AB6" s="15" t="n">
         <v>45848</v>
       </c>
-      <c r="AC6" s="6" t="n">
+      <c r="AC6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="AD6" s="6" t="n">
+      <c r="AD6" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(AC6,AA6,Y6,W6,U6),0)</f>
         <v>7</v>
       </c>
@@ -9145,7 +9288,7 @@
         <v>8</v>
       </c>
       <c r="AL6" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AM6" s="1" t="n">
         <v>8</v>
@@ -9160,7 +9303,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
@@ -9198,30 +9341,30 @@
         <f aca="false">Q7+S7/2</f>
         <v>9</v>
       </c>
-      <c r="U7" s="6" t="n">
+      <c r="U7" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(M7,O7,T7),0)</f>
         <v>10</v>
       </c>
-      <c r="V7" s="6" t="str">
+      <c r="V7" s="5" t="str">
         <f aca="false">IF(U7&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W7" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z7" s="6"/>
-      <c r="AA7" s="6" t="n">
+      <c r="W7" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="X7" s="5"/>
+      <c r="Y7" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z7" s="5"/>
+      <c r="AA7" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="AB7" s="6"/>
-      <c r="AC7" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD7" s="6" t="n">
+      <c r="AB7" s="5"/>
+      <c r="AC7" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD7" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(AC7,AA7,Y7,W7,U7),0)</f>
         <v>9</v>
       </c>
@@ -9229,7 +9372,7 @@
         <v>13</v>
       </c>
       <c r="AH7" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AI7" s="1" t="n">
         <v>1</v>
@@ -9250,7 +9393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" s="16" customFormat="true" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" s="16" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="n">
         <v>6</v>
       </c>
@@ -9288,7 +9431,7 @@
         <f aca="false">Q8+S8/2</f>
         <v>1</v>
       </c>
-      <c r="U8" s="6" t="n">
+      <c r="U8" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(C8,E8,G8,I8,K8,M8,O8,T8),0)</f>
         <v>1</v>
       </c>
@@ -9329,19 +9472,19 @@
         <v>6</v>
       </c>
       <c r="AJ8" s="16" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AK8" s="16" t="n">
         <v>6</v>
       </c>
       <c r="AL8" s="16" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AM8" s="16" t="n">
         <v>6</v>
       </c>
       <c r="AN8" s="16" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AO8" s="16" t="n">
         <v>6</v>
@@ -9350,7 +9493,7 @@
         <v>5</v>
       </c>
       <c r="AR8" s="16" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="AS8" s="16" t="n">
         <v>1</v>
@@ -9359,7 +9502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
@@ -9400,18 +9543,18 @@
         <f aca="false">Q9+S9/2</f>
         <v>10</v>
       </c>
-      <c r="U9" s="6" t="n">
+      <c r="U9" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(M9,O9,T9),0)</f>
         <v>9</v>
       </c>
-      <c r="V9" s="6" t="str">
+      <c r="V9" s="5" t="str">
         <f aca="false">IF(U9&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W9" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="X9" s="6"/>
+      <c r="W9" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="X9" s="5"/>
       <c r="Y9" s="13" t="n">
         <v>9</v>
       </c>
@@ -9424,10 +9567,10 @@
       <c r="AB9" s="12" t="n">
         <v>45849</v>
       </c>
-      <c r="AC9" s="6" t="n">
+      <c r="AC9" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="AD9" s="6" t="n">
+      <c r="AD9" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(AC9,AA9,Y9,W9,U9),0)</f>
         <v>8</v>
       </c>
@@ -9456,7 +9599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
@@ -9512,11 +9655,11 @@
         <f aca="false">Q10+S10/2</f>
         <v>8</v>
       </c>
-      <c r="U10" s="6" t="n">
+      <c r="U10" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(M10,O10,T10),0)</f>
         <v>6</v>
       </c>
-      <c r="V10" s="6" t="str">
+      <c r="V10" s="5" t="str">
         <f aca="false">IF(U10&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
@@ -9538,10 +9681,10 @@
       <c r="AB10" s="12" t="n">
         <v>45848</v>
       </c>
-      <c r="AC10" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD10" s="6" t="n">
+      <c r="AC10" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD10" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(AC10,AA10,Y10,W10,U10),0)</f>
         <v>7</v>
       </c>
@@ -9558,7 +9701,7 @@
         <v>5</v>
       </c>
       <c r="AL10" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="AM10" s="1" t="n">
         <v>8</v>
@@ -9573,7 +9716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
@@ -9611,11 +9754,11 @@
         <f aca="false">Q11+S11/2</f>
         <v>16</v>
       </c>
-      <c r="U11" s="6" t="n">
+      <c r="U11" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(M11,O11,T11),0)</f>
         <v>11</v>
       </c>
-      <c r="V11" s="6" t="str">
+      <c r="V11" s="5" t="str">
         <f aca="false">IF(U11&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -9637,10 +9780,10 @@
       <c r="AB11" s="12" t="n">
         <v>45848</v>
       </c>
-      <c r="AC11" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD11" s="6" t="n">
+      <c r="AC11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD11" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(AC11,AA11,Y11,W11,U11),0)</f>
         <v>9</v>
       </c>
@@ -9657,7 +9800,7 @@
         <v>10</v>
       </c>
       <c r="AL11" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AM11" s="1" t="n">
         <v>10</v>
@@ -9672,7 +9815,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
@@ -9731,11 +9874,11 @@
         <f aca="false">Q12+S12/2</f>
         <v>9</v>
       </c>
-      <c r="U12" s="6" t="n">
+      <c r="U12" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(M12,O12,T12),0)</f>
         <v>8</v>
       </c>
-      <c r="V12" s="6" t="str">
+      <c r="V12" s="5" t="str">
         <f aca="false">IF(U12&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -9751,14 +9894,14 @@
       <c r="Z12" s="12" t="n">
         <v>45848</v>
       </c>
-      <c r="AA12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB12" s="6"/>
-      <c r="AC12" s="6" t="n">
+      <c r="AA12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="5"/>
+      <c r="AC12" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="AD12" s="6" t="n">
+      <c r="AD12" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(AC12,AA12,Y12,W12,U12),0)</f>
         <v>6</v>
       </c>
@@ -9790,7 +9933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>26</v>
       </c>
@@ -9828,30 +9971,30 @@
         <f aca="false">Q13+S13/2</f>
         <v>10.5</v>
       </c>
-      <c r="U13" s="6" t="n">
+      <c r="U13" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(M13,O13,T13),0)</f>
         <v>10</v>
       </c>
-      <c r="V13" s="6" t="str">
+      <c r="V13" s="5" t="str">
         <f aca="false">IF(U13&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W13" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="X13" s="6"/>
-      <c r="Y13" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z13" s="6"/>
-      <c r="AA13" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB13" s="6"/>
-      <c r="AC13" s="6" t="n">
+      <c r="W13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="X13" s="5"/>
+      <c r="Y13" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z13" s="5"/>
+      <c r="AA13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB13" s="5"/>
+      <c r="AC13" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="AD13" s="6" t="n">
+      <c r="AD13" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(AC13,AA13,Y13,W13,U13),0)</f>
         <v>9</v>
       </c>
@@ -9868,7 +10011,7 @@
         <v>5</v>
       </c>
       <c r="AL13" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AM13" s="1" t="n">
         <v>1</v>
@@ -9883,7 +10026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>11</v>
       </c>
@@ -9933,11 +10076,11 @@
         <f aca="false">Q14+S14/2</f>
         <v>8.5</v>
       </c>
-      <c r="U14" s="6" t="n">
+      <c r="U14" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(M14,O14,T14),0)</f>
         <v>9</v>
       </c>
-      <c r="V14" s="6" t="str">
+      <c r="V14" s="5" t="str">
         <f aca="false">IF(U14&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -9959,10 +10102,10 @@
       <c r="AB14" s="12" t="n">
         <v>45848</v>
       </c>
-      <c r="AC14" s="6" t="n">
+      <c r="AC14" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="AD14" s="6" t="n">
+      <c r="AD14" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(AC14,AA14,Y14,W14,U14),0)</f>
         <v>8</v>
       </c>
@@ -9979,13 +10122,13 @@
         <v>5</v>
       </c>
       <c r="AL14" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="AM14" s="1" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>12</v>
       </c>
@@ -10023,30 +10166,30 @@
         <f aca="false">Q15+S15/2</f>
         <v>9</v>
       </c>
-      <c r="U15" s="6" t="n">
+      <c r="U15" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(M15,O15,T15),0)</f>
         <v>9</v>
       </c>
-      <c r="V15" s="6" t="str">
+      <c r="V15" s="5" t="str">
         <f aca="false">IF(U15&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W15" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="X15" s="6"/>
-      <c r="Y15" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z15" s="6"/>
-      <c r="AA15" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB15" s="6"/>
+      <c r="W15" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="X15" s="5"/>
+      <c r="Y15" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z15" s="5"/>
+      <c r="AA15" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB15" s="5"/>
       <c r="AC15" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="AD15" s="6" t="n">
+      <c r="AD15" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(AC15,AA15,Y15,W15,U15),0)</f>
         <v>10</v>
       </c>
@@ -10063,7 +10206,7 @@
         <v>8</v>
       </c>
       <c r="AL15" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="AM15" s="1" t="n">
         <v>8</v>
@@ -10078,7 +10221,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>13</v>
       </c>
@@ -10115,11 +10258,11 @@
       <c r="T16" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="U16" s="6" t="n">
+      <c r="U16" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(M16,O16,T16),0)</f>
         <v>8</v>
       </c>
-      <c r="V16" s="6" t="str">
+      <c r="V16" s="5" t="str">
         <f aca="false">IF(U16&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -10141,10 +10284,10 @@
       <c r="AB16" s="12" t="n">
         <v>45848</v>
       </c>
-      <c r="AC16" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD16" s="6" t="n">
+      <c r="AC16" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD16" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(AC16,AA16,Y16,W16,U16),0)</f>
         <v>7</v>
       </c>
@@ -10158,31 +10301,31 @@
         <v>9</v>
       </c>
       <c r="AJ16" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="AK16" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AL16" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="AM16" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AN16" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AO16" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AP16" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AQ16" s="1" t="n">
         <v>6</v>
       </c>
       <c r="AR16" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AS16" s="1" t="n">
         <v>1</v>
@@ -10191,7 +10334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>14</v>
       </c>
@@ -10253,11 +10396,11 @@
         <f aca="false">Q17+S17/2</f>
         <v>6</v>
       </c>
-      <c r="U17" s="6" t="n">
+      <c r="U17" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(C17,E17,G17,I17,K17,M17,O17,T17),0)</f>
         <v>7</v>
       </c>
-      <c r="V17" s="6" t="str">
+      <c r="V17" s="5" t="str">
         <f aca="false">IF(U17&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -10279,15 +10422,15 @@
       <c r="AB17" s="21" t="n">
         <v>45848</v>
       </c>
-      <c r="AC17" s="6" t="n">
+      <c r="AC17" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="AD17" s="6" t="n">
+      <c r="AD17" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(AC17,AA17,Y17,W17,U17),0)</f>
         <v>7</v>
       </c>
       <c r="AE17" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="AF17" s="1" t="s">
         <v>13</v>
@@ -10302,31 +10445,31 @@
         <v>7</v>
       </c>
       <c r="AJ17" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AK17" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AL17" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AM17" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AN17" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="AO17" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AP17" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="AQ17" s="1" t="n">
         <v>6</v>
       </c>
       <c r="AR17" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="AS17" s="1" t="n">
         <v>1</v>
@@ -10335,7 +10478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>15</v>
       </c>
@@ -10364,7 +10507,7 @@
         <v>9</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="Q18" s="1" t="n">
         <v>10</v>
@@ -10376,30 +10519,30 @@
         <f aca="false">Q18+S18/2</f>
         <v>10.5</v>
       </c>
-      <c r="U18" s="6" t="n">
+      <c r="U18" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(M18,O18,T18),0)</f>
         <v>10</v>
       </c>
-      <c r="V18" s="6" t="str">
+      <c r="V18" s="5" t="str">
         <f aca="false">IF(U18&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W18" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="X18" s="6"/>
-      <c r="Y18" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z18" s="6"/>
-      <c r="AA18" s="6" t="n">
+      <c r="W18" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="X18" s="5"/>
+      <c r="Y18" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="Z18" s="5"/>
+      <c r="AA18" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="AB18" s="6"/>
-      <c r="AC18" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD18" s="6" t="n">
+      <c r="AB18" s="5"/>
+      <c r="AC18" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD18" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(AC18,AA18,Y18,W18,U18),0)</f>
         <v>9</v>
       </c>
@@ -10448,18 +10591,18 @@
         <f aca="false">Q19+S19/2</f>
         <v>8.5</v>
       </c>
-      <c r="U19" s="6" t="n">
+      <c r="U19" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(M19,O19,T19),0)</f>
         <v>9</v>
       </c>
-      <c r="V19" s="6" t="str">
+      <c r="V19" s="5" t="str">
         <f aca="false">IF(U19&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W19" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="X19" s="6"/>
+      <c r="W19" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="X19" s="5"/>
       <c r="Y19" s="22" t="n">
         <v>9</v>
       </c>
@@ -10472,10 +10615,10 @@
       <c r="AB19" s="12" t="n">
         <v>45848</v>
       </c>
-      <c r="AC19" s="6" t="n">
+      <c r="AC19" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="AD19" s="6" t="n">
+      <c r="AD19" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(AC19,AA19,Y19,W19,U19),0)</f>
         <v>8</v>
       </c>
@@ -10489,31 +10632,31 @@
         <v>6</v>
       </c>
       <c r="AJ19" s="1" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="AK19" s="1" t="n">
         <v>5</v>
       </c>
       <c r="AL19" s="1" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="AM19" s="1" t="n">
         <v>6</v>
       </c>
       <c r="AN19" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="AO19" s="1" t="n">
         <v>6</v>
       </c>
       <c r="AP19" s="1" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AQ19" s="1" t="n">
         <v>5</v>
       </c>
       <c r="AR19" s="1" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AS19" s="1" t="n">
         <v>1</v>
@@ -10522,7 +10665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>17</v>
       </c>
@@ -10560,30 +10703,30 @@
         <f aca="false">Q20+S20/2</f>
         <v>10.5</v>
       </c>
-      <c r="U20" s="6" t="n">
+      <c r="U20" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(M20,O20,T20),0)</f>
         <v>10</v>
       </c>
-      <c r="V20" s="6" t="str">
+      <c r="V20" s="5" t="str">
         <f aca="false">IF(U20&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W20" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="X20" s="6"/>
-      <c r="Y20" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z20" s="6"/>
-      <c r="AA20" s="6" t="n">
+      <c r="W20" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="X20" s="5"/>
+      <c r="Y20" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z20" s="5"/>
+      <c r="AA20" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="AB20" s="6"/>
-      <c r="AC20" s="6" t="n">
+      <c r="AB20" s="5"/>
+      <c r="AC20" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="AD20" s="6" t="n">
+      <c r="AD20" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(AC20,AA20,Y20,W20,U20),0)</f>
         <v>8</v>
       </c>
@@ -10594,7 +10737,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>18</v>
       </c>
@@ -10632,30 +10775,30 @@
         <f aca="false">Q21+S21/2</f>
         <v>11</v>
       </c>
-      <c r="U21" s="6" t="n">
+      <c r="U21" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(M21,O21,T21),0)</f>
         <v>10</v>
       </c>
-      <c r="V21" s="6" t="str">
+      <c r="V21" s="5" t="str">
         <f aca="false">IF(U21&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W21" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="X21" s="6"/>
-      <c r="Y21" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z21" s="6"/>
-      <c r="AA21" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB21" s="6"/>
-      <c r="AC21" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD21" s="6" t="n">
+      <c r="W21" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="X21" s="5"/>
+      <c r="Y21" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z21" s="5"/>
+      <c r="AA21" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB21" s="5"/>
+      <c r="AC21" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD21" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(AC21,AA21,Y21,W21,U21),0)</f>
         <v>9</v>
       </c>
@@ -10666,7 +10809,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>19</v>
       </c>
@@ -10704,30 +10847,30 @@
         <f aca="false">Q22+S22/2</f>
         <v>2</v>
       </c>
-      <c r="U22" s="6" t="n">
+      <c r="U22" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(C22,E22,G22,I22,K22,M22,O22,T22),0)</f>
         <v>2</v>
       </c>
-      <c r="V22" s="6" t="str">
+      <c r="V22" s="5" t="str">
         <f aca="false">IF(U22&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="W22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="X22" s="6"/>
-      <c r="Y22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z22" s="6"/>
-      <c r="AA22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB22" s="6"/>
-      <c r="AC22" s="6" t="n">
+      <c r="W22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X22" s="5"/>
+      <c r="Y22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="5"/>
+      <c r="AA22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="5"/>
+      <c r="AC22" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="AD22" s="6" t="n">
+      <c r="AD22" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(AC22,AA22,Y22,W22,U22),0)</f>
         <v>2</v>
       </c>
@@ -10741,7 +10884,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>20</v>
       </c>
@@ -10782,30 +10925,30 @@
         <f aca="false">Q23+S23/2</f>
         <v>8</v>
       </c>
-      <c r="U23" s="6" t="n">
+      <c r="U23" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(M23,O23,T23),0)</f>
         <v>8</v>
       </c>
-      <c r="V23" s="6" t="str">
+      <c r="V23" s="5" t="str">
         <f aca="false">IF(U23&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W23" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="X23" s="6"/>
-      <c r="Y23" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z23" s="6"/>
-      <c r="AA23" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB23" s="6"/>
+      <c r="W23" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="X23" s="5"/>
+      <c r="Y23" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z23" s="5"/>
+      <c r="AA23" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB23" s="5"/>
       <c r="AC23" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="AD23" s="6" t="n">
+      <c r="AD23" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(AC23,AA23,Y23,W23,U23),0)</f>
         <v>8</v>
       </c>
@@ -10816,7 +10959,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
         <v>21</v>
       </c>
@@ -10854,30 +10997,30 @@
         <f aca="false">Q24+S24/2</f>
         <v>11.5</v>
       </c>
-      <c r="U24" s="6" t="n">
+      <c r="U24" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(M24,O24,T24),0)</f>
         <v>11</v>
       </c>
-      <c r="V24" s="6" t="str">
+      <c r="V24" s="5" t="str">
         <f aca="false">IF(U24&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W24" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="X24" s="6"/>
-      <c r="Y24" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB24" s="6"/>
-      <c r="AC24" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD24" s="6" t="n">
+      <c r="W24" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="X24" s="5"/>
+      <c r="Y24" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z24" s="5"/>
+      <c r="AA24" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB24" s="5"/>
+      <c r="AC24" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD24" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(AC24,AA24,Y24,W24,U24),0)</f>
         <v>10</v>
       </c>
@@ -10903,7 +11046,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <v>22</v>
       </c>
@@ -10941,29 +11084,29 @@
         <f aca="false">Q25+S25/2</f>
         <v>16.5</v>
       </c>
-      <c r="U25" s="6" t="n">
+      <c r="U25" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(M25,O25,T25),0)</f>
         <v>12</v>
       </c>
-      <c r="V25" s="6" t="str">
+      <c r="V25" s="5" t="str">
         <f aca="false">IF(U25&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
       <c r="W25" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="Y25" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z25" s="6"/>
-      <c r="AA25" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB25" s="6"/>
-      <c r="AC25" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD25" s="6" t="n">
+      <c r="Y25" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z25" s="5"/>
+      <c r="AA25" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB25" s="5"/>
+      <c r="AC25" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD25" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(AC25,AA25,Y25,W25,U25),0)</f>
         <v>10</v>
       </c>
@@ -10974,7 +11117,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
         <v>23</v>
       </c>
@@ -11012,11 +11155,11 @@
         <f aca="false">Q26+S26/2</f>
         <v>13.5</v>
       </c>
-      <c r="U26" s="6" t="n">
+      <c r="U26" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(M26,O26,T26),0)</f>
         <v>11</v>
       </c>
-      <c r="V26" s="6" t="str">
+      <c r="V26" s="5" t="str">
         <f aca="false">IF(U26&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -11029,10 +11172,10 @@
       <c r="AA26" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AC26" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD26" s="6" t="n">
+      <c r="AC26" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD26" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(AC26,AA26,Y26,W26,U26),0)</f>
         <v>10</v>
       </c>
@@ -11058,7 +11201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>24</v>
       </c>
@@ -11096,11 +11239,11 @@
         <f aca="false">Q27+S27/2</f>
         <v>10.5</v>
       </c>
-      <c r="U27" s="6" t="n">
+      <c r="U27" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(M27,O27,T27),0)</f>
         <v>9</v>
       </c>
-      <c r="V27" s="6" t="str">
+      <c r="V27" s="5" t="str">
         <f aca="false">IF(U27&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -11122,10 +11265,10 @@
       <c r="AB27" s="12" t="n">
         <v>45848</v>
       </c>
-      <c r="AC27" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD27" s="6" t="n">
+      <c r="AC27" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD27" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(AC27,AA27,Y27,W27,U27),0)</f>
         <v>8</v>
       </c>
@@ -11151,7 +11294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
         <v>25</v>
       </c>
@@ -11198,11 +11341,11 @@
         <f aca="false">Q28+S28/2</f>
         <v>7.5</v>
       </c>
-      <c r="U28" s="6" t="n">
+      <c r="U28" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(M28,O28,T28),0)</f>
         <v>8</v>
       </c>
-      <c r="V28" s="6" t="str">
+      <c r="V28" s="5" t="str">
         <f aca="false">IF(U28&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -11218,7 +11361,7 @@
       <c r="AC28" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AD28" s="6" t="n">
+      <c r="AD28" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(AC28,AA28,Y28,W28,U28),0)</f>
         <v>7</v>
       </c>
@@ -11296,7 +11439,7 @@
         <v>45804</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11716,8 +11859,8 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="21.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.2"/>
   </cols>
   <sheetData>
@@ -11727,22 +11870,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11756,10 +11899,10 @@
         <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>10</v>
@@ -11781,10 +11924,10 @@
         <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>5</v>
@@ -11801,10 +11944,10 @@
         <v>17</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>1</v>
@@ -11824,10 +11967,10 @@
         <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>6</v>
@@ -11847,10 +11990,10 @@
         <v>23</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>7</v>
@@ -11872,10 +12015,10 @@
         <v>23</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>6</v>
@@ -11886,10 +12029,10 @@
         <v>23</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>6</v>
@@ -11900,10 +12043,10 @@
         <v>23</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>5</v>
@@ -11914,10 +12057,10 @@
         <v>23</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>4</v>
@@ -11962,10 +12105,10 @@
         <v>33</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>8</v>
@@ -11985,10 +12128,10 @@
         <v>36</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -12010,10 +12153,10 @@
         <v>36</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>8</v>
@@ -12030,10 +12173,10 @@
         <v>39</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>10</v>
@@ -12053,10 +12196,10 @@
         <v>42</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>10</v>
@@ -12076,10 +12219,10 @@
         <v>45</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>0</v>
@@ -12113,10 +12256,10 @@
         <v>51</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>10</v>
@@ -12136,10 +12279,10 @@
         <v>55</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>8</v>
@@ -12173,10 +12316,10 @@
         <v>61</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>9</v>
@@ -12198,10 +12341,10 @@
         <v>61</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>5</v>
@@ -12218,10 +12361,10 @@
         <v>64</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>7</v>
@@ -12241,10 +12384,10 @@
         <v>67</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>7</v>
@@ -12264,10 +12407,10 @@
         <v>70</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>10</v>
@@ -12287,10 +12430,10 @@
         <v>73</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>10</v>
@@ -12312,10 +12455,10 @@
         <v>73</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>8</v>
@@ -12326,10 +12469,10 @@
         <v>73</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>8</v>
@@ -12340,10 +12483,10 @@
         <v>73</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>8</v>
@@ -12354,10 +12497,10 @@
         <v>73</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>5</v>
@@ -12368,10 +12511,10 @@
         <v>73</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>1</v>
@@ -12388,10 +12531,10 @@
         <v>76</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>9</v>
@@ -12413,10 +12556,10 @@
         <v>76</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>6</v>
@@ -12433,10 +12576,10 @@
         <v>80</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>10</v>
@@ -12458,10 +12601,10 @@
         <v>80</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>9</v>
@@ -12472,10 +12615,10 @@
         <v>80</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>6</v>
@@ -12492,10 +12635,10 @@
         <v>83</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="F39" s="1" t="n">
         <v>10</v>
@@ -12515,10 +12658,10 @@
         <v>86</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="F40" s="1" t="n">
         <v>10</v>
@@ -12540,10 +12683,10 @@
         <v>86</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="F41" s="1" t="n">
         <v>10</v>
@@ -12554,10 +12697,10 @@
         <v>86</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F42" s="1" t="n">
         <v>9</v>
@@ -12568,10 +12711,10 @@
         <v>86</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="F43" s="1" t="n">
         <v>9</v>
@@ -12588,10 +12731,10 @@
         <v>89</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>9</v>
@@ -12613,10 +12756,10 @@
         <v>89</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>8</v>
@@ -12627,10 +12770,10 @@
         <v>89</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="F46" s="1" t="n">
         <v>7</v>
@@ -12641,10 +12784,10 @@
         <v>89</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="F47" s="1" t="n">
         <v>3</v>
@@ -12702,7 +12845,7 @@
   <sheetFormatPr defaultColWidth="9.63671875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.2"/>
   </cols>
   <sheetData>
@@ -12711,22 +12854,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12740,10 +12883,10 @@
         <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>10</v>
@@ -12765,10 +12908,10 @@
         <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>9</v>
@@ -12779,10 +12922,10 @@
         <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>6</v>
@@ -12813,10 +12956,10 @@
         <v>20</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>8</v>
@@ -12838,10 +12981,10 @@
         <v>20</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>7</v>
@@ -12852,10 +12995,10 @@
         <v>20</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>6</v>
@@ -12914,10 +13057,10 @@
         <v>33</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>8</v>
@@ -12951,10 +13094,10 @@
         <v>39</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>9</v>
@@ -12988,10 +13131,10 @@
         <v>45</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>7</v>
@@ -13025,10 +13168,10 @@
         <v>51</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>10</v>
@@ -13048,10 +13191,10 @@
         <v>55</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>9</v>
@@ -13085,10 +13228,10 @@
         <v>61</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>7</v>
@@ -13108,10 +13251,10 @@
         <v>64</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>9</v>
@@ -13133,10 +13276,10 @@
         <v>64</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>6</v>
@@ -13167,10 +13310,10 @@
         <v>70</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>9</v>
@@ -13192,10 +13335,10 @@
         <v>70</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>7</v>
@@ -13226,10 +13369,10 @@
         <v>76</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>10</v>
@@ -13249,10 +13392,10 @@
         <v>80</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>10</v>
@@ -13272,10 +13415,10 @@
         <v>83</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>10</v>
@@ -13297,10 +13440,10 @@
         <v>83</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>10</v>
@@ -13311,10 +13454,10 @@
         <v>83</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>10</v>
@@ -13325,10 +13468,10 @@
         <v>83</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>8</v>
@@ -13345,10 +13488,10 @@
         <v>86</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>10</v>
@@ -13368,10 +13511,10 @@
         <v>89</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>10</v>
@@ -13391,10 +13534,10 @@
         <v>92</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>5</v>
@@ -13438,8 +13581,8 @@
   <sheetFormatPr defaultColWidth="9.63671875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.2"/>
   </cols>
   <sheetData>
@@ -13449,22 +13592,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13478,10 +13621,10 @@
         <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>10</v>
@@ -13515,10 +13658,10 @@
         <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>10</v>
@@ -13580,10 +13723,10 @@
         <v>33</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>9</v>
@@ -13617,10 +13760,10 @@
         <v>39</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>10</v>
@@ -13654,10 +13797,10 @@
         <v>45</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>6</v>
@@ -13679,10 +13822,10 @@
         <v>45</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>10</v>
@@ -13713,10 +13856,10 @@
         <v>51</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>9</v>
@@ -13736,10 +13879,10 @@
         <v>55</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>9</v>
@@ -13773,10 +13916,10 @@
         <v>61</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>10</v>
@@ -13796,10 +13939,10 @@
         <v>64</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>9</v>
@@ -13821,10 +13964,10 @@
         <v>64</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>5</v>
@@ -13835,10 +13978,10 @@
         <v>64</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>9</v>
@@ -13869,10 +14012,10 @@
         <v>70</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>10</v>
@@ -13906,10 +14049,10 @@
         <v>76</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -13929,10 +14072,10 @@
         <v>80</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>10</v>
@@ -13952,10 +14095,10 @@
         <v>83</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>10</v>
@@ -13975,10 +14118,10 @@
         <v>86</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>10</v>
@@ -13998,10 +14141,10 @@
         <v>89</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>10</v>
@@ -14055,8 +14198,8 @@
   <sheetFormatPr defaultColWidth="9.63671875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.2"/>
   </cols>
   <sheetData>
@@ -14065,22 +14208,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14122,10 +14265,10 @@
         <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>10</v>
@@ -14215,10 +14358,10 @@
         <v>39</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>10</v>
@@ -14240,10 +14383,10 @@
         <v>39</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>8</v>
@@ -14302,10 +14445,10 @@
         <v>51</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -14325,10 +14468,10 @@
         <v>55</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>9</v>
@@ -14362,10 +14505,10 @@
         <v>61</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>7</v>
@@ -14385,10 +14528,10 @@
         <v>64</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>9</v>
@@ -14408,10 +14551,10 @@
         <v>67</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>7</v>
@@ -14431,10 +14574,10 @@
         <v>70</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>9</v>
@@ -14456,10 +14599,10 @@
         <v>70</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>6</v>
@@ -14504,10 +14647,10 @@
         <v>80</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -14527,10 +14670,10 @@
         <v>83</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>10</v>
@@ -14550,10 +14693,10 @@
         <v>86</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>10</v>
@@ -14573,10 +14716,10 @@
         <v>89</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>8</v>
@@ -14637,8 +14780,8 @@
   <sheetFormatPr defaultColWidth="9.63671875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="21.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
   </cols>
@@ -14648,22 +14791,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14677,10 +14820,10 @@
         <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>8</v>
@@ -14714,10 +14857,10 @@
         <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>8</v>
@@ -14737,10 +14880,10 @@
         <v>23</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>6</v>
@@ -14760,10 +14903,10 @@
         <v>27</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>10</v>
@@ -14797,10 +14940,10 @@
         <v>33</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>8</v>
@@ -14834,10 +14977,10 @@
         <v>39</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>8</v>
@@ -14859,10 +15002,10 @@
         <v>39</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>7</v>
@@ -14893,10 +15036,10 @@
         <v>45</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>9</v>
@@ -14916,10 +15059,10 @@
         <v>48</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -14939,10 +15082,10 @@
         <v>51</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -14964,10 +15107,10 @@
         <v>51</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>9</v>
@@ -14978,10 +15121,10 @@
         <v>51</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>9</v>
@@ -14992,10 +15135,10 @@
         <v>51</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>7</v>
@@ -15006,10 +15149,10 @@
         <v>51</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>6</v>
@@ -15026,10 +15169,10 @@
         <v>55</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>9</v>
@@ -15063,10 +15206,10 @@
         <v>61</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>7</v>
@@ -15086,10 +15229,10 @@
         <v>64</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>9</v>
@@ -15109,10 +15252,10 @@
         <v>67</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>7</v>
@@ -15132,10 +15275,10 @@
         <v>70</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -15169,10 +15312,10 @@
         <v>76</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>9</v>
@@ -15192,10 +15335,10 @@
         <v>80</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>10</v>
@@ -15217,10 +15360,10 @@
         <v>80</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>9</v>
@@ -15231,10 +15374,10 @@
         <v>80</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>6</v>
@@ -15245,10 +15388,10 @@
         <v>80</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>6</v>
@@ -15259,10 +15402,10 @@
         <v>80</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>6</v>
@@ -15273,10 +15416,10 @@
         <v>80</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>5</v>
@@ -15293,10 +15436,10 @@
         <v>83</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>10</v>
@@ -15316,10 +15459,10 @@
         <v>86</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>10</v>
@@ -15339,16 +15482,16 @@
         <v>89</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>8</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="H36" s="1" t="n">
         <v>8</v>
@@ -15363,10 +15506,10 @@
         <v>89</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>8</v>
@@ -15377,10 +15520,10 @@
         <v>89</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>5</v>
@@ -15438,8 +15581,8 @@
   <sheetFormatPr defaultColWidth="9.63671875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
   </cols>
@@ -15449,22 +15592,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15478,10 +15621,10 @@
         <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>8</v>
@@ -15515,10 +15658,10 @@
         <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>8</v>
@@ -15540,10 +15683,10 @@
         <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>7</v>
@@ -15560,10 +15703,10 @@
         <v>23</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>2</v>
@@ -15583,10 +15726,10 @@
         <v>27</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>10</v>
@@ -15608,10 +15751,10 @@
         <v>27</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>9</v>
@@ -15622,10 +15765,10 @@
         <v>27</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>7</v>
@@ -15636,10 +15779,10 @@
         <v>27</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>6</v>
@@ -15650,10 +15793,10 @@
         <v>27</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>4</v>
@@ -15684,10 +15827,10 @@
         <v>33</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>8</v>
@@ -15721,10 +15864,10 @@
         <v>39</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -15758,10 +15901,10 @@
         <v>45</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>10</v>
@@ -15781,10 +15924,10 @@
         <v>48</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>9</v>
@@ -15806,10 +15949,10 @@
         <v>48</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>8</v>
@@ -15820,10 +15963,10 @@
         <v>48</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>3</v>
@@ -15840,10 +15983,10 @@
         <v>51</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>10</v>
@@ -15865,10 +16008,10 @@
         <v>51</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>8</v>
@@ -15879,10 +16022,10 @@
         <v>51</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>8</v>
@@ -15899,10 +16042,10 @@
         <v>55</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>9</v>
@@ -15936,10 +16079,10 @@
         <v>61</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>9</v>
@@ -15959,10 +16102,10 @@
         <v>64</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>10</v>
@@ -15984,10 +16127,10 @@
         <v>64</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>6</v>
@@ -16004,10 +16147,10 @@
         <v>67</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>8</v>
@@ -16027,10 +16170,10 @@
         <v>70</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>9</v>
@@ -16064,10 +16207,10 @@
         <v>76</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>8</v>
@@ -16087,10 +16230,10 @@
         <v>80</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>10</v>
@@ -16110,10 +16253,10 @@
         <v>83</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>9</v>
@@ -16133,10 +16276,10 @@
         <v>86</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>10</v>
@@ -16156,10 +16299,10 @@
         <v>89</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>8</v>
@@ -16184,7 +16327,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H38" s="1" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="I38" s="1" t="n">
         <f aca="false">COUNTIF(I2:I37,"&gt;0")</f>

--- a/inasistencias-6A-sistDeCtrolVirtual/Alumnos-6A-SistDeCtrolVirtual.xlsx
+++ b/inasistencias-6A-sistDeCtrolVirtual/Alumnos-6A-SistDeCtrolVirtual.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2180" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2194" uniqueCount="679">
   <si>
     <t xml:space="preserve">total</t>
   </si>
@@ -440,6 +440,9 @@
     <t xml:space="preserve">Final</t>
   </si>
   <si>
+    <t xml:space="preserve">nota Dic</t>
+  </si>
+  <si>
     <t xml:space="preserve">se subio 22/4</t>
   </si>
   <si>
@@ -488,6 +491,9 @@
     <t xml:space="preserve">Se subio 11/11/2025</t>
   </si>
   <si>
+    <t xml:space="preserve">Recup dic</t>
+  </si>
+  <si>
     <t xml:space="preserve">se subio el 16/9, tiene mal el nomb</t>
   </si>
   <si>
@@ -603,6 +609,9 @@
   </si>
   <si>
     <t xml:space="preserve">16/09/2025 atrasado no hace lo soliticado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recup intensif</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -2124,7 +2133,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2146,7 +2155,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF9800"/>
-        <bgColor rgb="FFFFC107"/>
+        <bgColor rgb="FFFFBF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -2169,8 +2178,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFBF00"/>
+        <bgColor rgb="FFFFC107"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC107"/>
-        <bgColor rgb="FFFFD428"/>
+        <bgColor rgb="FFFFBF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -2243,6 +2258,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2256,6 +2275,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2307,11 +2334,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2319,19 +2346,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2343,11 +2358,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2355,11 +2370,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2540,7 +2555,7 @@
       <rgbColor rgb="FFFFFFCC"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FFFFBF00"/>
       <rgbColor rgb="FF0066CC"/>
       <rgbColor rgb="FFCCCCFF"/>
       <rgbColor rgb="FF000080"/>
@@ -2883,6 +2898,12 @@
       <c r="AX2" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="AY2" s="7" t="n">
+        <v>45993</v>
+      </c>
+      <c r="AZ2" s="7" t="n">
+        <v>46000</v>
+      </c>
       <c r="BA2" s="3" t="s">
         <v>13</v>
       </c>
@@ -2890,7 +2911,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
@@ -2937,7 +2958,7 @@
         <f aca="false">M3+N3/2+O3/4</f>
         <v>5</v>
       </c>
-      <c r="Q3" s="7" t="n">
+      <c r="Q3" s="8" t="n">
         <f aca="false">ROUND(P3*10/$S$2,0)</f>
         <v>8</v>
       </c>
@@ -2950,13 +2971,13 @@
       <c r="X3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Y3" s="8" t="n">
+      <c r="Y3" s="9" t="n">
         <v>0.5625</v>
       </c>
       <c r="Z3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AA3" s="8" t="n">
+      <c r="AA3" s="9" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="AB3" s="1" t="s">
@@ -2965,7 +2986,7 @@
       <c r="AD3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AE3" s="8" t="n">
+      <c r="AE3" s="9" t="n">
         <v>0.570833333333333</v>
       </c>
       <c r="AF3" s="1" t="s">
@@ -2980,7 +3001,7 @@
       <c r="AK3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AL3" s="8" t="n">
+      <c r="AL3" s="9" t="n">
         <v>0.541666666666667</v>
       </c>
       <c r="AM3" s="3" t="s">
@@ -2989,13 +3010,13 @@
       <c r="AO3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AP3" s="8" t="n">
+      <c r="AP3" s="9" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="AQ3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AR3" s="9" t="n">
+      <c r="AR3" s="10" t="n">
         <v>0.5625</v>
       </c>
       <c r="AS3" s="2" t="s">
@@ -3013,7 +3034,7 @@
         <f aca="false">COUNTIF(T3:AO3,"T")</f>
         <v>4</v>
       </c>
-      <c r="AX3" s="7" t="n">
+      <c r="AX3" s="8" t="n">
         <f aca="false">ROUND((AU3+AV3/2+AW3/4)*10/12,0)</f>
         <v>5</v>
       </c>
@@ -3025,7 +3046,7 @@
       <c r="B4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="11" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -3065,7 +3086,7 @@
         <f aca="false">M4+N4/2+O4/4</f>
         <v>4</v>
       </c>
-      <c r="Q4" s="7" t="n">
+      <c r="Q4" s="8" t="n">
         <f aca="false">ROUND(P4*10/$S$2,0)</f>
         <v>7</v>
       </c>
@@ -3123,12 +3144,18 @@
         <f aca="false">COUNTIF(T4:AS4,"T")</f>
         <v>0</v>
       </c>
-      <c r="AX4" s="7" t="n">
+      <c r="AX4" s="8" t="n">
         <f aca="false">ROUND((AU4+AV4/2+AW4/4)*10/12,0)</f>
         <v>10</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AY4" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="AZ4" s="12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
@@ -3175,7 +3202,7 @@
         <f aca="false">M5+N5/2+O5/4</f>
         <v>5</v>
       </c>
-      <c r="Q5" s="7" t="n">
+      <c r="Q5" s="8" t="n">
         <f aca="false">ROUND(P5*10/$S$2,0)</f>
         <v>8</v>
       </c>
@@ -3185,13 +3212,13 @@
       <c r="V5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="W5" s="8" t="n">
+      <c r="W5" s="9" t="n">
         <v>0.597222222222222</v>
       </c>
       <c r="X5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Y5" s="8" t="n">
+      <c r="Y5" s="9" t="n">
         <v>0.5625</v>
       </c>
       <c r="Z5" s="1" t="s">
@@ -3239,12 +3266,12 @@
         <f aca="false">COUNTIF(T5:AO5,"T")</f>
         <v>2</v>
       </c>
-      <c r="AX5" s="7" t="n">
+      <c r="AX5" s="8" t="n">
         <f aca="false">ROUND((AU5+AV5/2+AW5/4)*10/12,0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
@@ -3291,18 +3318,18 @@
         <f aca="false">M6+N6/2+O6/4</f>
         <v>2</v>
       </c>
-      <c r="Q6" s="7" t="n">
+      <c r="Q6" s="8" t="n">
         <f aca="false">ROUND(P6*10/$S$2,0)</f>
         <v>3</v>
       </c>
       <c r="T6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="U6" s="8"/>
+      <c r="U6" s="9"/>
       <c r="V6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W6" s="8" t="n">
+      <c r="W6" s="9" t="n">
         <v>0.548611111111111</v>
       </c>
       <c r="X6" s="1" t="s">
@@ -3314,13 +3341,13 @@
       <c r="AB6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AC6" s="8" t="n">
+      <c r="AC6" s="9" t="n">
         <v>0.597222222222222</v>
       </c>
       <c r="AD6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AE6" s="8" t="n">
+      <c r="AE6" s="9" t="n">
         <v>0.570833333333333</v>
       </c>
       <c r="AF6" s="1" t="s">
@@ -3329,7 +3356,7 @@
       <c r="AG6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AH6" s="8" t="n">
+      <c r="AH6" s="9" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="AI6" s="3" t="s">
@@ -3347,7 +3374,7 @@
       <c r="AQ6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AR6" s="9" t="n">
+      <c r="AR6" s="10" t="n">
         <v>0.5625</v>
       </c>
       <c r="AS6" s="2" t="s">
@@ -3365,19 +3392,19 @@
         <f aca="false">COUNTIF(T6:AO6,"T")</f>
         <v>3</v>
       </c>
-      <c r="AX6" s="7" t="n">
+      <c r="AX6" s="8" t="n">
         <f aca="false">ROUND((AU6+AV6/2+AW6/4)*10/12,0)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="11" t="s">
         <v>32</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -3417,7 +3444,7 @@
         <f aca="false">M7+N7/2+O7/4</f>
         <v>5</v>
       </c>
-      <c r="Q7" s="7" t="n">
+      <c r="Q7" s="8" t="n">
         <f aca="false">ROUND(P7*10/$S$2,0)</f>
         <v>8</v>
       </c>
@@ -3454,7 +3481,7 @@
       <c r="AM7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="AN7" s="8" t="n">
+      <c r="AN7" s="9" t="n">
         <v>0.576388888888889</v>
       </c>
       <c r="AO7" s="3" t="s">
@@ -3478,7 +3505,7 @@
         <f aca="false">COUNTIF(T7:AS7,"T")</f>
         <v>1</v>
       </c>
-      <c r="AX7" s="7" t="n">
+      <c r="AX7" s="8" t="n">
         <f aca="false">ROUND((AU7+AV7/2+AW7/4)*10/12,0)</f>
         <v>10</v>
       </c>
@@ -3490,7 +3517,7 @@
       <c r="B8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="11" t="s">
         <v>35</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -3530,7 +3557,7 @@
         <f aca="false">M8+N8/2+O8/4</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="7" t="n">
+      <c r="Q8" s="8" t="n">
         <f aca="false">ROUND(P8*10/$S$2,0)</f>
         <v>0</v>
       </c>
@@ -3543,13 +3570,13 @@
       <c r="X8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Y8" s="8" t="n">
+      <c r="Y8" s="9" t="n">
         <v>0.5625</v>
       </c>
       <c r="Z8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AA8" s="8" t="n">
+      <c r="AA8" s="9" t="n">
         <v>0.583333333333333</v>
       </c>
       <c r="AB8" s="1" t="s">
@@ -3594,12 +3621,18 @@
         <f aca="false">COUNTIF(T8:AS8,"T")</f>
         <v>2</v>
       </c>
-      <c r="AX8" s="7" t="n">
+      <c r="AX8" s="8" t="n">
         <f aca="false">ROUND((AU8+AV8/2+AW8/4)*10/12,0)</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AY8" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="AZ8" s="12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
@@ -3646,7 +3679,7 @@
         <f aca="false">M9+N9/2+O9/4</f>
         <v>4</v>
       </c>
-      <c r="Q9" s="7" t="n">
+      <c r="Q9" s="8" t="n">
         <f aca="false">ROUND(P9*10/$S$2,0)</f>
         <v>7</v>
       </c>
@@ -3692,7 +3725,7 @@
       <c r="AS9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="AT9" s="8" t="n">
+      <c r="AT9" s="9" t="n">
         <v>0.604166666666667</v>
       </c>
       <c r="AU9" s="3" t="n">
@@ -3707,12 +3740,12 @@
         <f aca="false">COUNTIF(T9:AO9,"T")</f>
         <v>0</v>
       </c>
-      <c r="AX9" s="7" t="n">
+      <c r="AX9" s="8" t="n">
         <f aca="false">ROUND((AU9+AV9/2+AW9/4)*10/12,0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
@@ -3731,7 +3764,7 @@
       <c r="F10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G10" s="8" t="n">
+      <c r="G10" s="9" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="H10" s="1" t="s">
@@ -3762,22 +3795,22 @@
         <f aca="false">M10+N10/2+O10/4</f>
         <v>4.5</v>
       </c>
-      <c r="Q10" s="7" t="n">
+      <c r="Q10" s="8" t="n">
         <f aca="false">ROUND(P10*10/$S$2,0)</f>
         <v>8</v>
       </c>
       <c r="T10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="U10" s="8"/>
+      <c r="U10" s="9"/>
       <c r="V10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="W10" s="8"/>
+      <c r="W10" s="9"/>
       <c r="X10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Y10" s="8" t="n">
+      <c r="Y10" s="9" t="n">
         <v>0.5625</v>
       </c>
       <c r="Z10" s="1" t="s">
@@ -3789,7 +3822,7 @@
       <c r="AD10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AE10" s="8" t="n">
+      <c r="AE10" s="9" t="n">
         <v>0.55</v>
       </c>
       <c r="AF10" s="1" t="s">
@@ -3798,13 +3831,13 @@
       <c r="AG10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AH10" s="8" t="n">
+      <c r="AH10" s="9" t="n">
         <v>0.5625</v>
       </c>
       <c r="AI10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AJ10" s="8" t="n">
+      <c r="AJ10" s="9" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="AK10" s="3" t="s">
@@ -3834,12 +3867,12 @@
         <f aca="false">COUNTIF(T10:AO10,"T")</f>
         <v>5</v>
       </c>
-      <c r="AX10" s="7" t="n">
+      <c r="AX10" s="8" t="n">
         <f aca="false">ROUND((AU10+AV10/2+AW10/4)*10/12,0)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
@@ -3886,7 +3919,7 @@
         <f aca="false">M11+N11/2+O11/4</f>
         <v>6</v>
       </c>
-      <c r="Q11" s="7" t="n">
+      <c r="Q11" s="8" t="n">
         <f aca="false">ROUND(P11*10/$S$2,0)</f>
         <v>10</v>
       </c>
@@ -3944,19 +3977,19 @@
         <f aca="false">COUNTIF(T11:AO11,"T")</f>
         <v>0</v>
       </c>
-      <c r="AX11" s="7" t="n">
+      <c r="AX11" s="8" t="n">
         <f aca="false">ROUND((AU11+AV11/2+AW11/4)*10/12,0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="13" t="s">
         <v>47</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -3996,7 +4029,7 @@
         <f aca="false">M12+N12/2+O12/4</f>
         <v>4</v>
       </c>
-      <c r="Q12" s="7" t="n">
+      <c r="Q12" s="8" t="n">
         <f aca="false">ROUND(P12*10/$S$2,0)</f>
         <v>7</v>
       </c>
@@ -4054,12 +4087,12 @@
         <f aca="false">COUNTIF(T12:AS12,"T")</f>
         <v>0</v>
       </c>
-      <c r="AX12" s="7" t="n">
+      <c r="AX12" s="8" t="n">
         <f aca="false">ROUND((AU12+AV12/2+AW12/4)*10/12,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
@@ -4090,7 +4123,7 @@
       <c r="K13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L13" s="8" t="n">
+      <c r="L13" s="9" t="n">
         <v>0.614583333333333</v>
       </c>
       <c r="M13" s="1" t="n">
@@ -4109,12 +4142,12 @@
         <f aca="false">M13+N13/2+O13/4</f>
         <v>4.25</v>
       </c>
-      <c r="Q13" s="7" t="n">
+      <c r="Q13" s="8" t="n">
         <f aca="false">ROUND(P13*10/$S$2,0)</f>
         <v>7</v>
       </c>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="9"/>
       <c r="T13" s="1" t="s">
         <v>18</v>
       </c>
@@ -4142,7 +4175,7 @@
       <c r="AI13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AJ13" s="8" t="n">
+      <c r="AJ13" s="9" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="AK13" s="3" t="s">
@@ -4172,12 +4205,12 @@
         <f aca="false">COUNTIF(T13:AO13,"T")</f>
         <v>1</v>
       </c>
-      <c r="AX13" s="7" t="n">
+      <c r="AX13" s="8" t="n">
         <f aca="false">ROUND((AU13+AV13/2+AW13/4)*10/12,0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
@@ -4196,7 +4229,7 @@
       <c r="F14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="8" t="n">
+      <c r="G14" s="9" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="H14" s="1" t="s">
@@ -4211,7 +4244,7 @@
       <c r="K14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L14" s="8" t="n">
+      <c r="L14" s="9" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="M14" s="1" t="n">
@@ -4230,19 +4263,19 @@
         <f aca="false">M14+N14/2+O14/4</f>
         <v>4</v>
       </c>
-      <c r="Q14" s="7" t="n">
+      <c r="Q14" s="8" t="n">
         <f aca="false">ROUND(P14*10/$S$2,0)</f>
         <v>7</v>
       </c>
-      <c r="R14" s="8"/>
-      <c r="S14" s="8"/>
+      <c r="R14" s="9"/>
+      <c r="S14" s="9"/>
       <c r="T14" s="1" t="s">
         <v>19</v>
       </c>
       <c r="V14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="W14" s="8" t="n">
+      <c r="W14" s="9" t="n">
         <v>0.5625</v>
       </c>
       <c r="X14" s="1" t="s">
@@ -4251,7 +4284,7 @@
       <c r="Z14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AA14" s="8" t="n">
+      <c r="AA14" s="9" t="n">
         <v>0.569444444444444</v>
       </c>
       <c r="AB14" s="1" t="s">
@@ -4266,7 +4299,7 @@
       <c r="AG14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AH14" s="8" t="n">
+      <c r="AH14" s="9" t="n">
         <v>0.548611111111111</v>
       </c>
       <c r="AI14" s="3" t="s">
@@ -4275,25 +4308,25 @@
       <c r="AK14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AL14" s="8" t="n">
+      <c r="AL14" s="9" t="n">
         <v>0.583333333333333</v>
       </c>
       <c r="AM14" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="AN14" s="8" t="n">
+      <c r="AN14" s="9" t="n">
         <v>0.576388888888889</v>
       </c>
       <c r="AO14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AP14" s="8" t="n">
+      <c r="AP14" s="9" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="AQ14" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AR14" s="9" t="n">
+      <c r="AR14" s="10" t="n">
         <v>0.597222222222222</v>
       </c>
       <c r="AS14" s="2" t="s">
@@ -4311,12 +4344,12 @@
         <f aca="false">COUNTIF(T14:AO14,"T")</f>
         <v>5</v>
       </c>
-      <c r="AX14" s="7" t="n">
+      <c r="AX14" s="8" t="n">
         <f aca="false">ROUND((AU14+AV14/2+AW14/4)*10/12,0)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
@@ -4335,7 +4368,7 @@
       <c r="F15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="H15" s="14" t="s">
         <v>18</v>
       </c>
       <c r="I15" s="1" t="s">
@@ -4363,11 +4396,11 @@
         <f aca="false">M15+N15/2+O15/4</f>
         <v>6</v>
       </c>
-      <c r="Q15" s="12" t="n">
+      <c r="Q15" s="15" t="n">
         <f aca="false">ROUND(P15*10/$S$2,0)</f>
         <v>10</v>
       </c>
-      <c r="R15" s="8" t="s">
+      <c r="R15" s="9" t="s">
         <v>58</v>
       </c>
       <c r="T15" s="1" t="s">
@@ -4376,13 +4409,13 @@
       <c r="V15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="W15" s="8" t="n">
+      <c r="W15" s="9" t="n">
         <v>0.597222222222222</v>
       </c>
       <c r="X15" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Y15" s="8" t="n">
+      <c r="Y15" s="9" t="n">
         <v>0.541666666666667</v>
       </c>
       <c r="Z15" s="1" t="s">
@@ -4430,12 +4463,12 @@
         <f aca="false">COUNTIF(T15:AO15,"T")</f>
         <v>1</v>
       </c>
-      <c r="AX15" s="7" t="n">
+      <c r="AX15" s="8" t="n">
         <f aca="false">ROUND((AU15+AV15/2+AW15/4)*10/12,0)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
@@ -4482,7 +4515,7 @@
         <f aca="false">M16+N16/2+O16/4</f>
         <v>5</v>
       </c>
-      <c r="Q16" s="7" t="n">
+      <c r="Q16" s="8" t="n">
         <f aca="false">ROUND(P16*10/$S$2,0)</f>
         <v>8</v>
       </c>
@@ -4540,19 +4573,19 @@
         <f aca="false">COUNTIF(T16:AO16,"T")</f>
         <v>0</v>
       </c>
-      <c r="AX16" s="7" t="n">
+      <c r="AX16" s="8" t="n">
         <f aca="false">ROUND((AU16+AV16/2+AW16/4)*10/12,0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="13" t="s">
         <v>63</v>
       </c>
       <c r="D17" s="3" t="s">
@@ -4592,7 +4625,7 @@
         <f aca="false">M17+N17/2+O17/4</f>
         <v>3</v>
       </c>
-      <c r="Q17" s="7" t="n">
+      <c r="Q17" s="8" t="n">
         <f aca="false">ROUND(P17*10/$S$2,0)</f>
         <v>5</v>
       </c>
@@ -4632,7 +4665,7 @@
       <c r="AO17" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AP17" s="8" t="n">
+      <c r="AP17" s="9" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="AQ17" s="2" t="s">
@@ -4653,7 +4686,7 @@
         <f aca="false">COUNTIF(T17:AS17,"T")</f>
         <v>1</v>
       </c>
-      <c r="AX17" s="7" t="n">
+      <c r="AX17" s="8" t="n">
         <f aca="false">ROUND((AU17+AV17/2+AW17/4)*10/12,0)</f>
         <v>8</v>
       </c>
@@ -4665,7 +4698,7 @@
       <c r="B18" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="11" t="s">
         <v>66</v>
       </c>
       <c r="D18" s="3" t="s">
@@ -4705,7 +4738,7 @@
         <f aca="false">M18+N18/2+O18/4</f>
         <v>5</v>
       </c>
-      <c r="Q18" s="7" t="n">
+      <c r="Q18" s="8" t="n">
         <f aca="false">ROUND(P18*10/$S$2,0)</f>
         <v>8</v>
       </c>
@@ -4715,13 +4748,13 @@
       <c r="V18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W18" s="8" t="n">
+      <c r="W18" s="9" t="n">
         <v>0.548611111111111</v>
       </c>
       <c r="X18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Y18" s="8" t="n">
+      <c r="Y18" s="9" t="n">
         <v>0.541666666666667</v>
       </c>
       <c r="Z18" s="1" t="s">
@@ -4733,7 +4766,7 @@
       <c r="AD18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AE18" s="8" t="n">
+      <c r="AE18" s="9" t="n">
         <v>0.569444444444444</v>
       </c>
       <c r="AF18" s="1" t="s">
@@ -4754,7 +4787,7 @@
       <c r="AO18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AP18" s="8" t="n">
+      <c r="AP18" s="9" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="AQ18" s="2" t="s">
@@ -4763,7 +4796,7 @@
       <c r="AS18" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AT18" s="8" t="n">
+      <c r="AT18" s="9" t="n">
         <v>0.576388888888889</v>
       </c>
       <c r="AU18" s="3" t="n">
@@ -4778,12 +4811,18 @@
         <f aca="false">COUNTIF(T18:AS18,"T")</f>
         <v>3</v>
       </c>
-      <c r="AX18" s="7" t="n">
+      <c r="AX18" s="8" t="n">
         <f aca="false">ROUND((AU18+AV18/2+AW18/4)*10/12,0)</f>
         <v>7</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AY18" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="AZ18" s="12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
@@ -4830,14 +4869,14 @@
         <f aca="false">M19+N19/2+O19/4</f>
         <v>3</v>
       </c>
-      <c r="Q19" s="7" t="n">
+      <c r="Q19" s="8" t="n">
         <f aca="false">ROUND(P19*10/$S$2,0)</f>
         <v>5</v>
       </c>
       <c r="T19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U19" s="8" t="n">
+      <c r="U19" s="9" t="n">
         <v>0.611111111111111</v>
       </c>
       <c r="V19" s="1" t="s">
@@ -4849,7 +4888,7 @@
       <c r="Z19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AA19" s="8" t="n">
+      <c r="AA19" s="9" t="n">
         <v>0.569444444444444</v>
       </c>
       <c r="AB19" s="1" t="s">
@@ -4876,7 +4915,7 @@
       <c r="AO19" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AP19" s="8" t="n">
+      <c r="AP19" s="9" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="AQ19" s="2" t="s">
@@ -4897,12 +4936,12 @@
         <f aca="false">COUNTIF(T19:AO19,"T")</f>
         <v>3</v>
       </c>
-      <c r="AX19" s="7" t="n">
+      <c r="AX19" s="8" t="n">
         <f aca="false">ROUND((AU19+AV19/2+AW19/4)*10/12,0)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
@@ -4933,7 +4972,7 @@
       <c r="K20" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L20" s="8" t="n">
+      <c r="L20" s="9" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="M20" s="1" t="n">
@@ -4952,19 +4991,19 @@
         <f aca="false">M20+N20/2+O20/4</f>
         <v>3.5</v>
       </c>
-      <c r="Q20" s="7" t="n">
+      <c r="Q20" s="8" t="n">
         <f aca="false">ROUND(P20*10/$S$2,0)</f>
         <v>6</v>
       </c>
-      <c r="R20" s="8"/>
-      <c r="S20" s="8"/>
+      <c r="R20" s="9"/>
+      <c r="S20" s="9"/>
       <c r="T20" s="1" t="s">
         <v>18</v>
       </c>
       <c r="V20" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="W20" s="8" t="n">
+      <c r="W20" s="9" t="n">
         <v>0.5625</v>
       </c>
       <c r="X20" s="1" t="s">
@@ -4985,7 +5024,7 @@
       <c r="AG20" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AH20" s="8" t="n">
+      <c r="AH20" s="9" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="AI20" s="3" t="s">
@@ -5018,12 +5057,12 @@
         <f aca="false">COUNTIF(T20:AO20,"T")</f>
         <v>2</v>
       </c>
-      <c r="AX20" s="7" t="n">
+      <c r="AX20" s="8" t="n">
         <f aca="false">ROUND((AU20+AV20/2+AW20/4)*10/12,0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
@@ -5070,7 +5109,7 @@
         <f aca="false">M21+N21/2+O21/4</f>
         <v>6</v>
       </c>
-      <c r="Q21" s="7" t="n">
+      <c r="Q21" s="8" t="n">
         <f aca="false">ROUND(P21*10/$S$2,0)</f>
         <v>10</v>
       </c>
@@ -5080,7 +5119,7 @@
       <c r="V21" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="W21" s="8"/>
+      <c r="W21" s="9"/>
       <c r="X21" s="1" t="s">
         <v>18</v>
       </c>
@@ -5129,7 +5168,7 @@
         <f aca="false">COUNTIF(T21:AO21,"T")</f>
         <v>0</v>
       </c>
-      <c r="AX21" s="7" t="n">
+      <c r="AX21" s="8" t="n">
         <f aca="false">ROUND((AU21+AV21/2+AW21/4)*10/12,0)</f>
         <v>10</v>
       </c>
@@ -5141,7 +5180,7 @@
       <c r="B22" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="11" t="s">
         <v>78</v>
       </c>
       <c r="D22" s="3" t="s">
@@ -5165,7 +5204,7 @@
       <c r="K22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L22" s="8" t="n">
+      <c r="L22" s="9" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="M22" s="1" t="n">
@@ -5184,25 +5223,25 @@
         <f aca="false">M22+N22/2+O22/4</f>
         <v>3.5</v>
       </c>
-      <c r="Q22" s="7" t="n">
+      <c r="Q22" s="8" t="n">
         <f aca="false">ROUND(P22*10/$S$2,0)</f>
         <v>6</v>
       </c>
-      <c r="R22" s="8"/>
-      <c r="S22" s="8"/>
+      <c r="R22" s="9"/>
+      <c r="S22" s="9"/>
       <c r="T22" s="1" t="s">
         <v>18</v>
       </c>
       <c r="V22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="W22" s="8" t="n">
+      <c r="W22" s="9" t="n">
         <v>0.5625</v>
       </c>
       <c r="X22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Y22" s="8" t="n">
+      <c r="Y22" s="9" t="n">
         <v>0.5625</v>
       </c>
       <c r="Z22" s="1" t="s">
@@ -5226,7 +5265,7 @@
       <c r="AK22" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AL22" s="8" t="n">
+      <c r="AL22" s="9" t="n">
         <v>0.583333333333333</v>
       </c>
       <c r="AM22" s="3" t="s">
@@ -5253,12 +5292,18 @@
         <f aca="false">COUNTIF(T22:AO22,"T")</f>
         <v>4</v>
       </c>
-      <c r="AX22" s="7" t="n">
+      <c r="AX22" s="8" t="n">
         <f aca="false">ROUND((AU22+AV22/2+AW22/4)*10/12,0)</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AY22" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="AZ22" s="12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
@@ -5280,7 +5325,7 @@
       <c r="H23" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I23" s="11" t="s">
+      <c r="I23" s="14" t="s">
         <v>18</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -5305,7 +5350,7 @@
         <f aca="false">M23+N23/2+O23/4</f>
         <v>5</v>
       </c>
-      <c r="Q23" s="12" t="n">
+      <c r="Q23" s="15" t="n">
         <f aca="false">ROUND(P23*10/$S$2,0)</f>
         <v>8</v>
       </c>
@@ -5354,7 +5399,7 @@
       <c r="AS23" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AT23" s="8" t="n">
+      <c r="AT23" s="9" t="n">
         <v>0.552083333333333</v>
       </c>
       <c r="AU23" s="3" t="n">
@@ -5369,12 +5414,12 @@
         <f aca="false">COUNTIF(T23:AO23,"T")</f>
         <v>0</v>
       </c>
-      <c r="AX23" s="7" t="n">
+      <c r="AX23" s="8" t="n">
         <f aca="false">ROUND((AU23+AV23/2+AW23/4)*10/12,0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
@@ -5421,7 +5466,7 @@
         <f aca="false">M24+N24/2+O24/4</f>
         <v>5</v>
       </c>
-      <c r="Q24" s="7" t="n">
+      <c r="Q24" s="8" t="n">
         <f aca="false">ROUND(P24*10/$S$2,0)</f>
         <v>8</v>
       </c>
@@ -5479,12 +5524,12 @@
         <f aca="false">COUNTIF(T24:AO24,"T")</f>
         <v>0</v>
       </c>
-      <c r="AX24" s="7" t="n">
+      <c r="AX24" s="8" t="n">
         <f aca="false">ROUND((AU24+AV24/2+AW24/4)*10/12,0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
@@ -5531,7 +5576,7 @@
         <f aca="false">M25+N25/2+O25/4</f>
         <v>6</v>
       </c>
-      <c r="Q25" s="7" t="n">
+      <c r="Q25" s="8" t="n">
         <f aca="false">ROUND(P25*10/$S$2,0)</f>
         <v>10</v>
       </c>
@@ -5589,19 +5634,19 @@
         <f aca="false">COUNTIF(T25:AO25,"T")</f>
         <v>0</v>
       </c>
-      <c r="AX25" s="7" t="n">
+      <c r="AX25" s="8" t="n">
         <f aca="false">ROUND((AU25+AV25/2+AW25/4)*10/12,0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="26" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" s="2" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="13" t="s">
         <v>91</v>
       </c>
       <c r="D26" s="6" t="s">
@@ -5641,7 +5686,7 @@
         <f aca="false">M26+N26/2+O26/4</f>
         <v>5</v>
       </c>
-      <c r="Q26" s="13" t="n">
+      <c r="Q26" s="16" t="n">
         <f aca="false">ROUND(P26*10/$S$2,0)</f>
         <v>8</v>
       </c>
@@ -5657,7 +5702,7 @@
       <c r="Z26" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AA26" s="9" t="n">
+      <c r="AA26" s="10" t="n">
         <v>0.569444444444444</v>
       </c>
       <c r="AB26" s="2" t="s">
@@ -5703,12 +5748,12 @@
         <f aca="false">COUNTIF(T26:AO26,"T")</f>
         <v>1</v>
       </c>
-      <c r="AX26" s="13" t="n">
+      <c r="AX26" s="16" t="n">
         <f aca="false">ROUND((AU26+AV26/2+AW26/4)*10/12,0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
@@ -5755,7 +5800,7 @@
         <f aca="false">M27+N27/2+O27/4</f>
         <v>6</v>
       </c>
-      <c r="Q27" s="7" t="n">
+      <c r="Q27" s="8" t="n">
         <f aca="false">ROUND(P27*10/$S$2,0)</f>
         <v>10</v>
       </c>
@@ -5777,7 +5822,7 @@
       <c r="AD27" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AE27" s="8" t="n">
+      <c r="AE27" s="9" t="n">
         <v>0.572916666666667</v>
       </c>
       <c r="AF27" s="1" t="s">
@@ -5786,7 +5831,7 @@
       <c r="AG27" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AH27" s="8" t="n">
+      <c r="AH27" s="9" t="n">
         <v>0.604166666666667</v>
       </c>
       <c r="AI27" s="3" t="s">
@@ -5819,7 +5864,7 @@
         <f aca="false">COUNTIF(T27:AO27,"T")</f>
         <v>2</v>
       </c>
-      <c r="AX27" s="7" t="n">
+      <c r="AX27" s="8" t="n">
         <f aca="false">ROUND((AU27+AV27/2+AW27/4)*10/12,0)</f>
         <v>8</v>
       </c>
@@ -5831,7 +5876,7 @@
       <c r="B28" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="11" t="s">
         <v>97</v>
       </c>
       <c r="D28" s="3" t="s">
@@ -5873,7 +5918,7 @@
         <f aca="false">M28+N28/2+O28/4</f>
         <v>3</v>
       </c>
-      <c r="Q28" s="7" t="n">
+      <c r="Q28" s="8" t="n">
         <f aca="false">ROUND(P28*10/$S$2,0)</f>
         <v>5</v>
       </c>
@@ -5886,13 +5931,13 @@
       <c r="V28" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="W28" s="8" t="n">
+      <c r="W28" s="9" t="n">
         <v>0.576388888888889</v>
       </c>
       <c r="X28" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="Y28" s="8" t="n">
+      <c r="Y28" s="9" t="n">
         <v>0.583333333333333</v>
       </c>
       <c r="Z28" s="3" t="s">
@@ -5901,13 +5946,13 @@
       <c r="AB28" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AC28" s="8" t="n">
+      <c r="AC28" s="9" t="n">
         <v>0.59375</v>
       </c>
       <c r="AD28" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AE28" s="8" t="n">
+      <c r="AE28" s="9" t="n">
         <v>0.572916666666667</v>
       </c>
       <c r="AF28" s="3" t="s">
@@ -5916,19 +5961,19 @@
       <c r="AG28" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AH28" s="8" t="n">
+      <c r="AH28" s="9" t="n">
         <v>0.583333333333333</v>
       </c>
       <c r="AI28" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AJ28" s="8" t="n">
+      <c r="AJ28" s="9" t="n">
         <v>0.597222222222222</v>
       </c>
       <c r="AK28" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AL28" s="8" t="n">
+      <c r="AL28" s="9" t="n">
         <v>0.583333333333333</v>
       </c>
       <c r="AM28" s="3" t="s">
@@ -5956,9 +6001,15 @@
         <f aca="false">COUNTIF(T28:AS28,"T")</f>
         <v>8</v>
       </c>
-      <c r="AX28" s="7" t="n">
+      <c r="AX28" s="8" t="n">
         <f aca="false">ROUND((AU28+AV28/2+AW28/4)*10/12,0)</f>
         <v>3</v>
+      </c>
+      <c r="AY28" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="AZ28" s="12" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6261,22 +6312,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>116</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6290,10 +6341,10 @@
         <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>9</v>
@@ -6327,10 +6378,10 @@
         <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>10</v>
@@ -6352,10 +6403,10 @@
         <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>6</v>
@@ -6386,10 +6437,10 @@
         <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>10</v>
@@ -6411,10 +6462,10 @@
         <v>32</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>9</v>
@@ -6425,10 +6476,10 @@
         <v>32</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>9</v>
@@ -6439,10 +6490,10 @@
         <v>32</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>7</v>
@@ -6453,10 +6504,10 @@
         <v>32</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>5</v>
@@ -6467,10 +6518,10 @@
         <v>32</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>4</v>
@@ -6501,10 +6552,10 @@
         <v>38</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -6538,10 +6589,10 @@
         <v>44</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>8</v>
@@ -6575,10 +6626,10 @@
         <v>50</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>9</v>
@@ -6598,10 +6649,10 @@
         <v>53</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>8</v>
@@ -6621,10 +6672,10 @@
         <v>56</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>8</v>
@@ -6646,10 +6697,10 @@
         <v>56</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>7</v>
@@ -6666,10 +6717,10 @@
         <v>60</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>5</v>
@@ -6703,10 +6754,10 @@
         <v>66</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>9</v>
@@ -6726,10 +6777,10 @@
         <v>69</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -6749,10 +6800,10 @@
         <v>72</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>10</v>
@@ -6772,10 +6823,10 @@
         <v>75</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>9</v>
@@ -6809,10 +6860,10 @@
         <v>81</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>8</v>
@@ -6832,10 +6883,10 @@
         <v>85</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>10</v>
@@ -6855,10 +6906,10 @@
         <v>88</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>10</v>
@@ -6878,10 +6929,10 @@
         <v>91</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>10</v>
@@ -6903,10 +6954,10 @@
         <v>91</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>10</v>
@@ -6917,10 +6968,10 @@
         <v>91</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>10</v>
@@ -6931,10 +6982,10 @@
         <v>91</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>10</v>
@@ -6945,10 +6996,10 @@
         <v>91</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>10</v>
@@ -6959,10 +7010,10 @@
         <v>91</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>10</v>
@@ -6973,10 +7024,10 @@
         <v>91</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>10</v>
@@ -6987,10 +7038,10 @@
         <v>91</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F39" s="1" t="n">
         <v>10</v>
@@ -7001,10 +7052,10 @@
         <v>91</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="F40" s="1" t="n">
         <v>10</v>
@@ -7015,10 +7066,10 @@
         <v>91</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="F41" s="1" t="n">
         <v>10</v>
@@ -7029,10 +7080,10 @@
         <v>91</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="F42" s="1" t="n">
         <v>10</v>
@@ -7043,10 +7094,10 @@
         <v>91</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="F43" s="1" t="n">
         <v>10</v>
@@ -7057,10 +7108,10 @@
         <v>91</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>9</v>
@@ -7071,10 +7122,10 @@
         <v>91</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>7</v>
@@ -7085,10 +7136,10 @@
         <v>91</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F46" s="1" t="n">
         <v>7</v>
@@ -7105,10 +7156,10 @@
         <v>94</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F47" s="1" t="n">
         <v>10</v>
@@ -7130,10 +7181,10 @@
         <v>94</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="F48" s="1" t="n">
         <v>3</v>
@@ -7155,7 +7206,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H50" s="1" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="I50" s="1" t="n">
         <f aca="false">COUNTIF(I2:I49,"&gt;0")</f>
@@ -7211,22 +7262,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>116</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7240,10 +7291,10 @@
         <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>7</v>
@@ -7277,10 +7328,10 @@
         <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>9</v>
@@ -7314,10 +7365,10 @@
         <v>32</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>10</v>
@@ -7339,10 +7390,10 @@
         <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>9</v>
@@ -7353,10 +7404,10 @@
         <v>32</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>2</v>
@@ -7387,10 +7438,10 @@
         <v>38</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>10</v>
@@ -7424,10 +7475,10 @@
         <v>44</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>10</v>
@@ -7461,10 +7512,10 @@
         <v>50</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -7484,10 +7535,10 @@
         <v>53</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -7509,10 +7560,10 @@
         <v>53</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>5</v>
@@ -7529,10 +7580,10 @@
         <v>56</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>8</v>
@@ -7554,10 +7605,10 @@
         <v>56</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>7</v>
@@ -7568,10 +7619,10 @@
         <v>56</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>4</v>
@@ -7582,10 +7633,10 @@
         <v>56</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>4</v>
@@ -7602,10 +7653,10 @@
         <v>60</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>7</v>
@@ -7639,10 +7690,10 @@
         <v>66</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>10</v>
@@ -7662,10 +7713,10 @@
         <v>69</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>8</v>
@@ -7685,10 +7736,10 @@
         <v>72</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -7708,10 +7759,10 @@
         <v>75</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>10</v>
@@ -7745,10 +7796,10 @@
         <v>81</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>8</v>
@@ -7768,10 +7819,10 @@
         <v>85</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>10</v>
@@ -7791,10 +7842,10 @@
         <v>88</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>10</v>
@@ -7814,10 +7865,10 @@
         <v>91</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>10</v>
@@ -7839,10 +7890,10 @@
         <v>91</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>9</v>
@@ -7859,10 +7910,10 @@
         <v>94</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>10</v>
@@ -7884,10 +7935,10 @@
         <v>94</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>3</v>
@@ -7909,7 +7960,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H36" s="1" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="I36" s="1" t="n">
         <f aca="false">COUNTIF(I2:I35,"&gt;0")</f>
@@ -7965,19 +8016,19 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>116</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7994,7 +8045,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>7</v>
@@ -8031,7 +8082,7 @@
         <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>9</v>
@@ -8068,7 +8119,7 @@
         <v>31</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>10</v>
@@ -8091,7 +8142,7 @@
         <v>34</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>9</v>
@@ -8114,7 +8165,7 @@
         <v>37</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>10</v>
@@ -8179,7 +8230,7 @@
         <v>49</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>8</v>
@@ -8216,7 +8267,7 @@
         <v>55</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -8267,7 +8318,7 @@
         <v>65</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>9</v>
@@ -8290,7 +8341,7 @@
         <v>68</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>10</v>
@@ -8313,7 +8364,7 @@
         <v>71</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>10</v>
@@ -8336,7 +8387,7 @@
         <v>74</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>9</v>
@@ -8373,7 +8424,7 @@
         <v>80</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>9</v>
@@ -8396,7 +8447,7 @@
         <v>84</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>10</v>
@@ -8421,7 +8472,7 @@
         <v>84</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>9</v>
@@ -8441,7 +8492,7 @@
         <v>87</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>9</v>
@@ -8466,7 +8517,7 @@
         <v>87</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>9</v>
@@ -8480,7 +8531,7 @@
         <v>87</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>8</v>
@@ -8494,7 +8545,7 @@
         <v>87</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>6</v>
@@ -8508,7 +8559,7 @@
         <v>87</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>6</v>
@@ -8522,7 +8573,7 @@
         <v>87</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>4</v>
@@ -8542,7 +8593,7 @@
         <v>90</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>10</v>
@@ -8567,7 +8618,7 @@
         <v>90</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>10</v>
@@ -8581,7 +8632,7 @@
         <v>90</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>10</v>
@@ -8595,7 +8646,7 @@
         <v>90</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>10</v>
@@ -8609,7 +8660,7 @@
         <v>90</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>9</v>
@@ -8623,7 +8674,7 @@
         <v>90</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>9</v>
@@ -8637,7 +8688,7 @@
         <v>90</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>9</v>
@@ -8651,7 +8702,7 @@
         <v>90</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>9</v>
@@ -8725,19 +8776,19 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>116</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8754,7 +8805,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>10</v>
@@ -8791,7 +8842,7 @@
         <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>10</v>
@@ -8828,7 +8879,7 @@
         <v>31</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>3</v>
@@ -8853,7 +8904,7 @@
         <v>31</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>9</v>
@@ -8867,7 +8918,7 @@
         <v>31</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>10</v>
@@ -8957,7 +9008,7 @@
         <v>49</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -8994,7 +9045,7 @@
         <v>55</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>10</v>
@@ -9045,7 +9096,7 @@
         <v>65</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>6</v>
@@ -9082,7 +9133,7 @@
         <v>71</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>9</v>
@@ -9105,7 +9156,7 @@
         <v>74</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>9</v>
@@ -9142,7 +9193,7 @@
         <v>80</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>8</v>
@@ -9165,7 +9216,7 @@
         <v>84</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -9188,7 +9239,7 @@
         <v>87</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>10</v>
@@ -9213,7 +9264,7 @@
         <v>87</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>10</v>
@@ -9227,7 +9278,7 @@
         <v>87</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>9</v>
@@ -9241,7 +9292,7 @@
         <v>87</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>9</v>
@@ -9261,7 +9312,7 @@
         <v>90</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>9</v>
@@ -9286,7 +9337,7 @@
         <v>90</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>9</v>
@@ -9300,7 +9351,7 @@
         <v>90</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>10</v>
@@ -9314,7 +9365,7 @@
         <v>90</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>10</v>
@@ -9392,19 +9443,19 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>116</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9421,7 +9472,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>9</v>
@@ -9458,7 +9509,7 @@
         <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>8</v>
@@ -9495,7 +9546,7 @@
         <v>31</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>8</v>
@@ -9520,7 +9571,7 @@
         <v>31</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>8</v>
@@ -9534,7 +9585,7 @@
         <v>31</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>7</v>
@@ -9548,7 +9599,7 @@
         <v>31</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>2</v>
@@ -9638,7 +9689,7 @@
         <v>49</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>9</v>
@@ -9675,7 +9726,7 @@
         <v>55</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>9</v>
@@ -9726,7 +9777,7 @@
         <v>65</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>7</v>
@@ -9763,7 +9814,7 @@
         <v>71</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>7</v>
@@ -9786,7 +9837,7 @@
         <v>74</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>8</v>
@@ -9823,7 +9874,7 @@
         <v>80</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>8</v>
@@ -9846,7 +9897,7 @@
         <v>84</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>9</v>
@@ -9869,7 +9920,7 @@
         <v>87</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>9</v>
@@ -9894,7 +9945,7 @@
         <v>87</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>9</v>
@@ -9908,7 +9959,7 @@
         <v>87</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>9</v>
@@ -9928,7 +9979,7 @@
         <v>90</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>10</v>
@@ -9953,7 +10004,7 @@
         <v>90</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>10</v>
@@ -9967,7 +10018,7 @@
         <v>90</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>10</v>
@@ -9981,7 +10032,7 @@
         <v>90</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>9</v>
@@ -9995,7 +10046,7 @@
         <v>90</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>9</v>
@@ -10009,7 +10060,7 @@
         <v>90</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>8</v>
@@ -10023,7 +10074,7 @@
         <v>90</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>6</v>
@@ -10037,7 +10088,7 @@
         <v>90</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>6</v>
@@ -10129,6 +10180,7 @@
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="49" min="49" style="1" width="9.64"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="50" min="50" style="1" width="23.39"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="54" min="51" style="1" width="9.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="58" min="58" style="0" width="13.37"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10336,12 +10388,15 @@
       <c r="BD2" s="3" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="BE2" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="1" t="n">
@@ -10353,7 +10408,7 @@
       <c r="G3" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="I3" s="15" t="n">
+      <c r="I3" s="18" t="n">
         <v>7</v>
       </c>
       <c r="J3" s="4" t="n">
@@ -10378,26 +10433,26 @@
         <f aca="false">Q3+S3/2</f>
         <v>7</v>
       </c>
-      <c r="U3" s="7" t="n">
+      <c r="U3" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(M3,O3,T3,C3),0)</f>
         <v>8</v>
       </c>
-      <c r="V3" s="7" t="str">
+      <c r="V3" s="8" t="str">
         <f aca="false">IF(U3&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W3" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z3" s="7"/>
-      <c r="AA3" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB3" s="7"/>
+      <c r="W3" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X3" s="8"/>
+      <c r="Y3" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z3" s="8"/>
+      <c r="AA3" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB3" s="8"/>
       <c r="AC3" s="1" t="n">
         <v>8</v>
       </c>
@@ -10405,7 +10460,7 @@
         <f aca="false">AC3+AD3/2</f>
         <v>8</v>
       </c>
-      <c r="AF3" s="7" t="n">
+      <c r="AF3" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AE3,AA3,Y3,W3,U3),0)</f>
         <v>8</v>
       </c>
@@ -10418,8 +10473,8 @@
       <c r="AK3" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AL3" s="14" t="s">
-        <v>135</v>
+      <c r="AL3" s="17" t="s">
+        <v>136</v>
       </c>
       <c r="AM3" s="1" t="n">
         <v>9</v>
@@ -10428,13 +10483,13 @@
         <v>7</v>
       </c>
       <c r="AP3" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AQ3" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AR3" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AS3" s="1" t="n">
         <v>7</v>
@@ -10452,7 +10507,7 @@
         <v>7</v>
       </c>
       <c r="AX3" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AY3" s="1" t="n">
         <v>5</v>
@@ -10461,11 +10516,11 @@
         <f aca="false">AY3+AZ3/2</f>
         <v>5</v>
       </c>
-      <c r="BC3" s="7" t="n">
+      <c r="BC3" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AJ3,AK3,AM3,AO3,AQ3,AS3,AU3,AW3,BA3),0)</f>
         <v>7</v>
       </c>
-      <c r="BD3" s="7" t="n">
+      <c r="BD3" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AF3,BC3),0)</f>
         <v>8</v>
       </c>
@@ -10474,16 +10529,16 @@
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="F4" s="20" t="n">
         <v>45846</v>
       </c>
       <c r="G4" s="1" t="n">
@@ -10511,26 +10566,26 @@
         <f aca="false">Q4+S4/2</f>
         <v>1.5</v>
       </c>
-      <c r="U4" s="7" t="n">
+      <c r="U4" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(M4,O4,T4),0)</f>
         <v>1</v>
       </c>
-      <c r="V4" s="7" t="str">
+      <c r="V4" s="8" t="str">
         <f aca="false">IF(U4&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="W4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="X4" s="7"/>
-      <c r="Y4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="7"/>
-      <c r="AA4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="7"/>
+      <c r="W4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" s="8"/>
+      <c r="Y4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="8"/>
+      <c r="AA4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="8"/>
       <c r="AC4" s="1" t="n">
         <v>7</v>
       </c>
@@ -10538,7 +10593,7 @@
         <f aca="false">AC4+AD4/2</f>
         <v>7</v>
       </c>
-      <c r="AF4" s="7" t="n">
+      <c r="AF4" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AE4,AA4,Y4,W4,U4),0)</f>
         <v>2</v>
       </c>
@@ -10555,24 +10610,24 @@
         <v>7</v>
       </c>
       <c r="AL4" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AM4" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AN4" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="AO4" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ4" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS4" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU4" s="18" t="n">
+        <v>141</v>
+      </c>
+      <c r="AO4" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" s="21" t="n">
         <v>1</v>
       </c>
       <c r="AW4" s="1" t="n">
@@ -10589,20 +10644,20 @@
       <c r="BB4" s="6" t="n">
         <v>9.25</v>
       </c>
-      <c r="BC4" s="7" t="n">
+      <c r="BC4" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AJ4,AK4,AM4,AO4,AQ4,AS4,AU4,AW4,BA4,BB4),0)</f>
         <v>4</v>
       </c>
-      <c r="BD4" s="7" t="n">
+      <c r="BD4" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AF4,BC4),0)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="17" t="s">
         <v>26</v>
       </c>
       <c r="C5" s="1" t="n">
@@ -10636,35 +10691,35 @@
         <f aca="false">Q5+S5/2</f>
         <v>9.5</v>
       </c>
-      <c r="U5" s="7" t="n">
+      <c r="U5" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(M5,O5,T5),0)</f>
         <v>9</v>
       </c>
-      <c r="V5" s="7" t="str">
+      <c r="V5" s="8" t="str">
         <f aca="false">IF(U5&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W5" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z5" s="7"/>
-      <c r="AA5" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB5" s="7"/>
-      <c r="AC5" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD5" s="7"/>
+      <c r="W5" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="X5" s="8"/>
+      <c r="Y5" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z5" s="8"/>
+      <c r="AA5" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB5" s="8"/>
+      <c r="AC5" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD5" s="8"/>
       <c r="AE5" s="1" t="n">
         <f aca="false">AC5+AD5/2</f>
         <v>8</v>
       </c>
-      <c r="AF5" s="7" t="n">
+      <c r="AF5" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AE5,AA5,Y5,W5,U5),0)</f>
         <v>9</v>
       </c>
@@ -10678,13 +10733,13 @@
         <v>10</v>
       </c>
       <c r="AL5" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AM5" s="1" t="n">
         <v>10</v>
       </c>
       <c r="AN5" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AO5" s="1" t="n">
         <v>10</v>
@@ -10693,22 +10748,22 @@
         <v>6</v>
       </c>
       <c r="AR5" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AS5" s="1" t="n">
         <v>6</v>
       </c>
       <c r="AT5" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="AU5" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW5" s="18" t="n">
+        <v>145</v>
+      </c>
+      <c r="AU5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW5" s="21" t="n">
         <v>3</v>
       </c>
       <c r="AX5" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AY5" s="1" t="n">
         <v>8</v>
@@ -10720,106 +10775,106 @@
       <c r="BB5" s="1" t="n">
         <v>9.5</v>
       </c>
-      <c r="BC5" s="7" t="n">
+      <c r="BC5" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AJ5,AK5,AM5,AO5,AQ5,AS5,AU5,AW5,BA5),0)</f>
         <v>7</v>
       </c>
-      <c r="BD5" s="7" t="n">
+      <c r="BD5" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AF5,BC5),0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="17" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="20" t="n">
         <v>45940</v>
       </c>
-      <c r="G6" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="H6" s="17" t="n">
+      <c r="G6" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="H6" s="20" t="n">
         <v>45848</v>
       </c>
-      <c r="I6" s="11" t="n">
+      <c r="I6" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="J6" s="17" t="n">
+      <c r="J6" s="20" t="n">
         <v>45848</v>
       </c>
-      <c r="K6" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L6" s="17" t="n">
+      <c r="K6" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" s="20" t="n">
         <v>45848</v>
       </c>
       <c r="M6" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="O6" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="P6" s="17" t="n">
+      <c r="O6" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="P6" s="20" t="n">
         <v>45848</v>
       </c>
-      <c r="Q6" s="11" t="n">
+      <c r="Q6" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="R6" s="17" t="n">
+      <c r="R6" s="20" t="n">
         <v>45848</v>
       </c>
-      <c r="S6" s="20" t="n">
+      <c r="S6" s="23" t="n">
         <v>15</v>
       </c>
       <c r="T6" s="1" t="n">
         <f aca="false">Q6+S6/2</f>
         <v>13.5</v>
       </c>
-      <c r="U6" s="7" t="n">
+      <c r="U6" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(M6,O6,T6),0)</f>
         <v>8</v>
       </c>
-      <c r="V6" s="7" t="str">
+      <c r="V6" s="8" t="str">
         <f aca="false">IF(U6&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W6" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="X6" s="17" t="n">
+      <c r="W6" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="X6" s="20" t="n">
         <v>45848</v>
       </c>
-      <c r="Y6" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z6" s="17" t="n">
+      <c r="Y6" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z6" s="20" t="n">
         <v>45848</v>
       </c>
-      <c r="AA6" s="21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB6" s="22" t="n">
+      <c r="AA6" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB6" s="25" t="n">
         <v>45848</v>
       </c>
-      <c r="AC6" s="7" t="n">
+      <c r="AC6" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="AD6" s="7"/>
+      <c r="AD6" s="8"/>
       <c r="AE6" s="1" t="n">
         <f aca="false">AC6+AD6/2</f>
         <v>3</v>
       </c>
-      <c r="AF6" s="7" t="n">
+      <c r="AF6" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AE6,AA6,Y6,W6,U6),0)</f>
         <v>7</v>
       </c>
@@ -10833,43 +10888,43 @@
         <v>7</v>
       </c>
       <c r="AL6" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AM6" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AN6" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="AO6" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP6" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="AO6" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AP6" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="AQ6" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AR6" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AS6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="AT6" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AU6" s="1" t="n">
         <v>6</v>
       </c>
       <c r="AV6" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AW6" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AX6" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AY6" s="3" t="n">
         <v>4</v>
@@ -10880,11 +10935,11 @@
         <v>4</v>
       </c>
       <c r="BB6" s="3"/>
-      <c r="BC6" s="7" t="n">
+      <c r="BC6" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AJ6,AK6,AM6,AO6,AQ6,AS6,AU6,AW6,BA6),0)</f>
         <v>7</v>
       </c>
-      <c r="BD6" s="7" t="n">
+      <c r="BD6" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AF6,BC6),0)</f>
         <v>7</v>
       </c>
@@ -10893,7 +10948,7 @@
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="19" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="1" t="n">
@@ -10927,35 +10982,35 @@
         <f aca="false">Q7+S7/2</f>
         <v>9</v>
       </c>
-      <c r="U7" s="7" t="n">
+      <c r="U7" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(M7,O7,T7),0)</f>
         <v>10</v>
       </c>
-      <c r="V7" s="7" t="str">
+      <c r="V7" s="8" t="str">
         <f aca="false">IF(U7&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W7" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="X7" s="7"/>
-      <c r="Y7" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z7" s="7"/>
-      <c r="AA7" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB7" s="7"/>
-      <c r="AC7" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD7" s="7"/>
+      <c r="W7" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="X7" s="8"/>
+      <c r="Y7" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z7" s="8"/>
+      <c r="AA7" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB7" s="8"/>
+      <c r="AC7" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD7" s="8"/>
       <c r="AE7" s="1" t="n">
         <f aca="false">AC7+AD7/2</f>
         <v>8</v>
       </c>
-      <c r="AF7" s="7" t="n">
+      <c r="AF7" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AE7,AA7,Y7,W7,U7),0)</f>
         <v>9</v>
       </c>
@@ -10965,8 +11020,11 @@
       <c r="AJ7" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AK7" s="18" t="n">
-        <v>1</v>
+      <c r="AK7" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL7" s="27" t="s">
+        <v>152</v>
       </c>
       <c r="AM7" s="1" t="n">
         <v>1</v>
@@ -10997,151 +11055,153 @@
       <c r="BB7" s="3" t="n">
         <v>9.5</v>
       </c>
-      <c r="BC7" s="7" t="n">
+      <c r="BC7" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AJ7,AK7,AM7,AO7,AQ7,AS7,AU7,AW7,BA7,BB7),0)</f>
-        <v>3</v>
-      </c>
-      <c r="BD7" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(AF7,BC7),0)</f>
+        <v>4</v>
+      </c>
+      <c r="BD7" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF7" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" s="23" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" s="23" t="n">
+      <c r="C8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="T8" s="23" t="n">
+      <c r="T8" s="1" t="n">
         <f aca="false">Q8+S8/2</f>
         <v>1</v>
       </c>
-      <c r="U8" s="24" t="n">
+      <c r="U8" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(C8,E8,G8,I8,K8,M8,O8,T8),0)</f>
         <v>1</v>
       </c>
-      <c r="V8" s="24" t="str">
+      <c r="V8" s="8" t="str">
         <f aca="false">IF(U8&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="W8" s="24" t="n">
-        <v>9</v>
-      </c>
-      <c r="X8" s="24"/>
-      <c r="Y8" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="24"/>
-      <c r="AA8" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB8" s="24"/>
-      <c r="AC8" s="24" t="n">
+      <c r="W8" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="X8" s="8"/>
+      <c r="Y8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="8"/>
+      <c r="AA8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="8"/>
+      <c r="AC8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AD8" s="24"/>
-      <c r="AE8" s="23" t="n">
+      <c r="AD8" s="8"/>
+      <c r="AE8" s="1" t="n">
         <f aca="false">AC8+AD8/2</f>
         <v>0</v>
       </c>
-      <c r="AF8" s="24" t="n">
+      <c r="AF8" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AE8,AA8,Y8,W8,U8),0)</f>
         <v>2</v>
       </c>
-      <c r="AH8" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="AI8" s="23" t="s">
+      <c r="AH8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AI8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AJ8" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK8" s="23" t="n">
+      <c r="AJ8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AL8" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="AM8" s="23" t="n">
+      <c r="AL8" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="AM8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AN8" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="AO8" s="23" t="n">
+      <c r="AN8" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="AO8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AP8" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="AQ8" s="23" t="n">
+      <c r="AP8" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="AQ8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AS8" s="23" t="n">
+      <c r="AS8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AT8" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="AU8" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW8" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY8" s="23" t="n">
+      <c r="AT8" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="AU8" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY8" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="BA8" s="23" t="n">
+      <c r="BA8" s="1" t="n">
         <f aca="false">AY8+AZ8/2</f>
         <v>3</v>
       </c>
-      <c r="BB8" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC8" s="24" t="n">
+      <c r="BB8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC8" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AJ8,AK8,AM8,AO8,AQ8,AS8,AU8,AW8,BA8,BB8),0)</f>
         <v>4</v>
       </c>
-      <c r="BD8" s="24" t="n">
+      <c r="BD8" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AF8,BC8),0)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="17" t="s">
         <v>38</v>
       </c>
       <c r="C9" s="1" t="n">
@@ -11153,7 +11213,7 @@
       <c r="G9" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="I9" s="15" t="n">
+      <c r="I9" s="18" t="n">
         <v>7</v>
       </c>
       <c r="J9" s="4" t="n">
@@ -11178,39 +11238,39 @@
         <f aca="false">Q9+S9/2</f>
         <v>10</v>
       </c>
-      <c r="U9" s="7" t="n">
+      <c r="U9" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(M9,O9,T9),0)</f>
         <v>9</v>
       </c>
-      <c r="V9" s="7" t="str">
+      <c r="V9" s="8" t="str">
         <f aca="false">IF(U9&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W9" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z9" s="17" t="n">
+      <c r="W9" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="X9" s="8"/>
+      <c r="Y9" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z9" s="20" t="n">
         <v>45849</v>
       </c>
-      <c r="AA9" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB9" s="17" t="n">
+      <c r="AA9" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB9" s="20" t="n">
         <v>45849</v>
       </c>
-      <c r="AC9" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD9" s="7"/>
+      <c r="AC9" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD9" s="8"/>
       <c r="AE9" s="1" t="n">
         <f aca="false">AC9+AD9/2</f>
         <v>7</v>
       </c>
-      <c r="AF9" s="7" t="n">
+      <c r="AF9" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AE9,AA9,Y9,W9,U9),0)</f>
         <v>8</v>
       </c>
@@ -11224,43 +11284,43 @@
         <v>7</v>
       </c>
       <c r="AL9" s="6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AM9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AN9" s="6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AO9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AP9" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AQ9" s="1" t="n">
         <v>6</v>
       </c>
       <c r="AR9" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AS9" s="1" t="n">
         <v>5</v>
       </c>
       <c r="AT9" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AU9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AV9" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="AW9" s="18" t="n">
+        <v>156</v>
+      </c>
+      <c r="AW9" s="21" t="n">
         <v>5</v>
       </c>
       <c r="AX9" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AY9" s="2" t="n">
         <v>9</v>
@@ -11271,62 +11331,62 @@
         <v>9</v>
       </c>
       <c r="BB9" s="2"/>
-      <c r="BC9" s="7" t="n">
+      <c r="BC9" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AJ9,AK9,AM9,AO9,AQ9,AS9,AU9,AW9,BA9),0)</f>
         <v>7</v>
       </c>
-      <c r="BD9" s="7" t="n">
+      <c r="BD9" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AF9,BC9),0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="17" t="s">
         <v>41</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="E10" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="F10" s="17" t="n">
+      <c r="E10" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" s="20" t="n">
         <v>45846</v>
       </c>
-      <c r="G10" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H10" s="17" t="n">
+      <c r="G10" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="H10" s="20" t="n">
         <v>45846</v>
       </c>
-      <c r="I10" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="J10" s="17" t="n">
+      <c r="I10" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" s="20" t="n">
         <v>45846</v>
       </c>
-      <c r="K10" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="L10" s="17" t="n">
+      <c r="K10" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="L10" s="20" t="n">
         <v>45848</v>
       </c>
       <c r="M10" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="O10" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="P10" s="17" t="n">
+      <c r="O10" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="P10" s="20" t="n">
         <v>45848</v>
       </c>
-      <c r="Q10" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="R10" s="17" t="n">
+      <c r="Q10" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="R10" s="20" t="n">
         <v>45848</v>
       </c>
       <c r="S10" s="1" t="n">
@@ -11336,41 +11396,41 @@
         <f aca="false">Q10+S10/2</f>
         <v>8</v>
       </c>
-      <c r="U10" s="7" t="n">
+      <c r="U10" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(M10,O10,T10),0)</f>
         <v>6</v>
       </c>
-      <c r="V10" s="7" t="str">
+      <c r="V10" s="8" t="str">
         <f aca="false">IF(U10&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="W10" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="X10" s="17" t="n">
+      <c r="W10" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="X10" s="20" t="n">
         <v>45848</v>
       </c>
-      <c r="Y10" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z10" s="17" t="n">
+      <c r="Y10" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z10" s="20" t="n">
         <v>45848</v>
       </c>
-      <c r="AA10" s="20" t="n">
+      <c r="AA10" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="AB10" s="17" t="n">
+      <c r="AB10" s="20" t="n">
         <v>45848</v>
       </c>
-      <c r="AC10" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD10" s="7"/>
+      <c r="AC10" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD10" s="8"/>
       <c r="AE10" s="1" t="n">
         <f aca="false">AC10+AD10/2</f>
         <v>8</v>
       </c>
-      <c r="AF10" s="7" t="n">
+      <c r="AF10" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AE10,AA10,Y10,W10,U10),0)</f>
         <v>7</v>
       </c>
@@ -11384,43 +11444,43 @@
         <v>7</v>
       </c>
       <c r="AL10" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AM10" s="1" t="n">
         <v>5</v>
       </c>
       <c r="AN10" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AO10" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AP10" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AQ10" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AR10" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AS10" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AT10" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AU10" s="1" t="n">
         <v>6</v>
       </c>
       <c r="AV10" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AW10" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AX10" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AY10" s="3" t="n">
         <v>6</v>
@@ -11431,20 +11491,20 @@
         <v>6</v>
       </c>
       <c r="BB10" s="3"/>
-      <c r="BC10" s="7" t="n">
+      <c r="BC10" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AJ10,AK10,AM10,AO10,AQ10,AS10,AU10,AW10,BA10),0)</f>
         <v>7</v>
       </c>
-      <c r="BD10" s="7" t="n">
+      <c r="BD10" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AF10,BC10),0)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="17" t="s">
         <v>44</v>
       </c>
       <c r="C11" s="1" t="n">
@@ -11478,41 +11538,41 @@
         <f aca="false">Q11+S11/2</f>
         <v>16</v>
       </c>
-      <c r="U11" s="7" t="n">
+      <c r="U11" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(M11,O11,T11),0)</f>
         <v>11</v>
       </c>
-      <c r="V11" s="7" t="str">
+      <c r="V11" s="8" t="str">
         <f aca="false">IF(U11&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W11" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="X11" s="17" t="n">
+      <c r="W11" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="X11" s="20" t="n">
         <v>45848</v>
       </c>
-      <c r="Y11" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z11" s="17" t="n">
+      <c r="Y11" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z11" s="20" t="n">
         <v>45849</v>
       </c>
-      <c r="AA11" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB11" s="17" t="n">
+      <c r="AA11" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB11" s="20" t="n">
         <v>45848</v>
       </c>
-      <c r="AC11" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD11" s="7"/>
+      <c r="AC11" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD11" s="8"/>
       <c r="AE11" s="1" t="n">
         <f aca="false">AC11+AD11/2</f>
         <v>10</v>
       </c>
-      <c r="AF11" s="7" t="n">
+      <c r="AF11" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AE11,AA11,Y11,W11,U11),0)</f>
         <v>9</v>
       </c>
@@ -11529,7 +11589,7 @@
         <v>10</v>
       </c>
       <c r="AN11" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AO11" s="1" t="n">
         <v>10</v>
@@ -11558,195 +11618,193 @@
         <v>9</v>
       </c>
       <c r="BB11" s="3"/>
-      <c r="BC11" s="7" t="n">
+      <c r="BC11" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AJ11,AK11,AM11,AO11,AQ11,AS11,AU11,AW11,BA11),0)</f>
         <v>10</v>
       </c>
-      <c r="BD11" s="7" t="n">
+      <c r="BD11" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AF11,BC11),0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="12" s="29" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" s="14" t="s">
+    <row r="12" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="F12" s="26" t="n">
+      <c r="C12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="F12" s="4" t="n">
         <v>45783</v>
       </c>
-      <c r="G12" s="23" t="n">
+      <c r="G12" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="H12" s="26" t="n">
+      <c r="H12" s="4" t="n">
         <v>45783</v>
       </c>
-      <c r="I12" s="23" t="n">
+      <c r="I12" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="J12" s="26" t="n">
+      <c r="J12" s="4" t="n">
         <v>45784</v>
       </c>
-      <c r="K12" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="L12" s="26" t="n">
+      <c r="K12" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="L12" s="4" t="n">
         <v>45783</v>
       </c>
-      <c r="M12" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="N12" s="26" t="n">
+      <c r="M12" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="N12" s="4" t="n">
         <v>45783</v>
       </c>
-      <c r="O12" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="P12" s="26" t="n">
+      <c r="O12" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="P12" s="4" t="n">
         <v>45784</v>
       </c>
-      <c r="Q12" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="R12" s="26" t="n">
+      <c r="Q12" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="R12" s="4" t="n">
         <v>45783</v>
       </c>
-      <c r="S12" s="23" t="n">
+      <c r="S12" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="T12" s="23" t="n">
+      <c r="T12" s="1" t="n">
         <f aca="false">Q12+S12/2</f>
         <v>9</v>
       </c>
-      <c r="U12" s="24" t="n">
+      <c r="U12" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(M12,O12,T12),0)</f>
         <v>8</v>
       </c>
-      <c r="V12" s="24" t="str">
+      <c r="V12" s="8" t="str">
         <f aca="false">IF(U12&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W12" s="24" t="n">
-        <v>8</v>
-      </c>
-      <c r="X12" s="26" t="n">
+      <c r="W12" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="X12" s="4" t="n">
         <v>45848</v>
       </c>
-      <c r="Y12" s="24" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z12" s="26" t="n">
+      <c r="Y12" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z12" s="4" t="n">
         <v>45848</v>
       </c>
-      <c r="AA12" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB12" s="24"/>
-      <c r="AC12" s="24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD12" s="24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE12" s="23" t="n">
+      <c r="AA12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="8"/>
+      <c r="AC12" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD12" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE12" s="1" t="n">
         <f aca="false">AC12+AD12/2</f>
         <v>12</v>
       </c>
-      <c r="AF12" s="24" t="n">
+      <c r="AF12" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AE12,AA12,Y12,W12,U12),0)</f>
         <v>7</v>
       </c>
-      <c r="AG12" s="23"/>
-      <c r="AH12" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="AI12" s="23" t="s">
+      <c r="AH12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AI12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AJ12" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK12" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AL12" s="27" t="s">
-        <v>164</v>
-      </c>
-      <c r="AM12" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AN12" s="27" t="s">
-        <v>164</v>
-      </c>
-      <c r="AO12" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AP12" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="AQ12" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR12" s="26" t="n">
+      <c r="AJ12" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK12" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL12" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="AM12" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN12" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="AO12" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP12" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="AQ12" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR12" s="4" t="n">
         <v>45988</v>
       </c>
-      <c r="AS12" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT12" s="26" t="n">
+      <c r="AS12" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT12" s="4" t="n">
         <v>45988</v>
       </c>
-      <c r="AU12" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV12" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="AW12" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX12" s="28" t="n">
+      <c r="AU12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV12" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="AW12" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX12" s="29" t="n">
         <v>45988</v>
       </c>
-      <c r="AY12" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ12" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA12" s="23" t="n">
+      <c r="AY12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA12" s="1" t="n">
         <f aca="false">AY12+AZ12/2</f>
         <v>15</v>
       </c>
-      <c r="BB12" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC12" s="24" t="n">
+      <c r="BB12" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC12" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AJ12,AK12,AM12,AO12,AQ12,AS12,AU12,AW12,BA12,BB12),0)</f>
         <v>7</v>
       </c>
-      <c r="BD12" s="24" t="n">
+      <c r="BD12" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AF12,BC12),0)</f>
         <v>7</v>
       </c>
-      <c r="BF12" s="29" t="n">
+      <c r="BF12" s="1" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="17" t="s">
         <v>50</v>
       </c>
       <c r="C13" s="1" t="n">
@@ -11780,35 +11838,35 @@
         <f aca="false">Q13+S13/2</f>
         <v>10.5</v>
       </c>
-      <c r="U13" s="7" t="n">
+      <c r="U13" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(M13,O13,T13),0)</f>
         <v>10</v>
       </c>
-      <c r="V13" s="7" t="str">
+      <c r="V13" s="8" t="str">
         <f aca="false">IF(U13&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W13" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="X13" s="7"/>
-      <c r="Y13" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z13" s="7"/>
-      <c r="AA13" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB13" s="7"/>
-      <c r="AC13" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD13" s="7"/>
+      <c r="W13" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="X13" s="8"/>
+      <c r="Y13" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z13" s="8"/>
+      <c r="AA13" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB13" s="8"/>
+      <c r="AC13" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD13" s="8"/>
       <c r="AE13" s="1" t="n">
         <f aca="false">AC13+AD13/2</f>
         <v>7</v>
       </c>
-      <c r="AF13" s="7" t="n">
+      <c r="AF13" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AE13,AA13,Y13,W13,U13),0)</f>
         <v>9</v>
       </c>
@@ -11822,43 +11880,43 @@
         <v>7</v>
       </c>
       <c r="AL13" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AM13" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AN13" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AO13" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AP13" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AQ13" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AR13" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AS13" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AT13" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AU13" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AV13" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AW13" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AY13" s="3" t="n">
         <v>8</v>
@@ -11869,20 +11927,20 @@
         <v>8</v>
       </c>
       <c r="BB13" s="3"/>
-      <c r="BC13" s="7" t="n">
+      <c r="BC13" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AJ13,AK13,AM13,AO13,AQ13,AS13,AU13,AW13,BA13),0)</f>
         <v>7</v>
       </c>
-      <c r="BD13" s="7" t="n">
+      <c r="BD13" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AF13,BC13),0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="17" t="s">
         <v>53</v>
       </c>
       <c r="C14" s="2" t="n">
@@ -11928,41 +11986,41 @@
         <f aca="false">Q14+S14/2</f>
         <v>8.5</v>
       </c>
-      <c r="U14" s="7" t="n">
+      <c r="U14" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(M14,O14,T14),0)</f>
         <v>9</v>
       </c>
-      <c r="V14" s="7" t="str">
+      <c r="V14" s="8" t="str">
         <f aca="false">IF(U14&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W14" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="X14" s="17" t="n">
+      <c r="W14" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="X14" s="20" t="n">
         <v>45848</v>
       </c>
-      <c r="Y14" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z14" s="17" t="n">
+      <c r="Y14" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z14" s="20" t="n">
         <v>45848</v>
       </c>
-      <c r="AA14" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB14" s="17" t="n">
+      <c r="AA14" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB14" s="20" t="n">
         <v>45848</v>
       </c>
-      <c r="AC14" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD14" s="7"/>
+      <c r="AC14" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD14" s="8"/>
       <c r="AE14" s="1" t="n">
         <f aca="false">AC14+AD14/2</f>
         <v>7</v>
       </c>
-      <c r="AF14" s="7" t="n">
+      <c r="AF14" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AE14,AA14,Y14,W14,U14),0)</f>
         <v>8</v>
       </c>
@@ -11975,44 +12033,44 @@
       <c r="AK14" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AL14" s="14" t="s">
-        <v>135</v>
+      <c r="AL14" s="17" t="s">
+        <v>136</v>
       </c>
       <c r="AM14" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AN14" s="14" t="s">
-        <v>170</v>
+      <c r="AN14" s="17" t="s">
+        <v>172</v>
       </c>
       <c r="AO14" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AP14" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AQ14" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AR14" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AS14" s="6" t="n">
         <v>5</v>
       </c>
       <c r="AT14" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AU14" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AV14" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AW14" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AX14" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AY14" s="3" t="n">
         <v>3</v>
@@ -12027,20 +12085,20 @@
       <c r="BB14" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="BC14" s="7" t="n">
+      <c r="BC14" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AJ14,AK14,AM14,AO14,AQ14,AS14,AU14,AW14,BA14,BB14),0)</f>
         <v>8</v>
       </c>
-      <c r="BD14" s="7" t="n">
+      <c r="BD14" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AF14,BC14),0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="17" t="s">
         <v>56</v>
       </c>
       <c r="C15" s="1" t="n">
@@ -12074,35 +12132,35 @@
         <f aca="false">Q15+S15/2</f>
         <v>9</v>
       </c>
-      <c r="U15" s="7" t="n">
+      <c r="U15" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(M15,O15,T15),0)</f>
         <v>9</v>
       </c>
-      <c r="V15" s="7" t="str">
+      <c r="V15" s="8" t="str">
         <f aca="false">IF(U15&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W15" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="X15" s="7"/>
-      <c r="Y15" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z15" s="7"/>
-      <c r="AA15" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB15" s="7"/>
-      <c r="AC15" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD15" s="20"/>
+      <c r="W15" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="X15" s="8"/>
+      <c r="Y15" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z15" s="8"/>
+      <c r="AA15" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB15" s="8"/>
+      <c r="AC15" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD15" s="23"/>
       <c r="AE15" s="1" t="n">
         <f aca="false">AC15+AD15/2</f>
         <v>10</v>
       </c>
-      <c r="AF15" s="7" t="n">
+      <c r="AF15" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AE15,AA15,Y15,W15,U15),0)</f>
         <v>10</v>
       </c>
@@ -12115,44 +12173,44 @@
       <c r="AK15" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AL15" s="14" t="s">
-        <v>135</v>
+      <c r="AL15" s="17" t="s">
+        <v>136</v>
       </c>
       <c r="AM15" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AN15" s="14" t="s">
-        <v>173</v>
+      <c r="AN15" s="17" t="s">
+        <v>175</v>
       </c>
       <c r="AO15" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AP15" s="14" t="s">
-        <v>174</v>
+      <c r="AP15" s="17" t="s">
+        <v>176</v>
       </c>
       <c r="AQ15" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AR15" s="14" t="s">
-        <v>175</v>
+      <c r="AR15" s="17" t="s">
+        <v>177</v>
       </c>
       <c r="AS15" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="AT15" s="14" t="s">
-        <v>176</v>
+      <c r="AT15" s="17" t="s">
+        <v>178</v>
       </c>
       <c r="AU15" s="2" t="n">
         <v>7</v>
       </c>
       <c r="AV15" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AW15" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="AX15" s="14" t="s">
-        <v>178</v>
+      <c r="AX15" s="17" t="s">
+        <v>180</v>
       </c>
       <c r="AY15" s="6" t="n">
         <v>7</v>
@@ -12165,20 +12223,20 @@
         <v>11.5</v>
       </c>
       <c r="BB15" s="6"/>
-      <c r="BC15" s="7" t="n">
+      <c r="BC15" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AJ15,AK15,AM15,AO15,AQ15,AS15,AU15,AW15,BA15),0)</f>
         <v>9</v>
       </c>
-      <c r="BD15" s="7" t="n">
+      <c r="BD15" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AF15,BC15),0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="17" t="s">
         <v>60</v>
       </c>
       <c r="C16" s="1" t="n">
@@ -12211,41 +12269,41 @@
       <c r="T16" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="U16" s="7" t="n">
+      <c r="U16" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(M16,O16,T16),0)</f>
         <v>8</v>
       </c>
-      <c r="V16" s="7" t="str">
+      <c r="V16" s="8" t="str">
         <f aca="false">IF(U16&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
       <c r="W16" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="X16" s="17" t="n">
+      <c r="X16" s="20" t="n">
         <v>45848</v>
       </c>
-      <c r="Y16" s="20" t="n">
+      <c r="Y16" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="Z16" s="17" t="n">
+      <c r="Z16" s="20" t="n">
         <v>45848</v>
       </c>
-      <c r="AA16" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB16" s="17" t="n">
+      <c r="AA16" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB16" s="20" t="n">
         <v>45848</v>
       </c>
-      <c r="AC16" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD16" s="7"/>
+      <c r="AC16" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD16" s="8"/>
       <c r="AE16" s="1" t="n">
         <f aca="false">AC16+AD16/2</f>
         <v>8</v>
       </c>
-      <c r="AF16" s="7" t="n">
+      <c r="AF16" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AE16,AA16,Y16,W16,U16),0)</f>
         <v>7</v>
       </c>
@@ -12259,58 +12317,58 @@
         <v>9</v>
       </c>
       <c r="AL16" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AM16" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AN16" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AO16" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AP16" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AQ16" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AR16" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AS16" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AT16" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AU16" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AV16" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AW16" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AX16" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="AY16" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ16" s="14"/>
+        <v>186</v>
+      </c>
+      <c r="AY16" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ16" s="17"/>
       <c r="BA16" s="1" t="n">
         <f aca="false">AY16+AZ16/2</f>
         <v>9</v>
       </c>
-      <c r="BB16" s="14"/>
-      <c r="BC16" s="7" t="n">
+      <c r="BB16" s="17"/>
+      <c r="BC16" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AJ16,AK16,AM16,AO16,AQ16,AS16,AU16,AW16,BA16),0)</f>
         <v>8</v>
       </c>
-      <c r="BD16" s="7" t="n">
+      <c r="BD16" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AF16,BC16),0)</f>
         <v>8</v>
       </c>
@@ -12319,7 +12377,7 @@
       <c r="A17" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="17" t="s">
         <v>63</v>
       </c>
       <c r="C17" s="32" t="n">
@@ -12328,28 +12386,28 @@
       <c r="D17" s="33" t="n">
         <v>45881</v>
       </c>
-      <c r="E17" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="F17" s="17" t="n">
+      <c r="E17" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F17" s="20" t="n">
         <v>45846</v>
       </c>
-      <c r="G17" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="H17" s="17" t="n">
+      <c r="G17" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="H17" s="20" t="n">
         <v>45846</v>
       </c>
-      <c r="I17" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="J17" s="17" t="n">
+      <c r="I17" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" s="20" t="n">
         <v>45846</v>
       </c>
-      <c r="K17" s="11" t="n">
+      <c r="K17" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="L17" s="17" t="n">
+      <c r="L17" s="20" t="n">
         <v>45848</v>
       </c>
       <c r="M17" s="32" t="n">
@@ -12358,16 +12416,16 @@
       <c r="N17" s="33" t="n">
         <v>45881</v>
       </c>
-      <c r="O17" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="P17" s="17" t="n">
+      <c r="O17" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="P17" s="20" t="n">
         <v>45848</v>
       </c>
-      <c r="Q17" s="11" t="n">
+      <c r="Q17" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="R17" s="17" t="n">
+      <c r="R17" s="20" t="n">
         <v>45848</v>
       </c>
       <c r="S17" s="1" t="n">
@@ -12377,24 +12435,24 @@
         <f aca="false">Q17+S17/2</f>
         <v>6</v>
       </c>
-      <c r="U17" s="7" t="n">
+      <c r="U17" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(C17,E17,G17,I17,K17,M17,O17,T17),0)</f>
         <v>7</v>
       </c>
-      <c r="V17" s="7" t="str">
+      <c r="V17" s="8" t="str">
         <f aca="false">IF(U17&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W17" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="X17" s="17" t="n">
+      <c r="W17" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="X17" s="20" t="n">
         <v>45848</v>
       </c>
-      <c r="Y17" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z17" s="17" t="n">
+      <c r="Y17" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z17" s="20" t="n">
         <v>45848</v>
       </c>
       <c r="AA17" s="32" t="n">
@@ -12403,20 +12461,20 @@
       <c r="AB17" s="33" t="n">
         <v>45848</v>
       </c>
-      <c r="AC17" s="7" t="n">
+      <c r="AC17" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="AD17" s="7"/>
+      <c r="AD17" s="8"/>
       <c r="AE17" s="1" t="n">
         <f aca="false">AC17+AD17/2</f>
         <v>5</v>
       </c>
-      <c r="AF17" s="7" t="n">
+      <c r="AF17" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AE17,AA17,Y17,W17,U17),0)</f>
         <v>7</v>
       </c>
       <c r="AG17" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AH17" s="1" t="s">
         <v>18</v>
@@ -12431,31 +12489,31 @@
         <v>7</v>
       </c>
       <c r="AL17" s="34" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AM17" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AN17" s="34" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AO17" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AP17" s="34" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AQ17" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AR17" s="34" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AS17" s="1" t="n">
         <v>5</v>
       </c>
       <c r="AT17" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AU17" s="2" t="n">
         <v>5</v>
@@ -12479,20 +12537,23 @@
       <c r="BB17" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="BC17" s="7" t="n">
+      <c r="BC17" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AJ17,AK17,AM17,AO17,AQ17,AS17,AU17,AW17,BA17,BB17),0)</f>
         <v>7</v>
       </c>
-      <c r="BD17" s="7" t="n">
+      <c r="BD17" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AF17,BC17),0)</f>
         <v>7</v>
+      </c>
+      <c r="BF17" s="3" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="19" t="s">
         <v>66</v>
       </c>
       <c r="C18" s="1" t="n">
@@ -12517,7 +12578,7 @@
         <v>9</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q18" s="1" t="n">
         <v>10</v>
@@ -12529,35 +12590,35 @@
         <f aca="false">Q18+S18/2</f>
         <v>10.5</v>
       </c>
-      <c r="U18" s="7" t="n">
+      <c r="U18" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(M18,O18,T18),0)</f>
         <v>10</v>
       </c>
-      <c r="V18" s="7" t="str">
+      <c r="V18" s="8" t="str">
         <f aca="false">IF(U18&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W18" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="X18" s="7"/>
-      <c r="Y18" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="Z18" s="7"/>
-      <c r="AA18" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB18" s="7"/>
-      <c r="AC18" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD18" s="7"/>
+      <c r="W18" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="X18" s="8"/>
+      <c r="Y18" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="Z18" s="8"/>
+      <c r="AA18" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB18" s="8"/>
+      <c r="AC18" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD18" s="8"/>
       <c r="AE18" s="1" t="n">
         <f aca="false">AC18+AD18/2</f>
         <v>8</v>
       </c>
-      <c r="AF18" s="7" t="n">
+      <c r="AF18" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AE18,AA18,Y18,W18,U18),0)</f>
         <v>9</v>
       </c>
@@ -12577,20 +12638,20 @@
       <c r="BB18" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="BC18" s="7" t="n">
+      <c r="BC18" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AJ18,AK18,AM18,AO18,AQ18,AS18,AU18,AW18,BA18,BB18),0)</f>
         <v>3</v>
       </c>
-      <c r="BD18" s="7" t="n">
+      <c r="BD18" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AF18,BC18),0)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="17.7" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="17" t="s">
         <v>69</v>
       </c>
       <c r="C19" s="1" t="n">
@@ -12624,39 +12685,39 @@
         <f aca="false">Q19+S19/2</f>
         <v>8.5</v>
       </c>
-      <c r="U19" s="7" t="n">
+      <c r="U19" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(M19,O19,T19),0)</f>
         <v>9</v>
       </c>
-      <c r="V19" s="7" t="str">
+      <c r="V19" s="8" t="str">
         <f aca="false">IF(U19&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W19" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="X19" s="7"/>
+      <c r="W19" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="X19" s="8"/>
       <c r="Y19" s="35" t="n">
         <v>9</v>
       </c>
       <c r="Z19" s="4" t="n">
         <v>45848</v>
       </c>
-      <c r="AA19" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB19" s="17" t="n">
+      <c r="AA19" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB19" s="20" t="n">
         <v>45848</v>
       </c>
-      <c r="AC19" s="7" t="n">
+      <c r="AC19" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="AD19" s="7"/>
+      <c r="AD19" s="8"/>
       <c r="AE19" s="1" t="n">
         <f aca="false">AC19+AD19/2</f>
         <v>5</v>
       </c>
-      <c r="AF19" s="7" t="n">
+      <c r="AF19" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AE19,AA19,Y19,W19,U19),0)</f>
         <v>8</v>
       </c>
@@ -12670,43 +12731,43 @@
         <v>6</v>
       </c>
       <c r="AL19" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AM19" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AN19" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AO19" s="1" t="n">
         <v>6</v>
       </c>
       <c r="AP19" s="34" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AQ19" s="1" t="n">
         <v>6</v>
       </c>
       <c r="AR19" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AS19" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AT19" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AU19" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AV19" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AW19" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AX19" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="AY19" s="1" t="n">
         <v>7</v>
@@ -12715,20 +12776,20 @@
         <f aca="false">AY19+AZ19/2</f>
         <v>7</v>
       </c>
-      <c r="BC19" s="7" t="n">
+      <c r="BC19" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AJ19,AK19,AM19,AO19,AQ19,AS19,AU19,AW19,BA19),0)</f>
         <v>7</v>
       </c>
-      <c r="BD19" s="7" t="n">
+      <c r="BD19" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AF19,BC19),0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="17" t="s">
         <v>72</v>
       </c>
       <c r="C20" s="1" t="n">
@@ -12762,35 +12823,35 @@
         <f aca="false">Q20+S20/2</f>
         <v>10.5</v>
       </c>
-      <c r="U20" s="7" t="n">
+      <c r="U20" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(M20,O20,T20),0)</f>
         <v>10</v>
       </c>
-      <c r="V20" s="7" t="str">
+      <c r="V20" s="8" t="str">
         <f aca="false">IF(U20&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W20" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="X20" s="7"/>
-      <c r="Y20" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z20" s="7"/>
-      <c r="AA20" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB20" s="7"/>
-      <c r="AC20" s="7" t="n">
+      <c r="W20" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="X20" s="8"/>
+      <c r="Y20" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z20" s="8"/>
+      <c r="AA20" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB20" s="8"/>
+      <c r="AC20" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="AD20" s="7"/>
+      <c r="AD20" s="8"/>
       <c r="AE20" s="1" t="n">
         <f aca="false">AC20+AD20/2</f>
         <v>6</v>
       </c>
-      <c r="AF20" s="7" t="n">
+      <c r="AF20" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AE20,AA20,Y20,W20,U20),0)</f>
         <v>8</v>
       </c>
@@ -12804,43 +12865,43 @@
         <v>7</v>
       </c>
       <c r="AL20" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AM20" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AN20" s="6" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="AO20" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AP20" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AQ20" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AR20" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AS20" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AT20" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AU20" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AV20" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AW20" s="1" t="n">
         <v>4</v>
       </c>
       <c r="AX20" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AY20" s="2" t="n">
         <v>9</v>
@@ -12851,20 +12912,20 @@
         <v>9</v>
       </c>
       <c r="BB20" s="2"/>
-      <c r="BC20" s="7" t="n">
+      <c r="BC20" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AJ20,AK20,AM20,AO20,AQ20,AS20,AU20,AW20,BA20),0)</f>
         <v>7</v>
       </c>
-      <c r="BD20" s="7" t="n">
+      <c r="BD20" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AF20,BC20),0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="17" t="s">
         <v>75</v>
       </c>
       <c r="C21" s="1" t="n">
@@ -12898,35 +12959,35 @@
         <f aca="false">Q21+S21/2</f>
         <v>11</v>
       </c>
-      <c r="U21" s="7" t="n">
+      <c r="U21" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(M21,O21,T21),0)</f>
         <v>10</v>
       </c>
-      <c r="V21" s="7" t="str">
+      <c r="V21" s="8" t="str">
         <f aca="false">IF(U21&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W21" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="X21" s="7"/>
-      <c r="Y21" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z21" s="7"/>
-      <c r="AA21" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB21" s="7"/>
-      <c r="AC21" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD21" s="7"/>
+      <c r="W21" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="X21" s="8"/>
+      <c r="Y21" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z21" s="8"/>
+      <c r="AA21" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB21" s="8"/>
+      <c r="AC21" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD21" s="8"/>
       <c r="AE21" s="1" t="n">
         <f aca="false">AC21+AD21/2</f>
         <v>10</v>
       </c>
-      <c r="AF21" s="7" t="n">
+      <c r="AF21" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AE21,AA21,Y21,W21,U21),0)</f>
         <v>9</v>
       </c>
@@ -12940,31 +13001,31 @@
         <v>7</v>
       </c>
       <c r="AL21" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AM21" s="36" t="n">
         <v>7</v>
       </c>
       <c r="AN21" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AO21" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AP21" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AQ21" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AR21" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AS21" s="36" t="n">
         <v>7</v>
       </c>
       <c r="AT21" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="AU21" s="36" t="n">
         <v>7</v>
@@ -12973,7 +13034,7 @@
         <v>7</v>
       </c>
       <c r="AX21" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AY21" s="6" t="n">
         <v>10</v>
@@ -12986,11 +13047,11 @@
       <c r="BB21" s="6" t="n">
         <v>9.5</v>
       </c>
-      <c r="BC21" s="7" t="n">
+      <c r="BC21" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AJ21,AK21,AM21,AO21,AQ21,AS21,AU21,AW21,BA21,BB21),0)</f>
         <v>8</v>
       </c>
-      <c r="BD21" s="7" t="n">
+      <c r="BD21" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AF21,BC21),0)</f>
         <v>9</v>
       </c>
@@ -12999,7 +13060,7 @@
       <c r="A22" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="19" t="s">
         <v>78</v>
       </c>
       <c r="C22" s="1" t="n">
@@ -13033,35 +13094,35 @@
         <f aca="false">Q22+S22/2</f>
         <v>2</v>
       </c>
-      <c r="U22" s="7" t="n">
+      <c r="U22" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(C22,E22,G22,I22,K22,M22,O22,T22),0)</f>
         <v>2</v>
       </c>
-      <c r="V22" s="7" t="str">
+      <c r="V22" s="8" t="str">
         <f aca="false">IF(U22&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="W22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="X22" s="7"/>
-      <c r="Y22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z22" s="7"/>
-      <c r="AA22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB22" s="7"/>
-      <c r="AC22" s="7" t="n">
+      <c r="W22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X22" s="8"/>
+      <c r="Y22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="8"/>
+      <c r="AA22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="8"/>
+      <c r="AC22" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="AD22" s="7"/>
+      <c r="AD22" s="8"/>
       <c r="AE22" s="1" t="n">
         <f aca="false">AC22+AD22/2</f>
         <v>6</v>
       </c>
-      <c r="AF22" s="7" t="n">
+      <c r="AF22" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AE22,AA22,Y22,W22,U22),0)</f>
         <v>2</v>
       </c>
@@ -13078,43 +13139,43 @@
         <v>7</v>
       </c>
       <c r="AL22" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="AM22" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AN22" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="AO22" s="1" t="n">
         <v>5</v>
       </c>
       <c r="AP22" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AQ22" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AR22" s="6" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AS22" s="1" t="n">
         <v>5</v>
       </c>
       <c r="AT22" s="6" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AU22" s="1" t="n">
         <v>5</v>
       </c>
       <c r="AV22" s="6" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AW22" s="1" t="n">
         <v>2</v>
       </c>
       <c r="AX22" s="6" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="AY22" s="2" t="n">
         <v>3</v>
@@ -13125,20 +13186,20 @@
         <v>3</v>
       </c>
       <c r="BB22" s="2"/>
-      <c r="BC22" s="7" t="n">
+      <c r="BC22" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AJ22,AK22,AM22,AO22,AQ22,AS22,AU22,AW22,BA22),0)</f>
         <v>5</v>
       </c>
-      <c r="BD22" s="7" t="n">
+      <c r="BD22" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AF22,BC22),0)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="17" t="s">
         <v>81</v>
       </c>
       <c r="C23" s="1" t="n">
@@ -13150,7 +13211,7 @@
       <c r="G23" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="I23" s="15" t="n">
+      <c r="I23" s="18" t="n">
         <v>6</v>
       </c>
       <c r="J23" s="4" t="n">
@@ -13175,35 +13236,35 @@
         <f aca="false">Q23+S23/2</f>
         <v>8</v>
       </c>
-      <c r="U23" s="7" t="n">
+      <c r="U23" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(M23,O23,T23),0)</f>
         <v>8</v>
       </c>
-      <c r="V23" s="7" t="str">
+      <c r="V23" s="8" t="str">
         <f aca="false">IF(U23&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W23" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="X23" s="7"/>
-      <c r="Y23" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z23" s="7"/>
-      <c r="AA23" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB23" s="7"/>
-      <c r="AC23" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD23" s="20"/>
+      <c r="W23" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="X23" s="8"/>
+      <c r="Y23" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z23" s="8"/>
+      <c r="AA23" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB23" s="8"/>
+      <c r="AC23" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD23" s="23"/>
       <c r="AE23" s="1" t="n">
         <f aca="false">AC23+AD23/2</f>
         <v>8</v>
       </c>
-      <c r="AF23" s="7" t="n">
+      <c r="AF23" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AE23,AA23,Y23,W23,U23),0)</f>
         <v>8</v>
       </c>
@@ -13217,43 +13278,43 @@
         <v>7</v>
       </c>
       <c r="AL23" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AM23" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AN23" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AO23" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AP23" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AQ23" s="1" t="n">
         <v>6</v>
       </c>
       <c r="AR23" s="6" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AS23" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="AT23" s="14" t="s">
-        <v>212</v>
+      <c r="AT23" s="17" t="s">
+        <v>215</v>
       </c>
       <c r="AU23" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AV23" s="6" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AW23" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AX23" s="37" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AY23" s="6" t="n">
         <v>9</v>
@@ -13264,20 +13325,20 @@
         <v>9</v>
       </c>
       <c r="BB23" s="6"/>
-      <c r="BC23" s="7" t="n">
+      <c r="BC23" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AJ23,AK23,AM23,AO23,AQ23,AS23,AU23,AW23,BA23),0)</f>
         <v>7</v>
       </c>
-      <c r="BD23" s="7" t="n">
+      <c r="BD23" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AF23,BC23),0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="17" t="s">
         <v>85</v>
       </c>
       <c r="C24" s="1" t="n">
@@ -13311,35 +13372,35 @@
         <f aca="false">Q24+S24/2</f>
         <v>11.5</v>
       </c>
-      <c r="U24" s="7" t="n">
+      <c r="U24" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(M24,O24,T24),0)</f>
         <v>11</v>
       </c>
-      <c r="V24" s="7" t="str">
+      <c r="V24" s="8" t="str">
         <f aca="false">IF(U24&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W24" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="X24" s="7"/>
-      <c r="Y24" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z24" s="7"/>
-      <c r="AA24" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB24" s="7"/>
-      <c r="AC24" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD24" s="7"/>
+      <c r="W24" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="X24" s="8"/>
+      <c r="Y24" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z24" s="8"/>
+      <c r="AA24" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB24" s="8"/>
+      <c r="AC24" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD24" s="8"/>
       <c r="AE24" s="1" t="n">
         <f aca="false">AC24+AD24/2</f>
         <v>8</v>
       </c>
-      <c r="AF24" s="7" t="n">
+      <c r="AF24" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AE24,AA24,Y24,W24,U24),0)</f>
         <v>10</v>
       </c>
@@ -13353,43 +13414,43 @@
         <v>8</v>
       </c>
       <c r="AL24" s="6" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AM24" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AN24" s="14" t="s">
-        <v>215</v>
+      <c r="AN24" s="17" t="s">
+        <v>218</v>
       </c>
       <c r="AO24" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AP24" s="6" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AQ24" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AR24" s="6" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AS24" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AT24" s="6" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AU24" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AV24" s="14" t="s">
-        <v>214</v>
+      <c r="AV24" s="17" t="s">
+        <v>217</v>
       </c>
       <c r="AW24" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AX24" s="14" t="s">
-        <v>217</v>
+      <c r="AX24" s="17" t="s">
+        <v>220</v>
       </c>
       <c r="AY24" s="1" t="n">
         <v>9</v>
@@ -13398,20 +13459,20 @@
         <f aca="false">AY24+AZ24/2</f>
         <v>9</v>
       </c>
-      <c r="BC24" s="7" t="n">
+      <c r="BC24" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AJ24,AK24,AM24,AO24,AQ24,AS24,AU24,AW24,BA24),0)</f>
         <v>9</v>
       </c>
-      <c r="BD24" s="7" t="n">
+      <c r="BD24" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AF24,BC24),0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="17" t="s">
         <v>88</v>
       </c>
       <c r="C25" s="1" t="n">
@@ -13445,34 +13506,34 @@
         <f aca="false">Q25+S25/2</f>
         <v>16.5</v>
       </c>
-      <c r="U25" s="7" t="n">
+      <c r="U25" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(M25,O25,T25),0)</f>
         <v>12</v>
       </c>
-      <c r="V25" s="7" t="str">
+      <c r="V25" s="8" t="str">
         <f aca="false">IF(U25&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
       <c r="W25" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="Y25" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z25" s="7"/>
-      <c r="AA25" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB25" s="7"/>
-      <c r="AC25" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD25" s="7"/>
+      <c r="Y25" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z25" s="8"/>
+      <c r="AA25" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB25" s="8"/>
+      <c r="AC25" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD25" s="8"/>
       <c r="AE25" s="1" t="n">
         <f aca="false">AC25+AD25/2</f>
         <v>10</v>
       </c>
-      <c r="AF25" s="7" t="n">
+      <c r="AF25" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AE25,AA25,Y25,W25,U25),0)</f>
         <v>10</v>
       </c>
@@ -13486,43 +13547,43 @@
         <v>9</v>
       </c>
       <c r="AL25" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AM25" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AN25" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AO25" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AP25" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="AQ25" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AR25" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="AS25" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AT25" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="AU25" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AV25" s="14" t="s">
-        <v>221</v>
+      <c r="AV25" s="17" t="s">
+        <v>224</v>
       </c>
       <c r="AW25" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AX25" s="14" t="s">
-        <v>178</v>
+      <c r="AX25" s="17" t="s">
+        <v>180</v>
       </c>
       <c r="AY25" s="1" t="n">
         <v>8</v>
@@ -13534,20 +13595,20 @@
         <f aca="false">AY25+AZ25/2</f>
         <v>12</v>
       </c>
-      <c r="BC25" s="7" t="n">
+      <c r="BC25" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AJ25,AK25,AM25,AO25,AQ25,AS25,AU25,AW25,BA25),0)</f>
         <v>10</v>
       </c>
-      <c r="BD25" s="7" t="n">
+      <c r="BD25" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AF25,BC25),0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="17" t="s">
         <v>91</v>
       </c>
       <c r="C26" s="1" t="n">
@@ -13581,11 +13642,11 @@
         <f aca="false">Q26+S26/2</f>
         <v>13.5</v>
       </c>
-      <c r="U26" s="7" t="n">
+      <c r="U26" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(M26,O26,T26),0)</f>
         <v>11</v>
       </c>
-      <c r="V26" s="7" t="str">
+      <c r="V26" s="8" t="str">
         <f aca="false">IF(U26&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -13598,15 +13659,15 @@
       <c r="AA26" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AC26" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD26" s="7"/>
+      <c r="AC26" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD26" s="8"/>
       <c r="AE26" s="1" t="n">
         <f aca="false">AC26+AD26/2</f>
         <v>8</v>
       </c>
-      <c r="AF26" s="7" t="n">
+      <c r="AF26" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AE26,AA26,Y26,W26,U26),0)</f>
         <v>10</v>
       </c>
@@ -13619,44 +13680,44 @@
       <c r="AK26" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AL26" s="14" t="s">
-        <v>222</v>
+      <c r="AL26" s="17" t="s">
+        <v>225</v>
       </c>
       <c r="AM26" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AN26" s="14" t="s">
-        <v>222</v>
+      <c r="AN26" s="17" t="s">
+        <v>225</v>
       </c>
       <c r="AO26" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AP26" s="14" t="s">
-        <v>174</v>
+      <c r="AP26" s="17" t="s">
+        <v>176</v>
       </c>
       <c r="AQ26" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AR26" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AS26" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AT26" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AU26" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AV26" s="14" t="s">
-        <v>159</v>
+      <c r="AV26" s="17" t="s">
+        <v>161</v>
       </c>
       <c r="AW26" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AX26" s="14" t="s">
-        <v>223</v>
+      <c r="AX26" s="17" t="s">
+        <v>226</v>
       </c>
       <c r="AY26" s="1" t="n">
         <v>9</v>
@@ -13665,20 +13726,20 @@
         <f aca="false">AY26+AZ26/2</f>
         <v>9</v>
       </c>
-      <c r="BC26" s="7" t="n">
+      <c r="BC26" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AJ26,AK26,AM26,AO26,AQ26,AS26,AU26,AW26,BA26),0)</f>
         <v>10</v>
       </c>
-      <c r="BD26" s="7" t="n">
+      <c r="BD26" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AF26,BC26),0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="17" t="s">
         <v>94</v>
       </c>
       <c r="C27" s="1" t="n">
@@ -13712,41 +13773,41 @@
         <f aca="false">Q27+S27/2</f>
         <v>10.5</v>
       </c>
-      <c r="U27" s="7" t="n">
+      <c r="U27" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(M27,O27,T27),0)</f>
         <v>9</v>
       </c>
-      <c r="V27" s="7" t="str">
+      <c r="V27" s="8" t="str">
         <f aca="false">IF(U27&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W27" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="X27" s="17" t="n">
+      <c r="W27" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="X27" s="20" t="n">
         <v>45848</v>
       </c>
-      <c r="Y27" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z27" s="17" t="n">
+      <c r="Y27" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z27" s="20" t="n">
         <v>45848</v>
       </c>
-      <c r="AA27" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB27" s="17" t="n">
+      <c r="AA27" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB27" s="20" t="n">
         <v>45848</v>
       </c>
-      <c r="AC27" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD27" s="7"/>
+      <c r="AC27" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD27" s="8"/>
       <c r="AE27" s="1" t="n">
         <f aca="false">AC27+AD27/2</f>
         <v>10</v>
       </c>
-      <c r="AF27" s="7" t="n">
+      <c r="AF27" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AE27,AA27,Y27,W27,U27),0)</f>
         <v>8</v>
       </c>
@@ -13760,43 +13821,43 @@
         <v>9</v>
       </c>
       <c r="AL27" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AM27" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AN27" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AO27" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AP27" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AQ27" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AR27" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="AS27" s="18" t="n">
+        <v>227</v>
+      </c>
+      <c r="AS27" s="21" t="n">
         <v>1</v>
       </c>
       <c r="AT27" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AU27" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AV27" s="14" t="s">
-        <v>159</v>
+      <c r="AV27" s="17" t="s">
+        <v>161</v>
       </c>
       <c r="AW27" s="1" t="n">
         <v>3</v>
       </c>
       <c r="AX27" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AY27" s="1" t="n">
         <v>8</v>
@@ -13805,11 +13866,11 @@
         <f aca="false">AY27+AZ27/2</f>
         <v>8</v>
       </c>
-      <c r="BC27" s="7" t="n">
+      <c r="BC27" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AJ27,AK27,AM27,AO27,AQ27,AS27,AU27,AW27,BA27),0)</f>
         <v>7</v>
       </c>
-      <c r="BD27" s="7" t="n">
+      <c r="BD27" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AF27,BC27),0)</f>
         <v>8</v>
       </c>
@@ -13818,22 +13879,22 @@
       <c r="A28" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="11" t="s">
         <v>97</v>
       </c>
       <c r="C28" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="E28" s="11" t="n">
+      <c r="E28" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="F28" s="17" t="n">
+      <c r="F28" s="20" t="n">
         <v>45852</v>
       </c>
-      <c r="G28" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H28" s="17" t="n">
+      <c r="G28" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="H28" s="20" t="n">
         <v>45852</v>
       </c>
       <c r="I28" s="1" t="n">
@@ -13842,10 +13903,10 @@
       <c r="K28" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="M28" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="N28" s="17" t="n">
+      <c r="M28" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="N28" s="20" t="n">
         <v>45852</v>
       </c>
       <c r="O28" s="32" t="n">
@@ -13861,11 +13922,11 @@
         <f aca="false">Q28+S28/2</f>
         <v>7.5</v>
       </c>
-      <c r="U28" s="7" t="n">
+      <c r="U28" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(M28,O28,T28),0)</f>
         <v>8</v>
       </c>
-      <c r="V28" s="7" t="str">
+      <c r="V28" s="8" t="str">
         <f aca="false">IF(U28&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -13885,7 +13946,7 @@
         <f aca="false">AC28+AD28/2</f>
         <v>5</v>
       </c>
-      <c r="AF28" s="7" t="n">
+      <c r="AF28" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AE28,AA28,Y28,W28,U28),0)</f>
         <v>7</v>
       </c>
@@ -13899,31 +13960,31 @@
         <v>8</v>
       </c>
       <c r="AL28" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AM28" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AN28" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="AO28" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ28" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS28" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU28" s="18" t="n">
+        <v>230</v>
+      </c>
+      <c r="AO28" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ28" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS28" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU28" s="21" t="n">
         <v>1</v>
       </c>
       <c r="AW28" s="1" t="n">
         <v>3</v>
       </c>
       <c r="AX28" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="AY28" s="1" t="n">
         <v>3</v>
@@ -13932,11 +13993,11 @@
         <f aca="false">AY28+AZ28/2</f>
         <v>3</v>
       </c>
-      <c r="BC28" s="7" t="n">
+      <c r="BC28" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AJ28,AK28,AM28,AO28,AQ28,AS28,AU28,AW28,BA28),0)</f>
         <v>4</v>
       </c>
-      <c r="BD28" s="7" t="n">
+      <c r="BD28" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(AF28,BC28),0)</f>
         <v>6</v>
       </c>
@@ -13970,7 +14031,7 @@
       <formula>6</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BC3:BC28">
+  <conditionalFormatting sqref="BC3:BC28 BD7">
     <cfRule type="cellIs" priority="7" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>6</formula>
     </cfRule>
@@ -13982,7 +14043,7 @@
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BD3:BD28">
+  <conditionalFormatting sqref="BD8:BD28 BD3:BD6">
     <cfRule type="cellIs" priority="10" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>6</formula>
     </cfRule>
@@ -14466,22 +14527,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>116</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14495,10 +14556,10 @@
         <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>10</v>
@@ -14520,10 +14581,10 @@
         <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>5</v>
@@ -14540,10 +14601,10 @@
         <v>23</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>1</v>
@@ -14563,10 +14624,10 @@
         <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>6</v>
@@ -14586,10 +14647,10 @@
         <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>7</v>
@@ -14611,10 +14672,10 @@
         <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>6</v>
@@ -14625,10 +14686,10 @@
         <v>29</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>6</v>
@@ -14639,10 +14700,10 @@
         <v>29</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>5</v>
@@ -14653,10 +14714,10 @@
         <v>29</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>4</v>
@@ -14701,10 +14762,10 @@
         <v>38</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>8</v>
@@ -14724,10 +14785,10 @@
         <v>41</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -14749,10 +14810,10 @@
         <v>41</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>8</v>
@@ -14769,10 +14830,10 @@
         <v>44</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>10</v>
@@ -14792,10 +14853,10 @@
         <v>47</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>10</v>
@@ -14815,10 +14876,10 @@
         <v>50</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>0</v>
@@ -14852,10 +14913,10 @@
         <v>56</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>10</v>
@@ -14875,10 +14936,10 @@
         <v>60</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>8</v>
@@ -14912,10 +14973,10 @@
         <v>66</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>9</v>
@@ -14937,10 +14998,10 @@
         <v>66</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>5</v>
@@ -14957,10 +15018,10 @@
         <v>69</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>7</v>
@@ -14980,10 +15041,10 @@
         <v>72</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>7</v>
@@ -15003,10 +15064,10 @@
         <v>75</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>10</v>
@@ -15026,10 +15087,10 @@
         <v>78</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>10</v>
@@ -15051,10 +15112,10 @@
         <v>78</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>8</v>
@@ -15065,10 +15126,10 @@
         <v>78</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>8</v>
@@ -15079,10 +15140,10 @@
         <v>78</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>8</v>
@@ -15093,10 +15154,10 @@
         <v>78</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>5</v>
@@ -15107,10 +15168,10 @@
         <v>78</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>1</v>
@@ -15127,10 +15188,10 @@
         <v>81</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>9</v>
@@ -15152,10 +15213,10 @@
         <v>81</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>6</v>
@@ -15172,10 +15233,10 @@
         <v>85</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>10</v>
@@ -15197,10 +15258,10 @@
         <v>85</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>9</v>
@@ -15211,10 +15272,10 @@
         <v>85</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>6</v>
@@ -15231,10 +15292,10 @@
         <v>88</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F39" s="1" t="n">
         <v>10</v>
@@ -15254,10 +15315,10 @@
         <v>91</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F40" s="1" t="n">
         <v>10</v>
@@ -15279,10 +15340,10 @@
         <v>91</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F41" s="1" t="n">
         <v>10</v>
@@ -15293,10 +15354,10 @@
         <v>91</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F42" s="1" t="n">
         <v>9</v>
@@ -15307,10 +15368,10 @@
         <v>91</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F43" s="1" t="n">
         <v>9</v>
@@ -15327,10 +15388,10 @@
         <v>94</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>9</v>
@@ -15352,10 +15413,10 @@
         <v>94</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>8</v>
@@ -15366,10 +15427,10 @@
         <v>94</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F46" s="1" t="n">
         <v>7</v>
@@ -15380,10 +15441,10 @@
         <v>94</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F47" s="1" t="n">
         <v>3</v>
@@ -15450,22 +15511,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>116</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15479,10 +15540,10 @@
         <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>10</v>
@@ -15504,10 +15565,10 @@
         <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>9</v>
@@ -15518,10 +15579,10 @@
         <v>16</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>6</v>
@@ -15552,10 +15613,10 @@
         <v>26</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>8</v>
@@ -15577,10 +15638,10 @@
         <v>26</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>7</v>
@@ -15591,10 +15652,10 @@
         <v>26</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>6</v>
@@ -15653,10 +15714,10 @@
         <v>38</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>8</v>
@@ -15690,10 +15751,10 @@
         <v>44</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>9</v>
@@ -15727,10 +15788,10 @@
         <v>50</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>7</v>
@@ -15764,10 +15825,10 @@
         <v>56</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>10</v>
@@ -15787,10 +15848,10 @@
         <v>60</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>9</v>
@@ -15824,10 +15885,10 @@
         <v>66</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>7</v>
@@ -15847,10 +15908,10 @@
         <v>69</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>9</v>
@@ -15872,10 +15933,10 @@
         <v>69</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>6</v>
@@ -15906,10 +15967,10 @@
         <v>75</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>9</v>
@@ -15931,10 +15992,10 @@
         <v>75</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>7</v>
@@ -15965,10 +16026,10 @@
         <v>81</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>10</v>
@@ -15988,10 +16049,10 @@
         <v>85</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>10</v>
@@ -16011,10 +16072,10 @@
         <v>88</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>10</v>
@@ -16036,10 +16097,10 @@
         <v>88</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>10</v>
@@ -16050,10 +16111,10 @@
         <v>88</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>10</v>
@@ -16064,10 +16125,10 @@
         <v>88</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>8</v>
@@ -16084,10 +16145,10 @@
         <v>91</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>10</v>
@@ -16107,10 +16168,10 @@
         <v>94</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>10</v>
@@ -16130,10 +16191,10 @@
         <v>97</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>5</v>
@@ -16188,22 +16249,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>116</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16217,10 +16278,10 @@
         <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>10</v>
@@ -16254,10 +16315,10 @@
         <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>10</v>
@@ -16319,10 +16380,10 @@
         <v>38</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>9</v>
@@ -16356,10 +16417,10 @@
         <v>44</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>10</v>
@@ -16393,10 +16454,10 @@
         <v>50</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>6</v>
@@ -16418,10 +16479,10 @@
         <v>50</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>10</v>
@@ -16452,10 +16513,10 @@
         <v>56</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>9</v>
@@ -16475,10 +16536,10 @@
         <v>60</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>9</v>
@@ -16512,10 +16573,10 @@
         <v>66</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>10</v>
@@ -16535,10 +16596,10 @@
         <v>69</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>9</v>
@@ -16560,10 +16621,10 @@
         <v>69</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>5</v>
@@ -16574,10 +16635,10 @@
         <v>69</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>9</v>
@@ -16608,10 +16669,10 @@
         <v>75</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>10</v>
@@ -16645,10 +16706,10 @@
         <v>81</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -16668,10 +16729,10 @@
         <v>85</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>10</v>
@@ -16691,10 +16752,10 @@
         <v>88</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>10</v>
@@ -16714,10 +16775,10 @@
         <v>91</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>10</v>
@@ -16737,10 +16798,10 @@
         <v>94</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>10</v>
@@ -16804,22 +16865,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>116</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16861,10 +16922,10 @@
         <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>10</v>
@@ -16954,10 +17015,10 @@
         <v>44</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>10</v>
@@ -16979,10 +17040,10 @@
         <v>44</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>8</v>
@@ -17041,10 +17102,10 @@
         <v>56</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -17064,10 +17125,10 @@
         <v>60</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>9</v>
@@ -17101,10 +17162,10 @@
         <v>66</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>7</v>
@@ -17124,10 +17185,10 @@
         <v>69</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>9</v>
@@ -17147,10 +17208,10 @@
         <v>72</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>7</v>
@@ -17170,10 +17231,10 @@
         <v>75</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>9</v>
@@ -17195,10 +17256,10 @@
         <v>75</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>6</v>
@@ -17243,10 +17304,10 @@
         <v>85</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -17266,10 +17327,10 @@
         <v>88</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>10</v>
@@ -17289,10 +17350,10 @@
         <v>91</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>10</v>
@@ -17312,10 +17373,10 @@
         <v>94</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>8</v>
@@ -17387,22 +17448,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>116</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17416,10 +17477,10 @@
         <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>8</v>
@@ -17453,10 +17514,10 @@
         <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>8</v>
@@ -17476,10 +17537,10 @@
         <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>6</v>
@@ -17499,10 +17560,10 @@
         <v>32</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>10</v>
@@ -17536,10 +17597,10 @@
         <v>38</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>8</v>
@@ -17573,10 +17634,10 @@
         <v>44</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>8</v>
@@ -17598,10 +17659,10 @@
         <v>44</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>7</v>
@@ -17632,10 +17693,10 @@
         <v>50</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>9</v>
@@ -17655,10 +17716,10 @@
         <v>53</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -17678,10 +17739,10 @@
         <v>56</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -17703,10 +17764,10 @@
         <v>56</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>9</v>
@@ -17717,10 +17778,10 @@
         <v>56</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>9</v>
@@ -17731,10 +17792,10 @@
         <v>56</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>7</v>
@@ -17745,10 +17806,10 @@
         <v>56</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>6</v>
@@ -17765,10 +17826,10 @@
         <v>60</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>9</v>
@@ -17802,10 +17863,10 @@
         <v>66</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>7</v>
@@ -17825,10 +17886,10 @@
         <v>69</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>9</v>
@@ -17848,10 +17909,10 @@
         <v>72</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>7</v>
@@ -17871,10 +17932,10 @@
         <v>75</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -17908,10 +17969,10 @@
         <v>81</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>9</v>
@@ -17931,10 +17992,10 @@
         <v>85</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>10</v>
@@ -17956,10 +18017,10 @@
         <v>85</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>9</v>
@@ -17970,10 +18031,10 @@
         <v>85</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>6</v>
@@ -17984,10 +18045,10 @@
         <v>85</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>6</v>
@@ -17998,10 +18059,10 @@
         <v>85</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>6</v>
@@ -18012,10 +18073,10 @@
         <v>85</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>5</v>
@@ -18032,15 +18093,15 @@
         <v>88</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="I34" s="15" t="n">
+      <c r="I34" s="18" t="n">
         <v>10</v>
       </c>
     </row>
@@ -18055,10 +18116,10 @@
         <v>91</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>10</v>
@@ -18078,16 +18139,16 @@
         <v>94</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>8</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="H36" s="1" t="n">
         <v>8</v>
@@ -18102,10 +18163,10 @@
         <v>94</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>8</v>
@@ -18116,10 +18177,10 @@
         <v>94</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>5</v>
@@ -18188,22 +18249,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>116</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18217,10 +18278,10 @@
         <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>8</v>
@@ -18254,10 +18315,10 @@
         <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>8</v>
@@ -18279,10 +18340,10 @@
         <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>7</v>
@@ -18299,10 +18360,10 @@
         <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>2</v>
@@ -18322,10 +18383,10 @@
         <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>10</v>
@@ -18347,10 +18408,10 @@
         <v>32</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>9</v>
@@ -18361,10 +18422,10 @@
         <v>32</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>7</v>
@@ -18375,10 +18436,10 @@
         <v>32</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>6</v>
@@ -18389,10 +18450,10 @@
         <v>32</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>4</v>
@@ -18423,10 +18484,10 @@
         <v>38</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>8</v>
@@ -18460,10 +18521,10 @@
         <v>44</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -18497,10 +18558,10 @@
         <v>50</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>10</v>
@@ -18520,10 +18581,10 @@
         <v>53</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>9</v>
@@ -18545,10 +18606,10 @@
         <v>53</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>8</v>
@@ -18559,10 +18620,10 @@
         <v>53</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>3</v>
@@ -18579,10 +18640,10 @@
         <v>56</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>10</v>
@@ -18604,10 +18665,10 @@
         <v>56</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>8</v>
@@ -18618,10 +18679,10 @@
         <v>56</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>8</v>
@@ -18638,10 +18699,10 @@
         <v>60</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>9</v>
@@ -18675,10 +18736,10 @@
         <v>66</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>9</v>
@@ -18698,10 +18759,10 @@
         <v>69</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>10</v>
@@ -18723,10 +18784,10 @@
         <v>69</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>6</v>
@@ -18743,10 +18804,10 @@
         <v>72</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>8</v>
@@ -18766,10 +18827,10 @@
         <v>75</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>9</v>
@@ -18803,10 +18864,10 @@
         <v>81</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>8</v>
@@ -18826,10 +18887,10 @@
         <v>85</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>10</v>
@@ -18849,10 +18910,10 @@
         <v>88</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>9</v>
@@ -18872,10 +18933,10 @@
         <v>91</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>10</v>
@@ -18895,10 +18956,10 @@
         <v>94</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>8</v>
@@ -18923,7 +18984,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H38" s="1" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="I38" s="1" t="n">
         <f aca="false">COUNTIF(I2:I37,"&gt;0")</f>

--- a/inasistencias-6A-sistDeCtrolVirtual/Alumnos-6A-SistDeCtrolVirtual.xlsx
+++ b/inasistencias-6A-sistDeCtrolVirtual/Alumnos-6A-SistDeCtrolVirtual.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2194" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2200" uniqueCount="680">
   <si>
     <t xml:space="preserve">total</t>
   </si>
@@ -459,6 +459,9 @@
   </si>
   <si>
     <t xml:space="preserve">se subio el 30/9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ausente</t>
   </si>
   <si>
     <t xml:space="preserve">se subio el 08/4</t>
@@ -2229,7 +2232,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2258,10 +2261,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2275,14 +2274,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2898,10 +2889,10 @@
       <c r="AX2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="AY2" s="7" t="n">
+      <c r="AY2" s="4" t="n">
         <v>45993</v>
       </c>
-      <c r="AZ2" s="7" t="n">
+      <c r="AZ2" s="4" t="n">
         <v>46000</v>
       </c>
       <c r="BA2" s="3" t="s">
@@ -2911,7 +2902,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
@@ -2958,7 +2949,7 @@
         <f aca="false">M3+N3/2+O3/4</f>
         <v>5</v>
       </c>
-      <c r="Q3" s="8" t="n">
+      <c r="Q3" s="7" t="n">
         <f aca="false">ROUND(P3*10/$S$2,0)</f>
         <v>8</v>
       </c>
@@ -2971,13 +2962,13 @@
       <c r="X3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Y3" s="9" t="n">
+      <c r="Y3" s="8" t="n">
         <v>0.5625</v>
       </c>
       <c r="Z3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AA3" s="9" t="n">
+      <c r="AA3" s="8" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="AB3" s="1" t="s">
@@ -2986,7 +2977,7 @@
       <c r="AD3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AE3" s="9" t="n">
+      <c r="AE3" s="8" t="n">
         <v>0.570833333333333</v>
       </c>
       <c r="AF3" s="1" t="s">
@@ -3001,7 +2992,7 @@
       <c r="AK3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AL3" s="9" t="n">
+      <c r="AL3" s="8" t="n">
         <v>0.541666666666667</v>
       </c>
       <c r="AM3" s="3" t="s">
@@ -3010,13 +3001,13 @@
       <c r="AO3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AP3" s="9" t="n">
+      <c r="AP3" s="8" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="AQ3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AR3" s="10" t="n">
+      <c r="AR3" s="9" t="n">
         <v>0.5625</v>
       </c>
       <c r="AS3" s="2" t="s">
@@ -3034,7 +3025,7 @@
         <f aca="false">COUNTIF(T3:AO3,"T")</f>
         <v>4</v>
       </c>
-      <c r="AX3" s="8" t="n">
+      <c r="AX3" s="7" t="n">
         <f aca="false">ROUND((AU3+AV3/2+AW3/4)*10/12,0)</f>
         <v>5</v>
       </c>
@@ -3046,7 +3037,7 @@
       <c r="B4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -3086,7 +3077,7 @@
         <f aca="false">M4+N4/2+O4/4</f>
         <v>4</v>
       </c>
-      <c r="Q4" s="8" t="n">
+      <c r="Q4" s="7" t="n">
         <f aca="false">ROUND(P4*10/$S$2,0)</f>
         <v>7</v>
       </c>
@@ -3144,18 +3135,18 @@
         <f aca="false">COUNTIF(T4:AS4,"T")</f>
         <v>0</v>
       </c>
-      <c r="AX4" s="8" t="n">
+      <c r="AX4" s="7" t="n">
         <f aca="false">ROUND((AU4+AV4/2+AW4/4)*10/12,0)</f>
         <v>10</v>
       </c>
-      <c r="AY4" s="12" t="s">
+      <c r="AY4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AZ4" s="12" t="s">
+      <c r="AZ4" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
@@ -3202,7 +3193,7 @@
         <f aca="false">M5+N5/2+O5/4</f>
         <v>5</v>
       </c>
-      <c r="Q5" s="8" t="n">
+      <c r="Q5" s="7" t="n">
         <f aca="false">ROUND(P5*10/$S$2,0)</f>
         <v>8</v>
       </c>
@@ -3212,13 +3203,13 @@
       <c r="V5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="W5" s="9" t="n">
+      <c r="W5" s="8" t="n">
         <v>0.597222222222222</v>
       </c>
       <c r="X5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Y5" s="9" t="n">
+      <c r="Y5" s="8" t="n">
         <v>0.5625</v>
       </c>
       <c r="Z5" s="1" t="s">
@@ -3266,12 +3257,12 @@
         <f aca="false">COUNTIF(T5:AO5,"T")</f>
         <v>2</v>
       </c>
-      <c r="AX5" s="8" t="n">
+      <c r="AX5" s="7" t="n">
         <f aca="false">ROUND((AU5+AV5/2+AW5/4)*10/12,0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
@@ -3318,18 +3309,18 @@
         <f aca="false">M6+N6/2+O6/4</f>
         <v>2</v>
       </c>
-      <c r="Q6" s="8" t="n">
+      <c r="Q6" s="7" t="n">
         <f aca="false">ROUND(P6*10/$S$2,0)</f>
         <v>3</v>
       </c>
       <c r="T6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="U6" s="9"/>
+      <c r="U6" s="8"/>
       <c r="V6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W6" s="9" t="n">
+      <c r="W6" s="8" t="n">
         <v>0.548611111111111</v>
       </c>
       <c r="X6" s="1" t="s">
@@ -3341,13 +3332,13 @@
       <c r="AB6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AC6" s="9" t="n">
+      <c r="AC6" s="8" t="n">
         <v>0.597222222222222</v>
       </c>
       <c r="AD6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AE6" s="9" t="n">
+      <c r="AE6" s="8" t="n">
         <v>0.570833333333333</v>
       </c>
       <c r="AF6" s="1" t="s">
@@ -3356,7 +3347,7 @@
       <c r="AG6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AH6" s="9" t="n">
+      <c r="AH6" s="8" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="AI6" s="3" t="s">
@@ -3374,7 +3365,7 @@
       <c r="AQ6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AR6" s="10" t="n">
+      <c r="AR6" s="9" t="n">
         <v>0.5625</v>
       </c>
       <c r="AS6" s="2" t="s">
@@ -3392,19 +3383,19 @@
         <f aca="false">COUNTIF(T6:AO6,"T")</f>
         <v>3</v>
       </c>
-      <c r="AX6" s="8" t="n">
+      <c r="AX6" s="7" t="n">
         <f aca="false">ROUND((AU6+AV6/2+AW6/4)*10/12,0)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="10" t="s">
         <v>32</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -3444,7 +3435,7 @@
         <f aca="false">M7+N7/2+O7/4</f>
         <v>5</v>
       </c>
-      <c r="Q7" s="8" t="n">
+      <c r="Q7" s="7" t="n">
         <f aca="false">ROUND(P7*10/$S$2,0)</f>
         <v>8</v>
       </c>
@@ -3481,7 +3472,7 @@
       <c r="AM7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="AN7" s="9" t="n">
+      <c r="AN7" s="8" t="n">
         <v>0.576388888888889</v>
       </c>
       <c r="AO7" s="3" t="s">
@@ -3505,9 +3496,15 @@
         <f aca="false">COUNTIF(T7:AS7,"T")</f>
         <v>1</v>
       </c>
-      <c r="AX7" s="8" t="n">
+      <c r="AX7" s="7" t="n">
         <f aca="false">ROUND((AU7+AV7/2+AW7/4)*10/12,0)</f>
         <v>10</v>
+      </c>
+      <c r="AY7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AZ7" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3517,7 +3514,7 @@
       <c r="B8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="10" t="s">
         <v>35</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -3557,7 +3554,7 @@
         <f aca="false">M8+N8/2+O8/4</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="8" t="n">
+      <c r="Q8" s="7" t="n">
         <f aca="false">ROUND(P8*10/$S$2,0)</f>
         <v>0</v>
       </c>
@@ -3570,13 +3567,13 @@
       <c r="X8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Y8" s="9" t="n">
+      <c r="Y8" s="8" t="n">
         <v>0.5625</v>
       </c>
       <c r="Z8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AA8" s="9" t="n">
+      <c r="AA8" s="8" t="n">
         <v>0.583333333333333</v>
       </c>
       <c r="AB8" s="1" t="s">
@@ -3621,18 +3618,18 @@
         <f aca="false">COUNTIF(T8:AS8,"T")</f>
         <v>2</v>
       </c>
-      <c r="AX8" s="8" t="n">
+      <c r="AX8" s="7" t="n">
         <f aca="false">ROUND((AU8+AV8/2+AW8/4)*10/12,0)</f>
         <v>3</v>
       </c>
-      <c r="AY8" s="12" t="s">
+      <c r="AY8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AZ8" s="12" t="s">
+      <c r="AZ8" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
@@ -3679,7 +3676,7 @@
         <f aca="false">M9+N9/2+O9/4</f>
         <v>4</v>
       </c>
-      <c r="Q9" s="8" t="n">
+      <c r="Q9" s="7" t="n">
         <f aca="false">ROUND(P9*10/$S$2,0)</f>
         <v>7</v>
       </c>
@@ -3725,7 +3722,7 @@
       <c r="AS9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="AT9" s="9" t="n">
+      <c r="AT9" s="8" t="n">
         <v>0.604166666666667</v>
       </c>
       <c r="AU9" s="3" t="n">
@@ -3740,12 +3737,12 @@
         <f aca="false">COUNTIF(T9:AO9,"T")</f>
         <v>0</v>
       </c>
-      <c r="AX9" s="8" t="n">
+      <c r="AX9" s="7" t="n">
         <f aca="false">ROUND((AU9+AV9/2+AW9/4)*10/12,0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
@@ -3764,7 +3761,7 @@
       <c r="F10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G10" s="8" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="H10" s="1" t="s">
@@ -3795,22 +3792,22 @@
         <f aca="false">M10+N10/2+O10/4</f>
         <v>4.5</v>
       </c>
-      <c r="Q10" s="8" t="n">
+      <c r="Q10" s="7" t="n">
         <f aca="false">ROUND(P10*10/$S$2,0)</f>
         <v>8</v>
       </c>
       <c r="T10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="U10" s="9"/>
+      <c r="U10" s="8"/>
       <c r="V10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="W10" s="9"/>
+      <c r="W10" s="8"/>
       <c r="X10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Y10" s="9" t="n">
+      <c r="Y10" s="8" t="n">
         <v>0.5625</v>
       </c>
       <c r="Z10" s="1" t="s">
@@ -3822,7 +3819,7 @@
       <c r="AD10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AE10" s="9" t="n">
+      <c r="AE10" s="8" t="n">
         <v>0.55</v>
       </c>
       <c r="AF10" s="1" t="s">
@@ -3831,13 +3828,13 @@
       <c r="AG10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AH10" s="9" t="n">
+      <c r="AH10" s="8" t="n">
         <v>0.5625</v>
       </c>
       <c r="AI10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AJ10" s="9" t="n">
+      <c r="AJ10" s="8" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="AK10" s="3" t="s">
@@ -3867,12 +3864,12 @@
         <f aca="false">COUNTIF(T10:AO10,"T")</f>
         <v>5</v>
       </c>
-      <c r="AX10" s="8" t="n">
+      <c r="AX10" s="7" t="n">
         <f aca="false">ROUND((AU10+AV10/2+AW10/4)*10/12,0)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
@@ -3919,7 +3916,7 @@
         <f aca="false">M11+N11/2+O11/4</f>
         <v>6</v>
       </c>
-      <c r="Q11" s="8" t="n">
+      <c r="Q11" s="7" t="n">
         <f aca="false">ROUND(P11*10/$S$2,0)</f>
         <v>10</v>
       </c>
@@ -3977,19 +3974,19 @@
         <f aca="false">COUNTIF(T11:AO11,"T")</f>
         <v>0</v>
       </c>
-      <c r="AX11" s="8" t="n">
+      <c r="AX11" s="7" t="n">
         <f aca="false">ROUND((AU11+AV11/2+AW11/4)*10/12,0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -4029,7 +4026,7 @@
         <f aca="false">M12+N12/2+O12/4</f>
         <v>4</v>
       </c>
-      <c r="Q12" s="8" t="n">
+      <c r="Q12" s="7" t="n">
         <f aca="false">ROUND(P12*10/$S$2,0)</f>
         <v>7</v>
       </c>
@@ -4087,12 +4084,12 @@
         <f aca="false">COUNTIF(T12:AS12,"T")</f>
         <v>0</v>
       </c>
-      <c r="AX12" s="8" t="n">
+      <c r="AX12" s="7" t="n">
         <f aca="false">ROUND((AU12+AV12/2+AW12/4)*10/12,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
@@ -4123,7 +4120,7 @@
       <c r="K13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L13" s="9" t="n">
+      <c r="L13" s="8" t="n">
         <v>0.614583333333333</v>
       </c>
       <c r="M13" s="1" t="n">
@@ -4142,12 +4139,12 @@
         <f aca="false">M13+N13/2+O13/4</f>
         <v>4.25</v>
       </c>
-      <c r="Q13" s="8" t="n">
+      <c r="Q13" s="7" t="n">
         <f aca="false">ROUND(P13*10/$S$2,0)</f>
         <v>7</v>
       </c>
-      <c r="R13" s="9"/>
-      <c r="S13" s="9"/>
+      <c r="R13" s="8"/>
+      <c r="S13" s="8"/>
       <c r="T13" s="1" t="s">
         <v>18</v>
       </c>
@@ -4175,7 +4172,7 @@
       <c r="AI13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AJ13" s="9" t="n">
+      <c r="AJ13" s="8" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="AK13" s="3" t="s">
@@ -4205,12 +4202,12 @@
         <f aca="false">COUNTIF(T13:AO13,"T")</f>
         <v>1</v>
       </c>
-      <c r="AX13" s="8" t="n">
+      <c r="AX13" s="7" t="n">
         <f aca="false">ROUND((AU13+AV13/2+AW13/4)*10/12,0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
@@ -4229,7 +4226,7 @@
       <c r="F14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="9" t="n">
+      <c r="G14" s="8" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="H14" s="1" t="s">
@@ -4244,7 +4241,7 @@
       <c r="K14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L14" s="9" t="n">
+      <c r="L14" s="8" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="M14" s="1" t="n">
@@ -4263,19 +4260,19 @@
         <f aca="false">M14+N14/2+O14/4</f>
         <v>4</v>
       </c>
-      <c r="Q14" s="8" t="n">
+      <c r="Q14" s="7" t="n">
         <f aca="false">ROUND(P14*10/$S$2,0)</f>
         <v>7</v>
       </c>
-      <c r="R14" s="9"/>
-      <c r="S14" s="9"/>
+      <c r="R14" s="8"/>
+      <c r="S14" s="8"/>
       <c r="T14" s="1" t="s">
         <v>19</v>
       </c>
       <c r="V14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="W14" s="9" t="n">
+      <c r="W14" s="8" t="n">
         <v>0.5625</v>
       </c>
       <c r="X14" s="1" t="s">
@@ -4284,7 +4281,7 @@
       <c r="Z14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AA14" s="9" t="n">
+      <c r="AA14" s="8" t="n">
         <v>0.569444444444444</v>
       </c>
       <c r="AB14" s="1" t="s">
@@ -4299,7 +4296,7 @@
       <c r="AG14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AH14" s="9" t="n">
+      <c r="AH14" s="8" t="n">
         <v>0.548611111111111</v>
       </c>
       <c r="AI14" s="3" t="s">
@@ -4308,25 +4305,25 @@
       <c r="AK14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AL14" s="9" t="n">
+      <c r="AL14" s="8" t="n">
         <v>0.583333333333333</v>
       </c>
       <c r="AM14" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="AN14" s="9" t="n">
+      <c r="AN14" s="8" t="n">
         <v>0.576388888888889</v>
       </c>
       <c r="AO14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AP14" s="9" t="n">
+      <c r="AP14" s="8" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="AQ14" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AR14" s="10" t="n">
+      <c r="AR14" s="9" t="n">
         <v>0.597222222222222</v>
       </c>
       <c r="AS14" s="2" t="s">
@@ -4344,12 +4341,12 @@
         <f aca="false">COUNTIF(T14:AO14,"T")</f>
         <v>5</v>
       </c>
-      <c r="AX14" s="8" t="n">
+      <c r="AX14" s="7" t="n">
         <f aca="false">ROUND((AU14+AV14/2+AW14/4)*10/12,0)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
@@ -4368,7 +4365,7 @@
       <c r="F15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="14" t="s">
+      <c r="H15" s="11" t="s">
         <v>18</v>
       </c>
       <c r="I15" s="1" t="s">
@@ -4396,11 +4393,11 @@
         <f aca="false">M15+N15/2+O15/4</f>
         <v>6</v>
       </c>
-      <c r="Q15" s="15" t="n">
+      <c r="Q15" s="12" t="n">
         <f aca="false">ROUND(P15*10/$S$2,0)</f>
         <v>10</v>
       </c>
-      <c r="R15" s="9" t="s">
+      <c r="R15" s="8" t="s">
         <v>58</v>
       </c>
       <c r="T15" s="1" t="s">
@@ -4409,13 +4406,13 @@
       <c r="V15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="W15" s="9" t="n">
+      <c r="W15" s="8" t="n">
         <v>0.597222222222222</v>
       </c>
       <c r="X15" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Y15" s="9" t="n">
+      <c r="Y15" s="8" t="n">
         <v>0.541666666666667</v>
       </c>
       <c r="Z15" s="1" t="s">
@@ -4463,12 +4460,12 @@
         <f aca="false">COUNTIF(T15:AO15,"T")</f>
         <v>1</v>
       </c>
-      <c r="AX15" s="8" t="n">
+      <c r="AX15" s="7" t="n">
         <f aca="false">ROUND((AU15+AV15/2+AW15/4)*10/12,0)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
@@ -4515,7 +4512,7 @@
         <f aca="false">M16+N16/2+O16/4</f>
         <v>5</v>
       </c>
-      <c r="Q16" s="8" t="n">
+      <c r="Q16" s="7" t="n">
         <f aca="false">ROUND(P16*10/$S$2,0)</f>
         <v>8</v>
       </c>
@@ -4573,19 +4570,19 @@
         <f aca="false">COUNTIF(T16:AO16,"T")</f>
         <v>0</v>
       </c>
-      <c r="AX16" s="8" t="n">
+      <c r="AX16" s="7" t="n">
         <f aca="false">ROUND((AU16+AV16/2+AW16/4)*10/12,0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="3" t="s">
         <v>63</v>
       </c>
       <c r="D17" s="3" t="s">
@@ -4625,7 +4622,7 @@
         <f aca="false">M17+N17/2+O17/4</f>
         <v>3</v>
       </c>
-      <c r="Q17" s="8" t="n">
+      <c r="Q17" s="7" t="n">
         <f aca="false">ROUND(P17*10/$S$2,0)</f>
         <v>5</v>
       </c>
@@ -4665,7 +4662,7 @@
       <c r="AO17" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AP17" s="9" t="n">
+      <c r="AP17" s="8" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="AQ17" s="2" t="s">
@@ -4686,7 +4683,7 @@
         <f aca="false">COUNTIF(T17:AS17,"T")</f>
         <v>1</v>
       </c>
-      <c r="AX17" s="8" t="n">
+      <c r="AX17" s="7" t="n">
         <f aca="false">ROUND((AU17+AV17/2+AW17/4)*10/12,0)</f>
         <v>8</v>
       </c>
@@ -4698,7 +4695,7 @@
       <c r="B18" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="10" t="s">
         <v>66</v>
       </c>
       <c r="D18" s="3" t="s">
@@ -4738,7 +4735,7 @@
         <f aca="false">M18+N18/2+O18/4</f>
         <v>5</v>
       </c>
-      <c r="Q18" s="8" t="n">
+      <c r="Q18" s="7" t="n">
         <f aca="false">ROUND(P18*10/$S$2,0)</f>
         <v>8</v>
       </c>
@@ -4748,13 +4745,13 @@
       <c r="V18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W18" s="9" t="n">
+      <c r="W18" s="8" t="n">
         <v>0.548611111111111</v>
       </c>
       <c r="X18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Y18" s="9" t="n">
+      <c r="Y18" s="8" t="n">
         <v>0.541666666666667</v>
       </c>
       <c r="Z18" s="1" t="s">
@@ -4766,7 +4763,7 @@
       <c r="AD18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AE18" s="9" t="n">
+      <c r="AE18" s="8" t="n">
         <v>0.569444444444444</v>
       </c>
       <c r="AF18" s="1" t="s">
@@ -4787,7 +4784,7 @@
       <c r="AO18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AP18" s="9" t="n">
+      <c r="AP18" s="8" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="AQ18" s="2" t="s">
@@ -4796,7 +4793,7 @@
       <c r="AS18" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AT18" s="9" t="n">
+      <c r="AT18" s="8" t="n">
         <v>0.576388888888889</v>
       </c>
       <c r="AU18" s="3" t="n">
@@ -4811,18 +4808,18 @@
         <f aca="false">COUNTIF(T18:AS18,"T")</f>
         <v>3</v>
       </c>
-      <c r="AX18" s="8" t="n">
+      <c r="AX18" s="7" t="n">
         <f aca="false">ROUND((AU18+AV18/2+AW18/4)*10/12,0)</f>
         <v>7</v>
       </c>
-      <c r="AY18" s="12" t="s">
+      <c r="AY18" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AZ18" s="12" t="s">
+      <c r="AZ18" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
@@ -4869,14 +4866,14 @@
         <f aca="false">M19+N19/2+O19/4</f>
         <v>3</v>
       </c>
-      <c r="Q19" s="8" t="n">
+      <c r="Q19" s="7" t="n">
         <f aca="false">ROUND(P19*10/$S$2,0)</f>
         <v>5</v>
       </c>
       <c r="T19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U19" s="9" t="n">
+      <c r="U19" s="8" t="n">
         <v>0.611111111111111</v>
       </c>
       <c r="V19" s="1" t="s">
@@ -4888,7 +4885,7 @@
       <c r="Z19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AA19" s="9" t="n">
+      <c r="AA19" s="8" t="n">
         <v>0.569444444444444</v>
       </c>
       <c r="AB19" s="1" t="s">
@@ -4915,7 +4912,7 @@
       <c r="AO19" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AP19" s="9" t="n">
+      <c r="AP19" s="8" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="AQ19" s="2" t="s">
@@ -4936,12 +4933,12 @@
         <f aca="false">COUNTIF(T19:AO19,"T")</f>
         <v>3</v>
       </c>
-      <c r="AX19" s="8" t="n">
+      <c r="AX19" s="7" t="n">
         <f aca="false">ROUND((AU19+AV19/2+AW19/4)*10/12,0)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
@@ -4972,7 +4969,7 @@
       <c r="K20" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L20" s="9" t="n">
+      <c r="L20" s="8" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="M20" s="1" t="n">
@@ -4991,19 +4988,19 @@
         <f aca="false">M20+N20/2+O20/4</f>
         <v>3.5</v>
       </c>
-      <c r="Q20" s="8" t="n">
+      <c r="Q20" s="7" t="n">
         <f aca="false">ROUND(P20*10/$S$2,0)</f>
         <v>6</v>
       </c>
-      <c r="R20" s="9"/>
-      <c r="S20" s="9"/>
+      <c r="R20" s="8"/>
+      <c r="S20" s="8"/>
       <c r="T20" s="1" t="s">
         <v>18</v>
       </c>
       <c r="V20" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="W20" s="9" t="n">
+      <c r="W20" s="8" t="n">
         <v>0.5625</v>
       </c>
       <c r="X20" s="1" t="s">
@@ -5024,7 +5021,7 @@
       <c r="AG20" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AH20" s="9" t="n">
+      <c r="AH20" s="8" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="AI20" s="3" t="s">
@@ -5057,12 +5054,12 @@
         <f aca="false">COUNTIF(T20:AO20,"T")</f>
         <v>2</v>
       </c>
-      <c r="AX20" s="8" t="n">
+      <c r="AX20" s="7" t="n">
         <f aca="false">ROUND((AU20+AV20/2+AW20/4)*10/12,0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
@@ -5109,7 +5106,7 @@
         <f aca="false">M21+N21/2+O21/4</f>
         <v>6</v>
       </c>
-      <c r="Q21" s="8" t="n">
+      <c r="Q21" s="7" t="n">
         <f aca="false">ROUND(P21*10/$S$2,0)</f>
         <v>10</v>
       </c>
@@ -5119,7 +5116,7 @@
       <c r="V21" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="W21" s="9"/>
+      <c r="W21" s="8"/>
       <c r="X21" s="1" t="s">
         <v>18</v>
       </c>
@@ -5168,7 +5165,7 @@
         <f aca="false">COUNTIF(T21:AO21,"T")</f>
         <v>0</v>
       </c>
-      <c r="AX21" s="8" t="n">
+      <c r="AX21" s="7" t="n">
         <f aca="false">ROUND((AU21+AV21/2+AW21/4)*10/12,0)</f>
         <v>10</v>
       </c>
@@ -5180,7 +5177,7 @@
       <c r="B22" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="10" t="s">
         <v>78</v>
       </c>
       <c r="D22" s="3" t="s">
@@ -5204,7 +5201,7 @@
       <c r="K22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L22" s="9" t="n">
+      <c r="L22" s="8" t="n">
         <v>0.555555555555556</v>
       </c>
       <c r="M22" s="1" t="n">
@@ -5223,25 +5220,25 @@
         <f aca="false">M22+N22/2+O22/4</f>
         <v>3.5</v>
       </c>
-      <c r="Q22" s="8" t="n">
+      <c r="Q22" s="7" t="n">
         <f aca="false">ROUND(P22*10/$S$2,0)</f>
         <v>6</v>
       </c>
-      <c r="R22" s="9"/>
-      <c r="S22" s="9"/>
+      <c r="R22" s="8"/>
+      <c r="S22" s="8"/>
       <c r="T22" s="1" t="s">
         <v>18</v>
       </c>
       <c r="V22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="W22" s="9" t="n">
+      <c r="W22" s="8" t="n">
         <v>0.5625</v>
       </c>
       <c r="X22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Y22" s="9" t="n">
+      <c r="Y22" s="8" t="n">
         <v>0.5625</v>
       </c>
       <c r="Z22" s="1" t="s">
@@ -5265,7 +5262,7 @@
       <c r="AK22" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AL22" s="9" t="n">
+      <c r="AL22" s="8" t="n">
         <v>0.583333333333333</v>
       </c>
       <c r="AM22" s="3" t="s">
@@ -5292,18 +5289,18 @@
         <f aca="false">COUNTIF(T22:AO22,"T")</f>
         <v>4</v>
       </c>
-      <c r="AX22" s="8" t="n">
+      <c r="AX22" s="7" t="n">
         <f aca="false">ROUND((AU22+AV22/2+AW22/4)*10/12,0)</f>
         <v>3</v>
       </c>
-      <c r="AY22" s="12" t="s">
+      <c r="AY22" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AZ22" s="12" t="s">
+      <c r="AZ22" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
@@ -5325,7 +5322,7 @@
       <c r="H23" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I23" s="14" t="s">
+      <c r="I23" s="11" t="s">
         <v>18</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -5350,7 +5347,7 @@
         <f aca="false">M23+N23/2+O23/4</f>
         <v>5</v>
       </c>
-      <c r="Q23" s="15" t="n">
+      <c r="Q23" s="12" t="n">
         <f aca="false">ROUND(P23*10/$S$2,0)</f>
         <v>8</v>
       </c>
@@ -5399,7 +5396,7 @@
       <c r="AS23" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AT23" s="9" t="n">
+      <c r="AT23" s="8" t="n">
         <v>0.552083333333333</v>
       </c>
       <c r="AU23" s="3" t="n">
@@ -5414,12 +5411,12 @@
         <f aca="false">COUNTIF(T23:AO23,"T")</f>
         <v>0</v>
       </c>
-      <c r="AX23" s="8" t="n">
+      <c r="AX23" s="7" t="n">
         <f aca="false">ROUND((AU23+AV23/2+AW23/4)*10/12,0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
@@ -5466,7 +5463,7 @@
         <f aca="false">M24+N24/2+O24/4</f>
         <v>5</v>
       </c>
-      <c r="Q24" s="8" t="n">
+      <c r="Q24" s="7" t="n">
         <f aca="false">ROUND(P24*10/$S$2,0)</f>
         <v>8</v>
       </c>
@@ -5524,12 +5521,12 @@
         <f aca="false">COUNTIF(T24:AO24,"T")</f>
         <v>0</v>
       </c>
-      <c r="AX24" s="8" t="n">
+      <c r="AX24" s="7" t="n">
         <f aca="false">ROUND((AU24+AV24/2+AW24/4)*10/12,0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
@@ -5576,7 +5573,7 @@
         <f aca="false">M25+N25/2+O25/4</f>
         <v>6</v>
       </c>
-      <c r="Q25" s="8" t="n">
+      <c r="Q25" s="7" t="n">
         <f aca="false">ROUND(P25*10/$S$2,0)</f>
         <v>10</v>
       </c>
@@ -5634,19 +5631,19 @@
         <f aca="false">COUNTIF(T25:AO25,"T")</f>
         <v>0</v>
       </c>
-      <c r="AX25" s="8" t="n">
+      <c r="AX25" s="7" t="n">
         <f aca="false">ROUND((AU25+AV25/2+AW25/4)*10/12,0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="26" s="2" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="3" t="s">
         <v>91</v>
       </c>
       <c r="D26" s="6" t="s">
@@ -5686,7 +5683,7 @@
         <f aca="false">M26+N26/2+O26/4</f>
         <v>5</v>
       </c>
-      <c r="Q26" s="16" t="n">
+      <c r="Q26" s="13" t="n">
         <f aca="false">ROUND(P26*10/$S$2,0)</f>
         <v>8</v>
       </c>
@@ -5702,7 +5699,7 @@
       <c r="Z26" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AA26" s="10" t="n">
+      <c r="AA26" s="9" t="n">
         <v>0.569444444444444</v>
       </c>
       <c r="AB26" s="2" t="s">
@@ -5748,12 +5745,12 @@
         <f aca="false">COUNTIF(T26:AO26,"T")</f>
         <v>1</v>
       </c>
-      <c r="AX26" s="16" t="n">
+      <c r="AX26" s="13" t="n">
         <f aca="false">ROUND((AU26+AV26/2+AW26/4)*10/12,0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
@@ -5800,7 +5797,7 @@
         <f aca="false">M27+N27/2+O27/4</f>
         <v>6</v>
       </c>
-      <c r="Q27" s="8" t="n">
+      <c r="Q27" s="7" t="n">
         <f aca="false">ROUND(P27*10/$S$2,0)</f>
         <v>10</v>
       </c>
@@ -5822,7 +5819,7 @@
       <c r="AD27" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AE27" s="9" t="n">
+      <c r="AE27" s="8" t="n">
         <v>0.572916666666667</v>
       </c>
       <c r="AF27" s="1" t="s">
@@ -5831,7 +5828,7 @@
       <c r="AG27" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AH27" s="9" t="n">
+      <c r="AH27" s="8" t="n">
         <v>0.604166666666667</v>
       </c>
       <c r="AI27" s="3" t="s">
@@ -5864,7 +5861,7 @@
         <f aca="false">COUNTIF(T27:AO27,"T")</f>
         <v>2</v>
       </c>
-      <c r="AX27" s="8" t="n">
+      <c r="AX27" s="7" t="n">
         <f aca="false">ROUND((AU27+AV27/2+AW27/4)*10/12,0)</f>
         <v>8</v>
       </c>
@@ -5876,7 +5873,7 @@
       <c r="B28" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="10" t="s">
         <v>97</v>
       </c>
       <c r="D28" s="3" t="s">
@@ -5918,7 +5915,7 @@
         <f aca="false">M28+N28/2+O28/4</f>
         <v>3</v>
       </c>
-      <c r="Q28" s="8" t="n">
+      <c r="Q28" s="7" t="n">
         <f aca="false">ROUND(P28*10/$S$2,0)</f>
         <v>5</v>
       </c>
@@ -5931,13 +5928,13 @@
       <c r="V28" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="W28" s="9" t="n">
+      <c r="W28" s="8" t="n">
         <v>0.576388888888889</v>
       </c>
       <c r="X28" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="Y28" s="9" t="n">
+      <c r="Y28" s="8" t="n">
         <v>0.583333333333333</v>
       </c>
       <c r="Z28" s="3" t="s">
@@ -5946,13 +5943,13 @@
       <c r="AB28" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AC28" s="9" t="n">
+      <c r="AC28" s="8" t="n">
         <v>0.59375</v>
       </c>
       <c r="AD28" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AE28" s="9" t="n">
+      <c r="AE28" s="8" t="n">
         <v>0.572916666666667</v>
       </c>
       <c r="AF28" s="3" t="s">
@@ -5961,19 +5958,19 @@
       <c r="AG28" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AH28" s="9" t="n">
+      <c r="AH28" s="8" t="n">
         <v>0.583333333333333</v>
       </c>
       <c r="AI28" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AJ28" s="9" t="n">
+      <c r="AJ28" s="8" t="n">
         <v>0.597222222222222</v>
       </c>
       <c r="AK28" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AL28" s="9" t="n">
+      <c r="AL28" s="8" t="n">
         <v>0.583333333333333</v>
       </c>
       <c r="AM28" s="3" t="s">
@@ -6001,14 +5998,14 @@
         <f aca="false">COUNTIF(T28:AS28,"T")</f>
         <v>8</v>
       </c>
-      <c r="AX28" s="8" t="n">
+      <c r="AX28" s="7" t="n">
         <f aca="false">ROUND((AU28+AV28/2+AW28/4)*10/12,0)</f>
         <v>3</v>
       </c>
-      <c r="AY28" s="12" t="s">
+      <c r="AY28" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AZ28" s="12" t="s">
+      <c r="AZ28" s="3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6312,22 +6309,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>116</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6341,10 +6338,10 @@
         <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>9</v>
@@ -6378,10 +6375,10 @@
         <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>10</v>
@@ -6403,10 +6400,10 @@
         <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>6</v>
@@ -6437,10 +6434,10 @@
         <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>10</v>
@@ -6462,10 +6459,10 @@
         <v>32</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>9</v>
@@ -6476,10 +6473,10 @@
         <v>32</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>9</v>
@@ -6490,10 +6487,10 @@
         <v>32</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>7</v>
@@ -6504,10 +6501,10 @@
         <v>32</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>5</v>
@@ -6518,10 +6515,10 @@
         <v>32</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>4</v>
@@ -6552,10 +6549,10 @@
         <v>38</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -6589,10 +6586,10 @@
         <v>44</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>8</v>
@@ -6626,10 +6623,10 @@
         <v>50</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>9</v>
@@ -6649,10 +6646,10 @@
         <v>53</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>8</v>
@@ -6672,10 +6669,10 @@
         <v>56</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>8</v>
@@ -6697,10 +6694,10 @@
         <v>56</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>7</v>
@@ -6717,10 +6714,10 @@
         <v>60</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>5</v>
@@ -6754,10 +6751,10 @@
         <v>66</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>9</v>
@@ -6777,10 +6774,10 @@
         <v>69</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -6800,10 +6797,10 @@
         <v>72</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>10</v>
@@ -6823,10 +6820,10 @@
         <v>75</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>9</v>
@@ -6860,10 +6857,10 @@
         <v>81</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>8</v>
@@ -6883,10 +6880,10 @@
         <v>85</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>10</v>
@@ -6906,10 +6903,10 @@
         <v>88</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>10</v>
@@ -6929,10 +6926,10 @@
         <v>91</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>10</v>
@@ -6954,10 +6951,10 @@
         <v>91</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>10</v>
@@ -6968,10 +6965,10 @@
         <v>91</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>10</v>
@@ -6982,10 +6979,10 @@
         <v>91</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>10</v>
@@ -6996,10 +6993,10 @@
         <v>91</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>10</v>
@@ -7010,10 +7007,10 @@
         <v>91</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>10</v>
@@ -7024,10 +7021,10 @@
         <v>91</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>10</v>
@@ -7038,10 +7035,10 @@
         <v>91</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F39" s="1" t="n">
         <v>10</v>
@@ -7052,10 +7049,10 @@
         <v>91</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F40" s="1" t="n">
         <v>10</v>
@@ -7066,10 +7063,10 @@
         <v>91</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F41" s="1" t="n">
         <v>10</v>
@@ -7080,10 +7077,10 @@
         <v>91</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F42" s="1" t="n">
         <v>10</v>
@@ -7094,10 +7091,10 @@
         <v>91</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F43" s="1" t="n">
         <v>10</v>
@@ -7108,10 +7105,10 @@
         <v>91</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>9</v>
@@ -7122,10 +7119,10 @@
         <v>91</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>7</v>
@@ -7136,10 +7133,10 @@
         <v>91</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F46" s="1" t="n">
         <v>7</v>
@@ -7156,10 +7153,10 @@
         <v>94</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F47" s="1" t="n">
         <v>10</v>
@@ -7181,10 +7178,10 @@
         <v>94</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F48" s="1" t="n">
         <v>3</v>
@@ -7206,7 +7203,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H50" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="I50" s="1" t="n">
         <f aca="false">COUNTIF(I2:I49,"&gt;0")</f>
@@ -7262,22 +7259,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>116</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7291,10 +7288,10 @@
         <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>7</v>
@@ -7328,10 +7325,10 @@
         <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>9</v>
@@ -7365,10 +7362,10 @@
         <v>32</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>10</v>
@@ -7390,10 +7387,10 @@
         <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>9</v>
@@ -7404,10 +7401,10 @@
         <v>32</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>2</v>
@@ -7438,10 +7435,10 @@
         <v>38</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>10</v>
@@ -7475,10 +7472,10 @@
         <v>44</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>10</v>
@@ -7512,10 +7509,10 @@
         <v>50</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -7535,10 +7532,10 @@
         <v>53</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -7560,10 +7557,10 @@
         <v>53</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>5</v>
@@ -7580,10 +7577,10 @@
         <v>56</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>8</v>
@@ -7605,10 +7602,10 @@
         <v>56</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>7</v>
@@ -7619,10 +7616,10 @@
         <v>56</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>4</v>
@@ -7633,10 +7630,10 @@
         <v>56</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>4</v>
@@ -7653,10 +7650,10 @@
         <v>60</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>7</v>
@@ -7690,10 +7687,10 @@
         <v>66</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>10</v>
@@ -7713,10 +7710,10 @@
         <v>69</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>8</v>
@@ -7736,10 +7733,10 @@
         <v>72</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -7759,10 +7756,10 @@
         <v>75</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>10</v>
@@ -7796,10 +7793,10 @@
         <v>81</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>8</v>
@@ -7819,10 +7816,10 @@
         <v>85</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>10</v>
@@ -7842,10 +7839,10 @@
         <v>88</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>10</v>
@@ -7865,10 +7862,10 @@
         <v>91</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>10</v>
@@ -7890,10 +7887,10 @@
         <v>91</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>9</v>
@@ -7910,10 +7907,10 @@
         <v>94</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>10</v>
@@ -7935,10 +7932,10 @@
         <v>94</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>3</v>
@@ -7960,7 +7957,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H36" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="I36" s="1" t="n">
         <f aca="false">COUNTIF(I2:I35,"&gt;0")</f>
@@ -8016,19 +8013,19 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>116</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8045,7 +8042,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>7</v>
@@ -8082,7 +8079,7 @@
         <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>9</v>
@@ -8119,7 +8116,7 @@
         <v>31</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>10</v>
@@ -8142,7 +8139,7 @@
         <v>34</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>9</v>
@@ -8165,7 +8162,7 @@
         <v>37</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>10</v>
@@ -8230,7 +8227,7 @@
         <v>49</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>8</v>
@@ -8267,7 +8264,7 @@
         <v>55</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -8318,7 +8315,7 @@
         <v>65</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>9</v>
@@ -8341,7 +8338,7 @@
         <v>68</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>10</v>
@@ -8364,7 +8361,7 @@
         <v>71</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>10</v>
@@ -8387,7 +8384,7 @@
         <v>74</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>9</v>
@@ -8424,7 +8421,7 @@
         <v>80</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>9</v>
@@ -8447,7 +8444,7 @@
         <v>84</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>10</v>
@@ -8472,7 +8469,7 @@
         <v>84</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>9</v>
@@ -8492,7 +8489,7 @@
         <v>87</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>9</v>
@@ -8517,7 +8514,7 @@
         <v>87</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>9</v>
@@ -8531,7 +8528,7 @@
         <v>87</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>8</v>
@@ -8545,7 +8542,7 @@
         <v>87</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>6</v>
@@ -8559,7 +8556,7 @@
         <v>87</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>6</v>
@@ -8573,7 +8570,7 @@
         <v>87</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>4</v>
@@ -8593,7 +8590,7 @@
         <v>90</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>10</v>
@@ -8618,7 +8615,7 @@
         <v>90</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>10</v>
@@ -8632,7 +8629,7 @@
         <v>90</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>10</v>
@@ -8646,7 +8643,7 @@
         <v>90</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>10</v>
@@ -8660,7 +8657,7 @@
         <v>90</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>9</v>
@@ -8674,7 +8671,7 @@
         <v>90</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>9</v>
@@ -8688,7 +8685,7 @@
         <v>90</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>9</v>
@@ -8702,7 +8699,7 @@
         <v>90</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>9</v>
@@ -8776,19 +8773,19 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>116</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8805,7 +8802,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>10</v>
@@ -8842,7 +8839,7 @@
         <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>10</v>
@@ -8879,7 +8876,7 @@
         <v>31</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>3</v>
@@ -8904,7 +8901,7 @@
         <v>31</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>9</v>
@@ -8918,7 +8915,7 @@
         <v>31</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>10</v>
@@ -9008,7 +9005,7 @@
         <v>49</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -9045,7 +9042,7 @@
         <v>55</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>10</v>
@@ -9096,7 +9093,7 @@
         <v>65</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>6</v>
@@ -9133,7 +9130,7 @@
         <v>71</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>9</v>
@@ -9156,7 +9153,7 @@
         <v>74</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>9</v>
@@ -9193,7 +9190,7 @@
         <v>80</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>8</v>
@@ -9216,7 +9213,7 @@
         <v>84</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -9239,7 +9236,7 @@
         <v>87</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>10</v>
@@ -9264,7 +9261,7 @@
         <v>87</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>10</v>
@@ -9278,7 +9275,7 @@
         <v>87</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>9</v>
@@ -9292,7 +9289,7 @@
         <v>87</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>9</v>
@@ -9312,7 +9309,7 @@
         <v>90</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>9</v>
@@ -9337,7 +9334,7 @@
         <v>90</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>9</v>
@@ -9351,7 +9348,7 @@
         <v>90</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>10</v>
@@ -9365,7 +9362,7 @@
         <v>90</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>10</v>
@@ -9443,19 +9440,19 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>116</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9472,7 +9469,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>9</v>
@@ -9509,7 +9506,7 @@
         <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>8</v>
@@ -9546,7 +9543,7 @@
         <v>31</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>8</v>
@@ -9571,7 +9568,7 @@
         <v>31</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>8</v>
@@ -9585,7 +9582,7 @@
         <v>31</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>7</v>
@@ -9599,7 +9596,7 @@
         <v>31</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>2</v>
@@ -9689,7 +9686,7 @@
         <v>49</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>9</v>
@@ -9726,7 +9723,7 @@
         <v>55</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>9</v>
@@ -9777,7 +9774,7 @@
         <v>65</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>7</v>
@@ -9814,7 +9811,7 @@
         <v>71</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>7</v>
@@ -9837,7 +9834,7 @@
         <v>74</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>8</v>
@@ -9874,7 +9871,7 @@
         <v>80</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>8</v>
@@ -9897,7 +9894,7 @@
         <v>84</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>9</v>
@@ -9920,7 +9917,7 @@
         <v>87</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>9</v>
@@ -9945,7 +9942,7 @@
         <v>87</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>9</v>
@@ -9959,7 +9956,7 @@
         <v>87</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>9</v>
@@ -9979,7 +9976,7 @@
         <v>90</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>10</v>
@@ -10004,7 +10001,7 @@
         <v>90</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>10</v>
@@ -10018,7 +10015,7 @@
         <v>90</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>10</v>
@@ -10032,7 +10029,7 @@
         <v>90</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>9</v>
@@ -10046,7 +10043,7 @@
         <v>90</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>9</v>
@@ -10060,7 +10057,7 @@
         <v>90</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>8</v>
@@ -10074,7 +10071,7 @@
         <v>90</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>6</v>
@@ -10088,7 +10085,7 @@
         <v>90</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>6</v>
@@ -10152,35 +10149,33 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.57"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="3" min="3" style="1" width="8.57"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="12" min="4" style="1" width="9.33"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="13" style="1" width="9.56"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="14" min="14" style="1" width="8.82"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="19" min="15" style="1" width="9.56"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="20" min="20" style="1" width="7.38"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="29" min="21" style="1" width="9.56"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="31" min="30" style="1" width="9.58"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="32" min="32" style="1" width="9.58"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="33" min="33" style="1" width="9.58"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="34" min="34" style="1" width="9.33"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="35" min="35" style="1" width="9.58"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="36" min="36" style="1" width="11.17"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="37" min="37" style="1" width="9.64"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="38" min="38" style="1" width="30.76"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="39" min="39" style="1" width="15.75"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="40" min="40" style="1" width="40.67"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="41" min="41" style="1" width="9.64"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="42" min="42" style="1" width="18.97"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="43" min="43" style="1" width="10.2"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="44" min="44" style="1" width="22.9"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="45" min="45" style="1" width="9.64"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="46" min="46" style="1" width="29.77"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="47" min="47" style="1" width="9.1"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="48" min="48" style="1" width="17.9"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="49" min="49" style="1" width="9.64"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="50" min="50" style="1" width="23.39"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="54" min="51" style="1" width="9.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="58" min="58" style="0" width="13.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="4" style="1" width="9.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="9.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="8.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="15" style="1" width="9.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="7.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="21" style="1" width="9.56"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="33" min="30" style="1" width="9.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="1" width="9.33"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="9.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="11.17"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="9.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="30.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="15.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="40.67"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="41" min="41" style="1" width="9.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="1" width="18.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="43" style="1" width="10.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="22.9"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="45" min="45" style="1" width="9.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="46" style="1" width="29.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="47" style="1" width="9.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="48" style="1" width="17.9"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="49" min="49" style="1" width="9.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="50" min="50" style="1" width="23.39"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="54" min="51" style="1" width="9.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="58" min="58" style="1" width="13.37"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10396,7 +10391,7 @@
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="1" t="n">
@@ -10408,7 +10403,7 @@
       <c r="G3" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="I3" s="18" t="n">
+      <c r="I3" s="15" t="n">
         <v>7</v>
       </c>
       <c r="J3" s="4" t="n">
@@ -10433,26 +10428,26 @@
         <f aca="false">Q3+S3/2</f>
         <v>7</v>
       </c>
-      <c r="U3" s="8" t="n">
+      <c r="U3" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(M3,O3,T3,C3),0)</f>
         <v>8</v>
       </c>
-      <c r="V3" s="8" t="str">
+      <c r="V3" s="7" t="str">
         <f aca="false">IF(U3&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W3" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X3" s="8"/>
-      <c r="Y3" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z3" s="8"/>
-      <c r="AA3" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB3" s="8"/>
+      <c r="W3" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z3" s="7"/>
+      <c r="AA3" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB3" s="7"/>
       <c r="AC3" s="1" t="n">
         <v>8</v>
       </c>
@@ -10460,7 +10455,7 @@
         <f aca="false">AC3+AD3/2</f>
         <v>8</v>
       </c>
-      <c r="AF3" s="8" t="n">
+      <c r="AF3" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AE3,AA3,Y3,W3,U3),0)</f>
         <v>8</v>
       </c>
@@ -10473,7 +10468,7 @@
       <c r="AK3" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AL3" s="17" t="s">
+      <c r="AL3" s="14" t="s">
         <v>136</v>
       </c>
       <c r="AM3" s="1" t="n">
@@ -10516,11 +10511,11 @@
         <f aca="false">AY3+AZ3/2</f>
         <v>5</v>
       </c>
-      <c r="BC3" s="8" t="n">
+      <c r="BC3" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AJ3,AK3,AM3,AO3,AQ3,AS3,AU3,AW3,BA3),0)</f>
         <v>7</v>
       </c>
-      <c r="BD3" s="8" t="n">
+      <c r="BD3" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AF3,BC3),0)</f>
         <v>8</v>
       </c>
@@ -10529,16 +10524,16 @@
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="16" t="s">
         <v>23</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="F4" s="20" t="n">
+      <c r="F4" s="17" t="n">
         <v>45846</v>
       </c>
       <c r="G4" s="1" t="n">
@@ -10566,26 +10561,26 @@
         <f aca="false">Q4+S4/2</f>
         <v>1.5</v>
       </c>
-      <c r="U4" s="8" t="n">
+      <c r="U4" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(M4,O4,T4),0)</f>
         <v>1</v>
       </c>
-      <c r="V4" s="8" t="str">
+      <c r="V4" s="7" t="str">
         <f aca="false">IF(U4&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="W4" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="X4" s="8"/>
-      <c r="Y4" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="8"/>
-      <c r="AA4" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="8"/>
+      <c r="W4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="7"/>
+      <c r="AA4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="7"/>
       <c r="AC4" s="1" t="n">
         <v>7</v>
       </c>
@@ -10593,7 +10588,7 @@
         <f aca="false">AC4+AD4/2</f>
         <v>7</v>
       </c>
-      <c r="AF4" s="8" t="n">
+      <c r="AF4" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AE4,AA4,Y4,W4,U4),0)</f>
         <v>2</v>
       </c>
@@ -10618,16 +10613,16 @@
       <c r="AN4" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="AO4" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ4" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS4" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU4" s="21" t="n">
+      <c r="AO4" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" s="18" t="n">
         <v>1</v>
       </c>
       <c r="AW4" s="1" t="n">
@@ -10644,20 +10639,26 @@
       <c r="BB4" s="6" t="n">
         <v>9.25</v>
       </c>
-      <c r="BC4" s="8" t="n">
+      <c r="BC4" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AJ4,AK4,AM4,AO4,AQ4,AS4,AU4,AW4,BA4,BB4),0)</f>
         <v>4</v>
       </c>
-      <c r="BD4" s="8" t="n">
+      <c r="BD4" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AF4,BC4),0)</f>
         <v>3</v>
+      </c>
+      <c r="BE4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF4" s="1" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C5" s="1" t="n">
@@ -10691,35 +10692,35 @@
         <f aca="false">Q5+S5/2</f>
         <v>9.5</v>
       </c>
-      <c r="U5" s="8" t="n">
+      <c r="U5" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(M5,O5,T5),0)</f>
         <v>9</v>
       </c>
-      <c r="V5" s="8" t="str">
+      <c r="V5" s="7" t="str">
         <f aca="false">IF(U5&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W5" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="X5" s="8"/>
-      <c r="Y5" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z5" s="8"/>
-      <c r="AA5" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB5" s="8"/>
-      <c r="AC5" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD5" s="8"/>
+      <c r="W5" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z5" s="7"/>
+      <c r="AA5" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB5" s="7"/>
+      <c r="AC5" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD5" s="7"/>
       <c r="AE5" s="1" t="n">
         <f aca="false">AC5+AD5/2</f>
         <v>8</v>
       </c>
-      <c r="AF5" s="8" t="n">
+      <c r="AF5" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AE5,AA5,Y5,W5,U5),0)</f>
         <v>9</v>
       </c>
@@ -10733,13 +10734,13 @@
         <v>10</v>
       </c>
       <c r="AL5" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AM5" s="1" t="n">
         <v>10</v>
       </c>
       <c r="AN5" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AO5" s="1" t="n">
         <v>10</v>
@@ -10748,22 +10749,22 @@
         <v>6</v>
       </c>
       <c r="AR5" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AS5" s="1" t="n">
         <v>6</v>
       </c>
       <c r="AT5" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="AU5" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW5" s="21" t="n">
+        <v>146</v>
+      </c>
+      <c r="AU5" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW5" s="18" t="n">
         <v>3</v>
       </c>
       <c r="AX5" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AY5" s="1" t="n">
         <v>8</v>
@@ -10775,11 +10776,11 @@
       <c r="BB5" s="1" t="n">
         <v>9.5</v>
       </c>
-      <c r="BC5" s="8" t="n">
+      <c r="BC5" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AJ5,AK5,AM5,AO5,AQ5,AS5,AU5,AW5,BA5),0)</f>
         <v>7</v>
       </c>
-      <c r="BD5" s="8" t="n">
+      <c r="BD5" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AF5,BC5),0)</f>
         <v>8</v>
       </c>
@@ -10788,93 +10789,93 @@
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="14" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="F6" s="20" t="n">
+      <c r="F6" s="17" t="n">
         <v>45940</v>
       </c>
-      <c r="G6" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="H6" s="20" t="n">
+      <c r="G6" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="H6" s="17" t="n">
         <v>45848</v>
       </c>
-      <c r="I6" s="14" t="n">
+      <c r="I6" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="J6" s="20" t="n">
+      <c r="J6" s="17" t="n">
         <v>45848</v>
       </c>
-      <c r="K6" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L6" s="20" t="n">
+      <c r="K6" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" s="17" t="n">
         <v>45848</v>
       </c>
       <c r="M6" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="O6" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="P6" s="20" t="n">
+      <c r="O6" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="P6" s="17" t="n">
         <v>45848</v>
       </c>
-      <c r="Q6" s="14" t="n">
+      <c r="Q6" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="R6" s="20" t="n">
+      <c r="R6" s="17" t="n">
         <v>45848</v>
       </c>
-      <c r="S6" s="23" t="n">
+      <c r="S6" s="20" t="n">
         <v>15</v>
       </c>
       <c r="T6" s="1" t="n">
         <f aca="false">Q6+S6/2</f>
         <v>13.5</v>
       </c>
-      <c r="U6" s="8" t="n">
+      <c r="U6" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(M6,O6,T6),0)</f>
         <v>8</v>
       </c>
-      <c r="V6" s="8" t="str">
+      <c r="V6" s="7" t="str">
         <f aca="false">IF(U6&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W6" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="X6" s="20" t="n">
+      <c r="W6" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="X6" s="17" t="n">
         <v>45848</v>
       </c>
-      <c r="Y6" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z6" s="20" t="n">
+      <c r="Y6" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z6" s="17" t="n">
         <v>45848</v>
       </c>
-      <c r="AA6" s="24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB6" s="25" t="n">
+      <c r="AA6" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB6" s="22" t="n">
         <v>45848</v>
       </c>
-      <c r="AC6" s="8" t="n">
+      <c r="AC6" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="AD6" s="8"/>
+      <c r="AD6" s="7"/>
       <c r="AE6" s="1" t="n">
         <f aca="false">AC6+AD6/2</f>
         <v>3</v>
       </c>
-      <c r="AF6" s="8" t="n">
+      <c r="AF6" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AE6,AA6,Y6,W6,U6),0)</f>
         <v>7</v>
       </c>
@@ -10888,43 +10889,43 @@
         <v>7</v>
       </c>
       <c r="AL6" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM6" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AN6" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="AO6" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP6" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="AO6" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AP6" s="1" t="s">
-        <v>147</v>
-      </c>
       <c r="AQ6" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AR6" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AS6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="AT6" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AU6" s="1" t="n">
         <v>6</v>
       </c>
       <c r="AV6" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AW6" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AX6" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AY6" s="3" t="n">
         <v>4</v>
@@ -10935,11 +10936,11 @@
         <v>4</v>
       </c>
       <c r="BB6" s="3"/>
-      <c r="BC6" s="8" t="n">
+      <c r="BC6" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AJ6,AK6,AM6,AO6,AQ6,AS6,AU6,AW6,BA6),0)</f>
         <v>7</v>
       </c>
-      <c r="BD6" s="8" t="n">
+      <c r="BD6" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AF6,BC6),0)</f>
         <v>7</v>
       </c>
@@ -10948,7 +10949,7 @@
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="16" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="1" t="n">
@@ -10982,35 +10983,35 @@
         <f aca="false">Q7+S7/2</f>
         <v>9</v>
       </c>
-      <c r="U7" s="8" t="n">
+      <c r="U7" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(M7,O7,T7),0)</f>
         <v>10</v>
       </c>
-      <c r="V7" s="8" t="str">
+      <c r="V7" s="7" t="str">
         <f aca="false">IF(U7&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W7" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="X7" s="8"/>
-      <c r="Y7" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z7" s="8"/>
-      <c r="AA7" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB7" s="8"/>
-      <c r="AC7" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD7" s="8"/>
+      <c r="W7" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z7" s="7"/>
+      <c r="AA7" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB7" s="7"/>
+      <c r="AC7" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD7" s="7"/>
       <c r="AE7" s="1" t="n">
         <f aca="false">AC7+AD7/2</f>
         <v>8</v>
       </c>
-      <c r="AF7" s="8" t="n">
+      <c r="AF7" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AE7,AA7,Y7,W7,U7),0)</f>
         <v>9</v>
       </c>
@@ -11020,11 +11021,11 @@
       <c r="AJ7" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AK7" s="26" t="n">
-        <v>7</v>
-      </c>
-      <c r="AL7" s="27" t="s">
-        <v>152</v>
+      <c r="AK7" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL7" s="24" t="s">
+        <v>153</v>
       </c>
       <c r="AM7" s="1" t="n">
         <v>1</v>
@@ -11055,22 +11056,25 @@
       <c r="BB7" s="3" t="n">
         <v>9.5</v>
       </c>
-      <c r="BC7" s="8" t="n">
+      <c r="BC7" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AJ7,AK7,AM7,AO7,AQ7,AS7,AU7,AW7,BA7,BB7),0)</f>
         <v>4</v>
       </c>
-      <c r="BD7" s="8" t="n">
+      <c r="BD7" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="BF7" s="3" t="s">
-        <v>152</v>
+      <c r="BE7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF7" s="1" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="16" t="s">
         <v>35</v>
       </c>
       <c r="C8" s="1" t="n">
@@ -11104,35 +11108,35 @@
         <f aca="false">Q8+S8/2</f>
         <v>1</v>
       </c>
-      <c r="U8" s="8" t="n">
+      <c r="U8" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(C8,E8,G8,I8,K8,M8,O8,T8),0)</f>
         <v>1</v>
       </c>
-      <c r="V8" s="8" t="str">
+      <c r="V8" s="7" t="str">
         <f aca="false">IF(U8&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="W8" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="X8" s="8"/>
-      <c r="Y8" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="8"/>
-      <c r="AA8" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB8" s="8"/>
-      <c r="AC8" s="8" t="n">
+      <c r="W8" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="7"/>
+      <c r="AA8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="7"/>
+      <c r="AC8" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AD8" s="8"/>
+      <c r="AD8" s="7"/>
       <c r="AE8" s="1" t="n">
         <f aca="false">AC8+AD8/2</f>
         <v>0</v>
       </c>
-      <c r="AF8" s="8" t="n">
+      <c r="AF8" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AE8,AA8,Y8,W8,U8),0)</f>
         <v>2</v>
       </c>
@@ -11149,19 +11153,19 @@
         <v>6</v>
       </c>
       <c r="AL8" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AM8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="AN8" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AO8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="AP8" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AQ8" s="1" t="n">
         <v>6</v>
@@ -11170,9 +11174,9 @@
         <v>5</v>
       </c>
       <c r="AT8" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="AU8" s="28" t="n">
+        <v>156</v>
+      </c>
+      <c r="AU8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="AW8" s="1" t="n">
@@ -11188,20 +11192,26 @@
       <c r="BB8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="BC8" s="8" t="n">
+      <c r="BC8" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AJ8,AK8,AM8,AO8,AQ8,AS8,AU8,AW8,BA8,BB8),0)</f>
         <v>4</v>
       </c>
-      <c r="BD8" s="8" t="n">
+      <c r="BD8" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AF8,BC8),0)</f>
         <v>3</v>
       </c>
+      <c r="BE8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF8" s="1" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C9" s="1" t="n">
@@ -11213,7 +11223,7 @@
       <c r="G9" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I9" s="15" t="n">
         <v>7</v>
       </c>
       <c r="J9" s="4" t="n">
@@ -11238,39 +11248,39 @@
         <f aca="false">Q9+S9/2</f>
         <v>10</v>
       </c>
-      <c r="U9" s="8" t="n">
+      <c r="U9" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(M9,O9,T9),0)</f>
         <v>9</v>
       </c>
-      <c r="V9" s="8" t="str">
+      <c r="V9" s="7" t="str">
         <f aca="false">IF(U9&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W9" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="X9" s="8"/>
-      <c r="Y9" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z9" s="20" t="n">
+      <c r="W9" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z9" s="17" t="n">
         <v>45849</v>
       </c>
-      <c r="AA9" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB9" s="20" t="n">
+      <c r="AA9" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB9" s="17" t="n">
         <v>45849</v>
       </c>
-      <c r="AC9" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD9" s="8"/>
+      <c r="AC9" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD9" s="7"/>
       <c r="AE9" s="1" t="n">
         <f aca="false">AC9+AD9/2</f>
         <v>7</v>
       </c>
-      <c r="AF9" s="8" t="n">
+      <c r="AF9" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AE9,AA9,Y9,W9,U9),0)</f>
         <v>8</v>
       </c>
@@ -11284,43 +11294,43 @@
         <v>7</v>
       </c>
       <c r="AL9" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AM9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AN9" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AP9" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AQ9" s="1" t="n">
         <v>6</v>
       </c>
       <c r="AR9" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AS9" s="1" t="n">
         <v>5</v>
       </c>
       <c r="AT9" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AU9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AV9" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="AW9" s="21" t="n">
+        <v>157</v>
+      </c>
+      <c r="AW9" s="18" t="n">
         <v>5</v>
       </c>
       <c r="AX9" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AY9" s="2" t="n">
         <v>9</v>
@@ -11331,11 +11341,11 @@
         <v>9</v>
       </c>
       <c r="BB9" s="2"/>
-      <c r="BC9" s="8" t="n">
+      <c r="BC9" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AJ9,AK9,AM9,AO9,AQ9,AS9,AU9,AW9,BA9),0)</f>
         <v>7</v>
       </c>
-      <c r="BD9" s="8" t="n">
+      <c r="BD9" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AF9,BC9),0)</f>
         <v>8</v>
       </c>
@@ -11344,49 +11354,49 @@
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="14" t="s">
         <v>41</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="E10" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="F10" s="20" t="n">
+      <c r="E10" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" s="17" t="n">
         <v>45846</v>
       </c>
-      <c r="G10" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="H10" s="20" t="n">
+      <c r="G10" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H10" s="17" t="n">
         <v>45846</v>
       </c>
-      <c r="I10" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="J10" s="20" t="n">
+      <c r="I10" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" s="17" t="n">
         <v>45846</v>
       </c>
-      <c r="K10" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="L10" s="20" t="n">
+      <c r="K10" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="L10" s="17" t="n">
         <v>45848</v>
       </c>
       <c r="M10" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="O10" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="P10" s="20" t="n">
+      <c r="O10" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="P10" s="17" t="n">
         <v>45848</v>
       </c>
-      <c r="Q10" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="R10" s="20" t="n">
+      <c r="Q10" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="R10" s="17" t="n">
         <v>45848</v>
       </c>
       <c r="S10" s="1" t="n">
@@ -11396,41 +11406,41 @@
         <f aca="false">Q10+S10/2</f>
         <v>8</v>
       </c>
-      <c r="U10" s="8" t="n">
+      <c r="U10" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(M10,O10,T10),0)</f>
         <v>6</v>
       </c>
-      <c r="V10" s="8" t="str">
+      <c r="V10" s="7" t="str">
         <f aca="false">IF(U10&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="W10" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="X10" s="20" t="n">
+      <c r="W10" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="X10" s="17" t="n">
         <v>45848</v>
       </c>
-      <c r="Y10" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z10" s="20" t="n">
+      <c r="Y10" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z10" s="17" t="n">
         <v>45848</v>
       </c>
-      <c r="AA10" s="23" t="n">
+      <c r="AA10" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="AB10" s="20" t="n">
+      <c r="AB10" s="17" t="n">
         <v>45848</v>
       </c>
-      <c r="AC10" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD10" s="8"/>
+      <c r="AC10" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD10" s="7"/>
       <c r="AE10" s="1" t="n">
         <f aca="false">AC10+AD10/2</f>
         <v>8</v>
       </c>
-      <c r="AF10" s="8" t="n">
+      <c r="AF10" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AE10,AA10,Y10,W10,U10),0)</f>
         <v>7</v>
       </c>
@@ -11444,43 +11454,43 @@
         <v>7</v>
       </c>
       <c r="AL10" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AM10" s="1" t="n">
         <v>5</v>
       </c>
       <c r="AN10" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="AO10" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP10" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="AO10" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AP10" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="AQ10" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AR10" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AS10" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AT10" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AU10" s="1" t="n">
         <v>6</v>
       </c>
       <c r="AV10" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AW10" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AX10" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AY10" s="3" t="n">
         <v>6</v>
@@ -11491,11 +11501,11 @@
         <v>6</v>
       </c>
       <c r="BB10" s="3"/>
-      <c r="BC10" s="8" t="n">
+      <c r="BC10" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AJ10,AK10,AM10,AO10,AQ10,AS10,AU10,AW10,BA10),0)</f>
         <v>7</v>
       </c>
-      <c r="BD10" s="8" t="n">
+      <c r="BD10" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AF10,BC10),0)</f>
         <v>7</v>
       </c>
@@ -11504,7 +11514,7 @@
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="14" t="s">
         <v>44</v>
       </c>
       <c r="C11" s="1" t="n">
@@ -11538,41 +11548,41 @@
         <f aca="false">Q11+S11/2</f>
         <v>16</v>
       </c>
-      <c r="U11" s="8" t="n">
+      <c r="U11" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(M11,O11,T11),0)</f>
         <v>11</v>
       </c>
-      <c r="V11" s="8" t="str">
+      <c r="V11" s="7" t="str">
         <f aca="false">IF(U11&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W11" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="X11" s="20" t="n">
+      <c r="W11" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="X11" s="17" t="n">
         <v>45848</v>
       </c>
-      <c r="Y11" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z11" s="20" t="n">
+      <c r="Y11" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z11" s="17" t="n">
         <v>45849</v>
       </c>
-      <c r="AA11" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB11" s="20" t="n">
+      <c r="AA11" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB11" s="17" t="n">
         <v>45848</v>
       </c>
-      <c r="AC11" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD11" s="8"/>
+      <c r="AC11" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD11" s="7"/>
       <c r="AE11" s="1" t="n">
         <f aca="false">AC11+AD11/2</f>
         <v>10</v>
       </c>
-      <c r="AF11" s="8" t="n">
+      <c r="AF11" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AE11,AA11,Y11,W11,U11),0)</f>
         <v>9</v>
       </c>
@@ -11589,7 +11599,7 @@
         <v>10</v>
       </c>
       <c r="AN11" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AO11" s="1" t="n">
         <v>10</v>
@@ -11618,11 +11628,11 @@
         <v>9</v>
       </c>
       <c r="BB11" s="3"/>
-      <c r="BC11" s="8" t="n">
+      <c r="BC11" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AJ11,AK11,AM11,AO11,AQ11,AS11,AU11,AW11,BA11),0)</f>
         <v>10</v>
       </c>
-      <c r="BD11" s="8" t="n">
+      <c r="BD11" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AF11,BC11),0)</f>
         <v>10</v>
       </c>
@@ -11631,7 +11641,7 @@
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="14" t="s">
         <v>47</v>
       </c>
       <c r="C12" s="1" t="n">
@@ -11686,41 +11696,41 @@
         <f aca="false">Q12+S12/2</f>
         <v>9</v>
       </c>
-      <c r="U12" s="8" t="n">
+      <c r="U12" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(M12,O12,T12),0)</f>
         <v>8</v>
       </c>
-      <c r="V12" s="8" t="str">
+      <c r="V12" s="7" t="str">
         <f aca="false">IF(U12&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W12" s="8" t="n">
+      <c r="W12" s="7" t="n">
         <v>8</v>
       </c>
       <c r="X12" s="4" t="n">
         <v>45848</v>
       </c>
-      <c r="Y12" s="8" t="n">
+      <c r="Y12" s="7" t="n">
         <v>8</v>
       </c>
       <c r="Z12" s="4" t="n">
         <v>45848</v>
       </c>
-      <c r="AA12" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB12" s="8"/>
-      <c r="AC12" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD12" s="8" t="n">
+      <c r="AA12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="7"/>
+      <c r="AC12" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD12" s="7" t="n">
         <v>10</v>
       </c>
       <c r="AE12" s="1" t="n">
         <f aca="false">AC12+AD12/2</f>
         <v>12</v>
       </c>
-      <c r="AF12" s="8" t="n">
+      <c r="AF12" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AE12,AA12,Y12,W12,U12),0)</f>
         <v>7</v>
       </c>
@@ -11737,19 +11747,19 @@
         <v>7</v>
       </c>
       <c r="AL12" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM12" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AN12" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AO12" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AP12" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AQ12" s="1" t="n">
         <v>7</v>
@@ -11767,12 +11777,12 @@
         <v>1</v>
       </c>
       <c r="AV12" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AW12" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AX12" s="29" t="n">
+      <c r="AX12" s="26" t="n">
         <v>45988</v>
       </c>
       <c r="AY12" s="3" t="n">
@@ -11788,11 +11798,11 @@
       <c r="BB12" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="BC12" s="8" t="n">
+      <c r="BC12" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AJ12,AK12,AM12,AO12,AQ12,AS12,AU12,AW12,BA12,BB12),0)</f>
         <v>7</v>
       </c>
-      <c r="BD12" s="8" t="n">
+      <c r="BD12" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AF12,BC12),0)</f>
         <v>7</v>
       </c>
@@ -11804,7 +11814,7 @@
       <c r="A13" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="14" t="s">
         <v>50</v>
       </c>
       <c r="C13" s="1" t="n">
@@ -11838,35 +11848,35 @@
         <f aca="false">Q13+S13/2</f>
         <v>10.5</v>
       </c>
-      <c r="U13" s="8" t="n">
+      <c r="U13" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(M13,O13,T13),0)</f>
         <v>10</v>
       </c>
-      <c r="V13" s="8" t="str">
+      <c r="V13" s="7" t="str">
         <f aca="false">IF(U13&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W13" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z13" s="8"/>
-      <c r="AA13" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB13" s="8"/>
-      <c r="AC13" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD13" s="8"/>
+      <c r="W13" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="X13" s="7"/>
+      <c r="Y13" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z13" s="7"/>
+      <c r="AA13" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB13" s="7"/>
+      <c r="AC13" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD13" s="7"/>
       <c r="AE13" s="1" t="n">
         <f aca="false">AC13+AD13/2</f>
         <v>7</v>
       </c>
-      <c r="AF13" s="8" t="n">
+      <c r="AF13" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AE13,AA13,Y13,W13,U13),0)</f>
         <v>9</v>
       </c>
@@ -11880,43 +11890,43 @@
         <v>7</v>
       </c>
       <c r="AL13" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AM13" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AN13" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AO13" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AP13" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AQ13" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AR13" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AS13" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AT13" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AU13" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AV13" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AW13" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AY13" s="3" t="n">
         <v>8</v>
@@ -11927,11 +11937,11 @@
         <v>8</v>
       </c>
       <c r="BB13" s="3"/>
-      <c r="BC13" s="8" t="n">
+      <c r="BC13" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AJ13,AK13,AM13,AO13,AQ13,AS13,AU13,AW13,BA13),0)</f>
         <v>7</v>
       </c>
-      <c r="BD13" s="8" t="n">
+      <c r="BD13" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AF13,BC13),0)</f>
         <v>8</v>
       </c>
@@ -11940,7 +11950,7 @@
       <c r="A14" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="14" t="s">
         <v>53</v>
       </c>
       <c r="C14" s="2" t="n">
@@ -11986,41 +11996,41 @@
         <f aca="false">Q14+S14/2</f>
         <v>8.5</v>
       </c>
-      <c r="U14" s="8" t="n">
+      <c r="U14" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(M14,O14,T14),0)</f>
         <v>9</v>
       </c>
-      <c r="V14" s="8" t="str">
+      <c r="V14" s="7" t="str">
         <f aca="false">IF(U14&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W14" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="X14" s="20" t="n">
+      <c r="W14" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="X14" s="17" t="n">
         <v>45848</v>
       </c>
-      <c r="Y14" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z14" s="20" t="n">
+      <c r="Y14" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z14" s="17" t="n">
         <v>45848</v>
       </c>
-      <c r="AA14" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB14" s="20" t="n">
+      <c r="AA14" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB14" s="17" t="n">
         <v>45848</v>
       </c>
-      <c r="AC14" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD14" s="8"/>
+      <c r="AC14" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD14" s="7"/>
       <c r="AE14" s="1" t="n">
         <f aca="false">AC14+AD14/2</f>
         <v>7</v>
       </c>
-      <c r="AF14" s="8" t="n">
+      <c r="AF14" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AE14,AA14,Y14,W14,U14),0)</f>
         <v>8</v>
       </c>
@@ -12033,32 +12043,32 @@
       <c r="AK14" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AL14" s="17" t="s">
+      <c r="AL14" s="14" t="s">
         <v>136</v>
       </c>
       <c r="AM14" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AN14" s="17" t="s">
-        <v>172</v>
+      <c r="AN14" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="AO14" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AP14" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AQ14" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AR14" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AS14" s="6" t="n">
         <v>5</v>
       </c>
       <c r="AT14" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AU14" s="1" t="n">
         <v>7</v>
@@ -12070,7 +12080,7 @@
         <v>7</v>
       </c>
       <c r="AX14" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AY14" s="3" t="n">
         <v>3</v>
@@ -12085,11 +12095,11 @@
       <c r="BB14" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="BC14" s="8" t="n">
+      <c r="BC14" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AJ14,AK14,AM14,AO14,AQ14,AS14,AU14,AW14,BA14,BB14),0)</f>
         <v>8</v>
       </c>
-      <c r="BD14" s="8" t="n">
+      <c r="BD14" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AF14,BC14),0)</f>
         <v>8</v>
       </c>
@@ -12098,7 +12108,7 @@
       <c r="A15" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="14" t="s">
         <v>56</v>
       </c>
       <c r="C15" s="1" t="n">
@@ -12132,35 +12142,35 @@
         <f aca="false">Q15+S15/2</f>
         <v>9</v>
       </c>
-      <c r="U15" s="8" t="n">
+      <c r="U15" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(M15,O15,T15),0)</f>
         <v>9</v>
       </c>
-      <c r="V15" s="8" t="str">
+      <c r="V15" s="7" t="str">
         <f aca="false">IF(U15&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W15" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="X15" s="8"/>
-      <c r="Y15" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z15" s="8"/>
-      <c r="AA15" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB15" s="8"/>
-      <c r="AC15" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD15" s="23"/>
+      <c r="W15" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="X15" s="7"/>
+      <c r="Y15" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z15" s="7"/>
+      <c r="AA15" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB15" s="7"/>
+      <c r="AC15" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD15" s="20"/>
       <c r="AE15" s="1" t="n">
         <f aca="false">AC15+AD15/2</f>
         <v>10</v>
       </c>
-      <c r="AF15" s="8" t="n">
+      <c r="AF15" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AE15,AA15,Y15,W15,U15),0)</f>
         <v>10</v>
       </c>
@@ -12173,44 +12183,44 @@
       <c r="AK15" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AL15" s="17" t="s">
+      <c r="AL15" s="14" t="s">
         <v>136</v>
       </c>
       <c r="AM15" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AN15" s="17" t="s">
-        <v>175</v>
+      <c r="AN15" s="14" t="s">
+        <v>176</v>
       </c>
       <c r="AO15" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AP15" s="17" t="s">
-        <v>176</v>
+      <c r="AP15" s="14" t="s">
+        <v>177</v>
       </c>
       <c r="AQ15" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AR15" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="AS15" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT15" s="17" t="s">
+      <c r="AR15" s="14" t="s">
         <v>178</v>
       </c>
+      <c r="AS15" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT15" s="14" t="s">
+        <v>179</v>
+      </c>
       <c r="AU15" s="2" t="n">
         <v>7</v>
       </c>
       <c r="AV15" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="AW15" s="30" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX15" s="17" t="s">
         <v>180</v>
+      </c>
+      <c r="AW15" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX15" s="14" t="s">
+        <v>181</v>
       </c>
       <c r="AY15" s="6" t="n">
         <v>7</v>
@@ -12223,11 +12233,11 @@
         <v>11.5</v>
       </c>
       <c r="BB15" s="6"/>
-      <c r="BC15" s="8" t="n">
+      <c r="BC15" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AJ15,AK15,AM15,AO15,AQ15,AS15,AU15,AW15,BA15),0)</f>
         <v>9</v>
       </c>
-      <c r="BD15" s="8" t="n">
+      <c r="BD15" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AF15,BC15),0)</f>
         <v>10</v>
       </c>
@@ -12236,7 +12246,7 @@
       <c r="A16" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="14" t="s">
         <v>60</v>
       </c>
       <c r="C16" s="1" t="n">
@@ -12269,41 +12279,41 @@
       <c r="T16" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="U16" s="8" t="n">
+      <c r="U16" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(M16,O16,T16),0)</f>
         <v>8</v>
       </c>
-      <c r="V16" s="8" t="str">
+      <c r="V16" s="7" t="str">
         <f aca="false">IF(U16&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W16" s="31" t="n">
+      <c r="W16" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="X16" s="20" t="n">
+      <c r="X16" s="17" t="n">
         <v>45848</v>
       </c>
-      <c r="Y16" s="23" t="n">
+      <c r="Y16" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="Z16" s="20" t="n">
+      <c r="Z16" s="17" t="n">
         <v>45848</v>
       </c>
-      <c r="AA16" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB16" s="20" t="n">
+      <c r="AA16" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB16" s="17" t="n">
         <v>45848</v>
       </c>
-      <c r="AC16" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD16" s="8"/>
+      <c r="AC16" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD16" s="7"/>
       <c r="AE16" s="1" t="n">
         <f aca="false">AC16+AD16/2</f>
         <v>8</v>
       </c>
-      <c r="AF16" s="8" t="n">
+      <c r="AF16" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AE16,AA16,Y16,W16,U16),0)</f>
         <v>7</v>
       </c>
@@ -12317,115 +12327,115 @@
         <v>9</v>
       </c>
       <c r="AL16" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM16" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AN16" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AO16" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AP16" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AQ16" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AR16" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AS16" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AT16" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AU16" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AV16" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AW16" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AX16" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="AY16" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ16" s="17"/>
+        <v>187</v>
+      </c>
+      <c r="AY16" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ16" s="14"/>
       <c r="BA16" s="1" t="n">
         <f aca="false">AY16+AZ16/2</f>
         <v>9</v>
       </c>
-      <c r="BB16" s="17"/>
-      <c r="BC16" s="8" t="n">
+      <c r="BB16" s="14"/>
+      <c r="BC16" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AJ16,AK16,AM16,AO16,AQ16,AS16,AU16,AW16,BA16),0)</f>
         <v>8</v>
       </c>
-      <c r="BD16" s="8" t="n">
+      <c r="BD16" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AF16,BC16),0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C17" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="D17" s="33" t="n">
+      <c r="C17" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="D17" s="30" t="n">
         <v>45881</v>
       </c>
-      <c r="E17" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="F17" s="20" t="n">
+      <c r="E17" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="F17" s="17" t="n">
         <v>45846</v>
       </c>
-      <c r="G17" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="H17" s="20" t="n">
+      <c r="G17" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="H17" s="17" t="n">
         <v>45846</v>
       </c>
-      <c r="I17" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="J17" s="20" t="n">
+      <c r="I17" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" s="17" t="n">
         <v>45846</v>
       </c>
-      <c r="K17" s="14" t="n">
+      <c r="K17" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="L17" s="20" t="n">
+      <c r="L17" s="17" t="n">
         <v>45848</v>
       </c>
-      <c r="M17" s="32" t="n">
+      <c r="M17" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="N17" s="33" t="n">
+      <c r="N17" s="30" t="n">
         <v>45881</v>
       </c>
-      <c r="O17" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="P17" s="20" t="n">
+      <c r="O17" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="P17" s="17" t="n">
         <v>45848</v>
       </c>
-      <c r="Q17" s="14" t="n">
+      <c r="Q17" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="R17" s="20" t="n">
+      <c r="R17" s="17" t="n">
         <v>45848</v>
       </c>
       <c r="S17" s="1" t="n">
@@ -12435,46 +12445,46 @@
         <f aca="false">Q17+S17/2</f>
         <v>6</v>
       </c>
-      <c r="U17" s="8" t="n">
+      <c r="U17" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(C17,E17,G17,I17,K17,M17,O17,T17),0)</f>
         <v>7</v>
       </c>
-      <c r="V17" s="8" t="str">
+      <c r="V17" s="7" t="str">
         <f aca="false">IF(U17&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W17" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="X17" s="20" t="n">
+      <c r="W17" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="X17" s="17" t="n">
         <v>45848</v>
       </c>
-      <c r="Y17" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z17" s="20" t="n">
+      <c r="Y17" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z17" s="17" t="n">
         <v>45848</v>
       </c>
-      <c r="AA17" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB17" s="33" t="n">
+      <c r="AA17" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB17" s="30" t="n">
         <v>45848</v>
       </c>
-      <c r="AC17" s="8" t="n">
+      <c r="AC17" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AD17" s="8"/>
+      <c r="AD17" s="7"/>
       <c r="AE17" s="1" t="n">
         <f aca="false">AC17+AD17/2</f>
         <v>5</v>
       </c>
-      <c r="AF17" s="8" t="n">
+      <c r="AF17" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AE17,AA17,Y17,W17,U17),0)</f>
         <v>7</v>
       </c>
       <c r="AG17" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AH17" s="1" t="s">
         <v>18</v>
@@ -12488,32 +12498,32 @@
       <c r="AK17" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AL17" s="34" t="s">
-        <v>188</v>
+      <c r="AL17" s="31" t="s">
+        <v>189</v>
       </c>
       <c r="AM17" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AN17" s="34" t="s">
-        <v>189</v>
+      <c r="AN17" s="31" t="s">
+        <v>190</v>
       </c>
       <c r="AO17" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AP17" s="34" t="s">
-        <v>190</v>
+      <c r="AP17" s="31" t="s">
+        <v>191</v>
       </c>
       <c r="AQ17" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AR17" s="34" t="s">
-        <v>190</v>
+      <c r="AR17" s="31" t="s">
+        <v>191</v>
       </c>
       <c r="AS17" s="1" t="n">
         <v>5</v>
       </c>
       <c r="AT17" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AU17" s="2" t="n">
         <v>5</v>
@@ -12537,23 +12547,23 @@
       <c r="BB17" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="BC17" s="8" t="n">
+      <c r="BC17" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AJ17,AK17,AM17,AO17,AQ17,AS17,AU17,AW17,BA17,BB17),0)</f>
         <v>7</v>
       </c>
-      <c r="BD17" s="8" t="n">
+      <c r="BD17" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AF17,BC17),0)</f>
         <v>7</v>
       </c>
       <c r="BF17" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="16" t="s">
         <v>66</v>
       </c>
       <c r="C18" s="1" t="n">
@@ -12578,7 +12588,7 @@
         <v>9</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q18" s="1" t="n">
         <v>10</v>
@@ -12590,35 +12600,35 @@
         <f aca="false">Q18+S18/2</f>
         <v>10.5</v>
       </c>
-      <c r="U18" s="8" t="n">
+      <c r="U18" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(M18,O18,T18),0)</f>
         <v>10</v>
       </c>
-      <c r="V18" s="8" t="str">
+      <c r="V18" s="7" t="str">
         <f aca="false">IF(U18&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W18" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="X18" s="8"/>
-      <c r="Y18" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="Z18" s="8"/>
-      <c r="AA18" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB18" s="8"/>
-      <c r="AC18" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD18" s="8"/>
+      <c r="W18" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="X18" s="7"/>
+      <c r="Y18" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="Z18" s="7"/>
+      <c r="AA18" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB18" s="7"/>
+      <c r="AC18" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD18" s="7"/>
       <c r="AE18" s="1" t="n">
         <f aca="false">AC18+AD18/2</f>
         <v>8</v>
       </c>
-      <c r="AF18" s="8" t="n">
+      <c r="AF18" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AE18,AA18,Y18,W18,U18),0)</f>
         <v>9</v>
       </c>
@@ -12638,20 +12648,26 @@
       <c r="BB18" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="BC18" s="8" t="n">
+      <c r="BC18" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AJ18,AK18,AM18,AO18,AQ18,AS18,AU18,AW18,BA18,BB18),0)</f>
         <v>3</v>
       </c>
-      <c r="BD18" s="8" t="n">
+      <c r="BD18" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AF18,BC18),0)</f>
         <v>6</v>
+      </c>
+      <c r="BE18" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF18" s="1" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.7" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="14" t="s">
         <v>69</v>
       </c>
       <c r="C19" s="1" t="n">
@@ -12685,39 +12701,39 @@
         <f aca="false">Q19+S19/2</f>
         <v>8.5</v>
       </c>
-      <c r="U19" s="8" t="n">
+      <c r="U19" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(M19,O19,T19),0)</f>
         <v>9</v>
       </c>
-      <c r="V19" s="8" t="str">
+      <c r="V19" s="7" t="str">
         <f aca="false">IF(U19&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W19" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="X19" s="8"/>
-      <c r="Y19" s="35" t="n">
+      <c r="W19" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="X19" s="7"/>
+      <c r="Y19" s="32" t="n">
         <v>9</v>
       </c>
       <c r="Z19" s="4" t="n">
         <v>45848</v>
       </c>
-      <c r="AA19" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB19" s="20" t="n">
+      <c r="AA19" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB19" s="17" t="n">
         <v>45848</v>
       </c>
-      <c r="AC19" s="8" t="n">
+      <c r="AC19" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AD19" s="8"/>
+      <c r="AD19" s="7"/>
       <c r="AE19" s="1" t="n">
         <f aca="false">AC19+AD19/2</f>
         <v>5</v>
       </c>
-      <c r="AF19" s="8" t="n">
+      <c r="AF19" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AE19,AA19,Y19,W19,U19),0)</f>
         <v>8</v>
       </c>
@@ -12731,43 +12747,43 @@
         <v>6</v>
       </c>
       <c r="AL19" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AM19" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AN19" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AO19" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AP19" s="34" t="s">
-        <v>197</v>
+      <c r="AP19" s="31" t="s">
+        <v>198</v>
       </c>
       <c r="AQ19" s="1" t="n">
         <v>6</v>
       </c>
       <c r="AR19" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AS19" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AT19" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AU19" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AV19" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AW19" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AX19" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AY19" s="1" t="n">
         <v>7</v>
@@ -12776,11 +12792,11 @@
         <f aca="false">AY19+AZ19/2</f>
         <v>7</v>
       </c>
-      <c r="BC19" s="8" t="n">
+      <c r="BC19" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AJ19,AK19,AM19,AO19,AQ19,AS19,AU19,AW19,BA19),0)</f>
         <v>7</v>
       </c>
-      <c r="BD19" s="8" t="n">
+      <c r="BD19" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AF19,BC19),0)</f>
         <v>8</v>
       </c>
@@ -12789,7 +12805,7 @@
       <c r="A20" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="14" t="s">
         <v>72</v>
       </c>
       <c r="C20" s="1" t="n">
@@ -12823,35 +12839,35 @@
         <f aca="false">Q20+S20/2</f>
         <v>10.5</v>
       </c>
-      <c r="U20" s="8" t="n">
+      <c r="U20" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(M20,O20,T20),0)</f>
         <v>10</v>
       </c>
-      <c r="V20" s="8" t="str">
+      <c r="V20" s="7" t="str">
         <f aca="false">IF(U20&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W20" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="X20" s="8"/>
-      <c r="Y20" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z20" s="8"/>
-      <c r="AA20" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB20" s="8"/>
-      <c r="AC20" s="8" t="n">
+      <c r="W20" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="X20" s="7"/>
+      <c r="Y20" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z20" s="7"/>
+      <c r="AA20" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB20" s="7"/>
+      <c r="AC20" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="AD20" s="8"/>
+      <c r="AD20" s="7"/>
       <c r="AE20" s="1" t="n">
         <f aca="false">AC20+AD20/2</f>
         <v>6</v>
       </c>
-      <c r="AF20" s="8" t="n">
+      <c r="AF20" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AE20,AA20,Y20,W20,U20),0)</f>
         <v>8</v>
       </c>
@@ -12865,31 +12881,31 @@
         <v>7</v>
       </c>
       <c r="AL20" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AM20" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AN20" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AO20" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AP20" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AQ20" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AR20" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AS20" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AT20" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AU20" s="1" t="n">
         <v>7</v>
@@ -12901,7 +12917,7 @@
         <v>4</v>
       </c>
       <c r="AX20" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AY20" s="2" t="n">
         <v>9</v>
@@ -12912,11 +12928,11 @@
         <v>9</v>
       </c>
       <c r="BB20" s="2"/>
-      <c r="BC20" s="8" t="n">
+      <c r="BC20" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AJ20,AK20,AM20,AO20,AQ20,AS20,AU20,AW20,BA20),0)</f>
         <v>7</v>
       </c>
-      <c r="BD20" s="8" t="n">
+      <c r="BD20" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AF20,BC20),0)</f>
         <v>8</v>
       </c>
@@ -12925,7 +12941,7 @@
       <c r="A21" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="14" t="s">
         <v>75</v>
       </c>
       <c r="C21" s="1" t="n">
@@ -12959,35 +12975,35 @@
         <f aca="false">Q21+S21/2</f>
         <v>11</v>
       </c>
-      <c r="U21" s="8" t="n">
+      <c r="U21" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(M21,O21,T21),0)</f>
         <v>10</v>
       </c>
-      <c r="V21" s="8" t="str">
+      <c r="V21" s="7" t="str">
         <f aca="false">IF(U21&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W21" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="X21" s="8"/>
-      <c r="Y21" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z21" s="8"/>
-      <c r="AA21" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB21" s="8"/>
-      <c r="AC21" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD21" s="8"/>
+      <c r="W21" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="X21" s="7"/>
+      <c r="Y21" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z21" s="7"/>
+      <c r="AA21" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB21" s="7"/>
+      <c r="AC21" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD21" s="7"/>
       <c r="AE21" s="1" t="n">
         <f aca="false">AC21+AD21/2</f>
         <v>10</v>
       </c>
-      <c r="AF21" s="8" t="n">
+      <c r="AF21" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AE21,AA21,Y21,W21,U21),0)</f>
         <v>9</v>
       </c>
@@ -13001,40 +13017,40 @@
         <v>7</v>
       </c>
       <c r="AL21" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="AM21" s="36" t="n">
+        <v>206</v>
+      </c>
+      <c r="AM21" s="33" t="n">
         <v>7</v>
       </c>
       <c r="AN21" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AO21" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AP21" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AQ21" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AR21" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="AS21" s="36" t="n">
+        <v>208</v>
+      </c>
+      <c r="AS21" s="33" t="n">
         <v>7</v>
       </c>
       <c r="AT21" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="AU21" s="36" t="n">
+        <v>209</v>
+      </c>
+      <c r="AU21" s="33" t="n">
         <v>7</v>
       </c>
       <c r="AW21" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AX21" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AY21" s="6" t="n">
         <v>10</v>
@@ -13047,11 +13063,11 @@
       <c r="BB21" s="6" t="n">
         <v>9.5</v>
       </c>
-      <c r="BC21" s="8" t="n">
+      <c r="BC21" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AJ21,AK21,AM21,AO21,AQ21,AS21,AU21,AW21,BA21,BB21),0)</f>
         <v>8</v>
       </c>
-      <c r="BD21" s="8" t="n">
+      <c r="BD21" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AF21,BC21),0)</f>
         <v>9</v>
       </c>
@@ -13060,7 +13076,7 @@
       <c r="A22" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="16" t="s">
         <v>78</v>
       </c>
       <c r="C22" s="1" t="n">
@@ -13094,35 +13110,35 @@
         <f aca="false">Q22+S22/2</f>
         <v>2</v>
       </c>
-      <c r="U22" s="8" t="n">
+      <c r="U22" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(C22,E22,G22,I22,K22,M22,O22,T22),0)</f>
         <v>2</v>
       </c>
-      <c r="V22" s="8" t="str">
+      <c r="V22" s="7" t="str">
         <f aca="false">IF(U22&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="W22" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="X22" s="8"/>
-      <c r="Y22" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z22" s="8"/>
-      <c r="AA22" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB22" s="8"/>
-      <c r="AC22" s="8" t="n">
+      <c r="W22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X22" s="7"/>
+      <c r="Y22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="7"/>
+      <c r="AA22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="7"/>
+      <c r="AC22" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="AD22" s="8"/>
+      <c r="AD22" s="7"/>
       <c r="AE22" s="1" t="n">
         <f aca="false">AC22+AD22/2</f>
         <v>6</v>
       </c>
-      <c r="AF22" s="8" t="n">
+      <c r="AF22" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AE22,AA22,Y22,W22,U22),0)</f>
         <v>2</v>
       </c>
@@ -13139,43 +13155,43 @@
         <v>7</v>
       </c>
       <c r="AL22" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AM22" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AN22" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AO22" s="1" t="n">
         <v>5</v>
       </c>
       <c r="AP22" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AQ22" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AR22" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AS22" s="1" t="n">
         <v>5</v>
       </c>
       <c r="AT22" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AU22" s="1" t="n">
         <v>5</v>
       </c>
       <c r="AV22" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AW22" s="1" t="n">
         <v>2</v>
       </c>
       <c r="AX22" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AY22" s="2" t="n">
         <v>3</v>
@@ -13186,20 +13202,26 @@
         <v>3</v>
       </c>
       <c r="BB22" s="2"/>
-      <c r="BC22" s="8" t="n">
+      <c r="BC22" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AJ22,AK22,AM22,AO22,AQ22,AS22,AU22,AW22,BA22),0)</f>
         <v>5</v>
       </c>
-      <c r="BD22" s="8" t="n">
+      <c r="BD22" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AF22,BC22),0)</f>
         <v>4</v>
+      </c>
+      <c r="BE22" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF22" s="1" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="14" t="s">
         <v>81</v>
       </c>
       <c r="C23" s="1" t="n">
@@ -13211,7 +13233,7 @@
       <c r="G23" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="I23" s="18" t="n">
+      <c r="I23" s="15" t="n">
         <v>6</v>
       </c>
       <c r="J23" s="4" t="n">
@@ -13236,35 +13258,35 @@
         <f aca="false">Q23+S23/2</f>
         <v>8</v>
       </c>
-      <c r="U23" s="8" t="n">
+      <c r="U23" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(M23,O23,T23),0)</f>
         <v>8</v>
       </c>
-      <c r="V23" s="8" t="str">
+      <c r="V23" s="7" t="str">
         <f aca="false">IF(U23&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W23" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="X23" s="8"/>
-      <c r="Y23" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z23" s="8"/>
-      <c r="AA23" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB23" s="8"/>
-      <c r="AC23" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD23" s="23"/>
+      <c r="W23" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="X23" s="7"/>
+      <c r="Y23" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z23" s="7"/>
+      <c r="AA23" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB23" s="7"/>
+      <c r="AC23" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD23" s="20"/>
       <c r="AE23" s="1" t="n">
         <f aca="false">AC23+AD23/2</f>
         <v>8</v>
       </c>
-      <c r="AF23" s="8" t="n">
+      <c r="AF23" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AE23,AA23,Y23,W23,U23),0)</f>
         <v>8</v>
       </c>
@@ -13278,13 +13300,13 @@
         <v>7</v>
       </c>
       <c r="AL23" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AM23" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AN23" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AO23" s="1" t="n">
         <v>7</v>
@@ -13296,25 +13318,25 @@
         <v>6</v>
       </c>
       <c r="AR23" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="AS23" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT23" s="17" t="s">
         <v>215</v>
       </c>
+      <c r="AS23" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT23" s="14" t="s">
+        <v>216</v>
+      </c>
       <c r="AU23" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AV23" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AW23" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AX23" s="37" t="s">
-        <v>180</v>
+      <c r="AX23" s="34" t="s">
+        <v>181</v>
       </c>
       <c r="AY23" s="6" t="n">
         <v>9</v>
@@ -13325,11 +13347,11 @@
         <v>9</v>
       </c>
       <c r="BB23" s="6"/>
-      <c r="BC23" s="8" t="n">
+      <c r="BC23" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AJ23,AK23,AM23,AO23,AQ23,AS23,AU23,AW23,BA23),0)</f>
         <v>7</v>
       </c>
-      <c r="BD23" s="8" t="n">
+      <c r="BD23" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AF23,BC23),0)</f>
         <v>8</v>
       </c>
@@ -13338,7 +13360,7 @@
       <c r="A24" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="14" t="s">
         <v>85</v>
       </c>
       <c r="C24" s="1" t="n">
@@ -13372,35 +13394,35 @@
         <f aca="false">Q24+S24/2</f>
         <v>11.5</v>
       </c>
-      <c r="U24" s="8" t="n">
+      <c r="U24" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(M24,O24,T24),0)</f>
         <v>11</v>
       </c>
-      <c r="V24" s="8" t="str">
+      <c r="V24" s="7" t="str">
         <f aca="false">IF(U24&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W24" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z24" s="8"/>
-      <c r="AA24" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB24" s="8"/>
-      <c r="AC24" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD24" s="8"/>
+      <c r="W24" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="X24" s="7"/>
+      <c r="Y24" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z24" s="7"/>
+      <c r="AA24" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB24" s="7"/>
+      <c r="AC24" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD24" s="7"/>
       <c r="AE24" s="1" t="n">
         <f aca="false">AC24+AD24/2</f>
         <v>8</v>
       </c>
-      <c r="AF24" s="8" t="n">
+      <c r="AF24" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AE24,AA24,Y24,W24,U24),0)</f>
         <v>10</v>
       </c>
@@ -13414,43 +13436,43 @@
         <v>8</v>
       </c>
       <c r="AL24" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AM24" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AN24" s="17" t="s">
+      <c r="AN24" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="AO24" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP24" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="AQ24" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR24" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="AS24" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT24" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="AU24" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV24" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="AO24" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP24" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="AQ24" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR24" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="AS24" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT24" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="AU24" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV24" s="17" t="s">
-        <v>217</v>
-      </c>
       <c r="AW24" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AX24" s="17" t="s">
-        <v>220</v>
+      <c r="AX24" s="14" t="s">
+        <v>221</v>
       </c>
       <c r="AY24" s="1" t="n">
         <v>9</v>
@@ -13459,11 +13481,11 @@
         <f aca="false">AY24+AZ24/2</f>
         <v>9</v>
       </c>
-      <c r="BC24" s="8" t="n">
+      <c r="BC24" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AJ24,AK24,AM24,AO24,AQ24,AS24,AU24,AW24,BA24),0)</f>
         <v>9</v>
       </c>
-      <c r="BD24" s="8" t="n">
+      <c r="BD24" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AF24,BC24),0)</f>
         <v>10</v>
       </c>
@@ -13472,7 +13494,7 @@
       <c r="A25" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="14" t="s">
         <v>88</v>
       </c>
       <c r="C25" s="1" t="n">
@@ -13506,34 +13528,34 @@
         <f aca="false">Q25+S25/2</f>
         <v>16.5</v>
       </c>
-      <c r="U25" s="8" t="n">
+      <c r="U25" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(M25,O25,T25),0)</f>
         <v>12</v>
       </c>
-      <c r="V25" s="8" t="str">
+      <c r="V25" s="7" t="str">
         <f aca="false">IF(U25&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
       <c r="W25" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="Y25" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z25" s="8"/>
-      <c r="AA25" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB25" s="8"/>
-      <c r="AC25" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD25" s="8"/>
+      <c r="Y25" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z25" s="7"/>
+      <c r="AA25" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB25" s="7"/>
+      <c r="AC25" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD25" s="7"/>
       <c r="AE25" s="1" t="n">
         <f aca="false">AC25+AD25/2</f>
         <v>10</v>
       </c>
-      <c r="AF25" s="8" t="n">
+      <c r="AF25" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AE25,AA25,Y25,W25,U25),0)</f>
         <v>10</v>
       </c>
@@ -13547,43 +13569,43 @@
         <v>9</v>
       </c>
       <c r="AL25" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AM25" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AN25" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO25" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AP25" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AQ25" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AR25" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AS25" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AT25" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AU25" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AV25" s="17" t="s">
-        <v>224</v>
+      <c r="AV25" s="14" t="s">
+        <v>225</v>
       </c>
       <c r="AW25" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AX25" s="17" t="s">
-        <v>180</v>
+      <c r="AX25" s="14" t="s">
+        <v>181</v>
       </c>
       <c r="AY25" s="1" t="n">
         <v>8</v>
@@ -13595,11 +13617,11 @@
         <f aca="false">AY25+AZ25/2</f>
         <v>12</v>
       </c>
-      <c r="BC25" s="8" t="n">
+      <c r="BC25" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AJ25,AK25,AM25,AO25,AQ25,AS25,AU25,AW25,BA25),0)</f>
         <v>10</v>
       </c>
-      <c r="BD25" s="8" t="n">
+      <c r="BD25" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AF25,BC25),0)</f>
         <v>10</v>
       </c>
@@ -13608,7 +13630,7 @@
       <c r="A26" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="14" t="s">
         <v>91</v>
       </c>
       <c r="C26" s="1" t="n">
@@ -13642,11 +13664,11 @@
         <f aca="false">Q26+S26/2</f>
         <v>13.5</v>
       </c>
-      <c r="U26" s="8" t="n">
+      <c r="U26" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(M26,O26,T26),0)</f>
         <v>11</v>
       </c>
-      <c r="V26" s="8" t="str">
+      <c r="V26" s="7" t="str">
         <f aca="false">IF(U26&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -13659,15 +13681,15 @@
       <c r="AA26" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AC26" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD26" s="8"/>
+      <c r="AC26" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD26" s="7"/>
       <c r="AE26" s="1" t="n">
         <f aca="false">AC26+AD26/2</f>
         <v>8</v>
       </c>
-      <c r="AF26" s="8" t="n">
+      <c r="AF26" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AE26,AA26,Y26,W26,U26),0)</f>
         <v>10</v>
       </c>
@@ -13680,44 +13702,44 @@
       <c r="AK26" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AL26" s="17" t="s">
-        <v>225</v>
+      <c r="AL26" s="14" t="s">
+        <v>226</v>
       </c>
       <c r="AM26" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AN26" s="17" t="s">
-        <v>225</v>
+      <c r="AN26" s="14" t="s">
+        <v>226</v>
       </c>
       <c r="AO26" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AP26" s="17" t="s">
-        <v>176</v>
+      <c r="AP26" s="14" t="s">
+        <v>177</v>
       </c>
       <c r="AQ26" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AR26" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AS26" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AT26" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AU26" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AV26" s="17" t="s">
-        <v>161</v>
+      <c r="AV26" s="14" t="s">
+        <v>162</v>
       </c>
       <c r="AW26" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AX26" s="17" t="s">
-        <v>226</v>
+      <c r="AX26" s="14" t="s">
+        <v>227</v>
       </c>
       <c r="AY26" s="1" t="n">
         <v>9</v>
@@ -13726,11 +13748,11 @@
         <f aca="false">AY26+AZ26/2</f>
         <v>9</v>
       </c>
-      <c r="BC26" s="8" t="n">
+      <c r="BC26" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AJ26,AK26,AM26,AO26,AQ26,AS26,AU26,AW26,BA26),0)</f>
         <v>10</v>
       </c>
-      <c r="BD26" s="8" t="n">
+      <c r="BD26" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AF26,BC26),0)</f>
         <v>10</v>
       </c>
@@ -13739,7 +13761,7 @@
       <c r="A27" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="14" t="s">
         <v>94</v>
       </c>
       <c r="C27" s="1" t="n">
@@ -13773,41 +13795,41 @@
         <f aca="false">Q27+S27/2</f>
         <v>10.5</v>
       </c>
-      <c r="U27" s="8" t="n">
+      <c r="U27" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(M27,O27,T27),0)</f>
         <v>9</v>
       </c>
-      <c r="V27" s="8" t="str">
+      <c r="V27" s="7" t="str">
         <f aca="false">IF(U27&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W27" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="X27" s="20" t="n">
+      <c r="W27" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="X27" s="17" t="n">
         <v>45848</v>
       </c>
-      <c r="Y27" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z27" s="20" t="n">
+      <c r="Y27" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z27" s="17" t="n">
         <v>45848</v>
       </c>
-      <c r="AA27" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB27" s="20" t="n">
+      <c r="AA27" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB27" s="17" t="n">
         <v>45848</v>
       </c>
-      <c r="AC27" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD27" s="8"/>
+      <c r="AC27" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD27" s="7"/>
       <c r="AE27" s="1" t="n">
         <f aca="false">AC27+AD27/2</f>
         <v>10</v>
       </c>
-      <c r="AF27" s="8" t="n">
+      <c r="AF27" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AE27,AA27,Y27,W27,U27),0)</f>
         <v>8</v>
       </c>
@@ -13821,43 +13843,43 @@
         <v>9</v>
       </c>
       <c r="AL27" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AM27" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AN27" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO27" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AP27" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AQ27" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AR27" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="AS27" s="21" t="n">
+        <v>228</v>
+      </c>
+      <c r="AS27" s="18" t="n">
         <v>1</v>
       </c>
       <c r="AT27" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AU27" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AV27" s="17" t="s">
-        <v>161</v>
+      <c r="AV27" s="14" t="s">
+        <v>162</v>
       </c>
       <c r="AW27" s="1" t="n">
         <v>3</v>
       </c>
       <c r="AX27" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AY27" s="1" t="n">
         <v>8</v>
@@ -13866,11 +13888,11 @@
         <f aca="false">AY27+AZ27/2</f>
         <v>8</v>
       </c>
-      <c r="BC27" s="8" t="n">
+      <c r="BC27" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AJ27,AK27,AM27,AO27,AQ27,AS27,AU27,AW27,BA27),0)</f>
         <v>7</v>
       </c>
-      <c r="BD27" s="8" t="n">
+      <c r="BD27" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AF27,BC27),0)</f>
         <v>8</v>
       </c>
@@ -13879,40 +13901,40 @@
       <c r="A28" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="C28" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="E28" s="14" t="n">
+      <c r="C28" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="E28" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="F28" s="20" t="n">
+      <c r="F28" s="17" t="n">
         <v>45852</v>
       </c>
-      <c r="G28" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="H28" s="20" t="n">
+      <c r="G28" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H28" s="17" t="n">
         <v>45852</v>
       </c>
       <c r="I28" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="K28" s="32" t="n">
+      <c r="K28" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="M28" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="N28" s="20" t="n">
+      <c r="M28" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="N28" s="17" t="n">
         <v>45852</v>
       </c>
-      <c r="O28" s="32" t="n">
+      <c r="O28" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="Q28" s="32" t="n">
+      <c r="Q28" s="29" t="n">
         <v>7</v>
       </c>
       <c r="S28" s="1" t="n">
@@ -13922,21 +13944,21 @@
         <f aca="false">Q28+S28/2</f>
         <v>7.5</v>
       </c>
-      <c r="U28" s="8" t="n">
+      <c r="U28" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(M28,O28,T28),0)</f>
         <v>8</v>
       </c>
-      <c r="V28" s="8" t="str">
+      <c r="V28" s="7" t="str">
         <f aca="false">IF(U28&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="W28" s="32" t="n">
+      <c r="W28" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="Y28" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA28" s="32" t="n">
+      <c r="Y28" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA28" s="29" t="n">
         <v>7</v>
       </c>
       <c r="AC28" s="1" t="n">
@@ -13946,7 +13968,7 @@
         <f aca="false">AC28+AD28/2</f>
         <v>5</v>
       </c>
-      <c r="AF28" s="8" t="n">
+      <c r="AF28" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AE28,AA28,Y28,W28,U28),0)</f>
         <v>7</v>
       </c>
@@ -13960,31 +13982,31 @@
         <v>8</v>
       </c>
       <c r="AL28" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AM28" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AN28" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="AO28" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ28" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS28" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU28" s="21" t="n">
+        <v>231</v>
+      </c>
+      <c r="AO28" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ28" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS28" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU28" s="18" t="n">
         <v>1</v>
       </c>
       <c r="AW28" s="1" t="n">
         <v>3</v>
       </c>
       <c r="AX28" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AY28" s="1" t="n">
         <v>3</v>
@@ -13993,11 +14015,11 @@
         <f aca="false">AY28+AZ28/2</f>
         <v>3</v>
       </c>
-      <c r="BC28" s="8" t="n">
+      <c r="BC28" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AJ28,AK28,AM28,AO28,AQ28,AS28,AU28,AW28,BA28),0)</f>
         <v>4</v>
       </c>
-      <c r="BD28" s="8" t="n">
+      <c r="BD28" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(AF28,BC28),0)</f>
         <v>6</v>
       </c>
@@ -14527,22 +14549,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>116</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14556,10 +14578,10 @@
         <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>10</v>
@@ -14581,10 +14603,10 @@
         <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>5</v>
@@ -14601,10 +14623,10 @@
         <v>23</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>1</v>
@@ -14624,10 +14646,10 @@
         <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>6</v>
@@ -14647,10 +14669,10 @@
         <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>7</v>
@@ -14672,10 +14694,10 @@
         <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>6</v>
@@ -14686,10 +14708,10 @@
         <v>29</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>6</v>
@@ -14700,10 +14722,10 @@
         <v>29</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>5</v>
@@ -14714,10 +14736,10 @@
         <v>29</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>4</v>
@@ -14762,10 +14784,10 @@
         <v>38</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>8</v>
@@ -14785,10 +14807,10 @@
         <v>41</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -14810,10 +14832,10 @@
         <v>41</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>8</v>
@@ -14830,10 +14852,10 @@
         <v>44</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>10</v>
@@ -14853,10 +14875,10 @@
         <v>47</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>10</v>
@@ -14876,10 +14898,10 @@
         <v>50</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>0</v>
@@ -14913,10 +14935,10 @@
         <v>56</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>10</v>
@@ -14936,10 +14958,10 @@
         <v>60</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>8</v>
@@ -14973,10 +14995,10 @@
         <v>66</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>9</v>
@@ -14998,10 +15020,10 @@
         <v>66</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>5</v>
@@ -15018,10 +15040,10 @@
         <v>69</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>7</v>
@@ -15041,10 +15063,10 @@
         <v>72</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>7</v>
@@ -15064,10 +15086,10 @@
         <v>75</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>10</v>
@@ -15087,10 +15109,10 @@
         <v>78</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>10</v>
@@ -15112,10 +15134,10 @@
         <v>78</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>8</v>
@@ -15126,10 +15148,10 @@
         <v>78</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>8</v>
@@ -15140,10 +15162,10 @@
         <v>78</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>8</v>
@@ -15154,10 +15176,10 @@
         <v>78</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>5</v>
@@ -15168,10 +15190,10 @@
         <v>78</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>1</v>
@@ -15188,10 +15210,10 @@
         <v>81</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>9</v>
@@ -15213,10 +15235,10 @@
         <v>81</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>6</v>
@@ -15233,10 +15255,10 @@
         <v>85</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>10</v>
@@ -15258,10 +15280,10 @@
         <v>85</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>9</v>
@@ -15272,10 +15294,10 @@
         <v>85</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>6</v>
@@ -15292,10 +15314,10 @@
         <v>88</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F39" s="1" t="n">
         <v>10</v>
@@ -15315,10 +15337,10 @@
         <v>91</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F40" s="1" t="n">
         <v>10</v>
@@ -15340,10 +15362,10 @@
         <v>91</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F41" s="1" t="n">
         <v>10</v>
@@ -15354,10 +15376,10 @@
         <v>91</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F42" s="1" t="n">
         <v>9</v>
@@ -15368,10 +15390,10 @@
         <v>91</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F43" s="1" t="n">
         <v>9</v>
@@ -15388,10 +15410,10 @@
         <v>94</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>9</v>
@@ -15413,10 +15435,10 @@
         <v>94</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>8</v>
@@ -15427,10 +15449,10 @@
         <v>94</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F46" s="1" t="n">
         <v>7</v>
@@ -15441,10 +15463,10 @@
         <v>94</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F47" s="1" t="n">
         <v>3</v>
@@ -15511,22 +15533,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>116</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15540,10 +15562,10 @@
         <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>10</v>
@@ -15565,10 +15587,10 @@
         <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>9</v>
@@ -15579,10 +15601,10 @@
         <v>16</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>6</v>
@@ -15613,10 +15635,10 @@
         <v>26</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>8</v>
@@ -15638,10 +15660,10 @@
         <v>26</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>7</v>
@@ -15652,10 +15674,10 @@
         <v>26</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>6</v>
@@ -15714,10 +15736,10 @@
         <v>38</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>8</v>
@@ -15751,10 +15773,10 @@
         <v>44</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>9</v>
@@ -15788,10 +15810,10 @@
         <v>50</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>7</v>
@@ -15825,10 +15847,10 @@
         <v>56</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>10</v>
@@ -15848,10 +15870,10 @@
         <v>60</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>9</v>
@@ -15885,10 +15907,10 @@
         <v>66</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>7</v>
@@ -15908,10 +15930,10 @@
         <v>69</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>9</v>
@@ -15933,10 +15955,10 @@
         <v>69</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>6</v>
@@ -15967,10 +15989,10 @@
         <v>75</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>9</v>
@@ -15992,10 +16014,10 @@
         <v>75</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>7</v>
@@ -16026,10 +16048,10 @@
         <v>81</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>10</v>
@@ -16049,10 +16071,10 @@
         <v>85</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>10</v>
@@ -16072,10 +16094,10 @@
         <v>88</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>10</v>
@@ -16097,10 +16119,10 @@
         <v>88</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>10</v>
@@ -16111,10 +16133,10 @@
         <v>88</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>10</v>
@@ -16125,10 +16147,10 @@
         <v>88</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>8</v>
@@ -16145,10 +16167,10 @@
         <v>91</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>10</v>
@@ -16168,10 +16190,10 @@
         <v>94</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>10</v>
@@ -16191,10 +16213,10 @@
         <v>97</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>5</v>
@@ -16249,22 +16271,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>116</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16278,10 +16300,10 @@
         <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>10</v>
@@ -16315,10 +16337,10 @@
         <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>10</v>
@@ -16380,10 +16402,10 @@
         <v>38</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>9</v>
@@ -16417,10 +16439,10 @@
         <v>44</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>10</v>
@@ -16454,10 +16476,10 @@
         <v>50</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>6</v>
@@ -16479,10 +16501,10 @@
         <v>50</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>10</v>
@@ -16513,10 +16535,10 @@
         <v>56</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>9</v>
@@ -16536,10 +16558,10 @@
         <v>60</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>9</v>
@@ -16573,10 +16595,10 @@
         <v>66</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>10</v>
@@ -16596,10 +16618,10 @@
         <v>69</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>9</v>
@@ -16621,10 +16643,10 @@
         <v>69</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>5</v>
@@ -16635,10 +16657,10 @@
         <v>69</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>9</v>
@@ -16669,10 +16691,10 @@
         <v>75</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>10</v>
@@ -16706,10 +16728,10 @@
         <v>81</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -16729,10 +16751,10 @@
         <v>85</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>10</v>
@@ -16752,10 +16774,10 @@
         <v>88</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>10</v>
@@ -16775,10 +16797,10 @@
         <v>91</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>10</v>
@@ -16798,10 +16820,10 @@
         <v>94</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>10</v>
@@ -16865,22 +16887,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>116</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16922,10 +16944,10 @@
         <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>10</v>
@@ -17015,10 +17037,10 @@
         <v>44</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>10</v>
@@ -17040,10 +17062,10 @@
         <v>44</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>8</v>
@@ -17102,10 +17124,10 @@
         <v>56</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -17125,10 +17147,10 @@
         <v>60</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>9</v>
@@ -17162,10 +17184,10 @@
         <v>66</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>7</v>
@@ -17185,10 +17207,10 @@
         <v>69</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>9</v>
@@ -17208,10 +17230,10 @@
         <v>72</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>7</v>
@@ -17231,10 +17253,10 @@
         <v>75</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>9</v>
@@ -17256,10 +17278,10 @@
         <v>75</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>6</v>
@@ -17304,10 +17326,10 @@
         <v>85</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -17327,10 +17349,10 @@
         <v>88</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>10</v>
@@ -17350,10 +17372,10 @@
         <v>91</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>10</v>
@@ -17373,10 +17395,10 @@
         <v>94</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>8</v>
@@ -17448,22 +17470,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>116</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17477,10 +17499,10 @@
         <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>8</v>
@@ -17514,10 +17536,10 @@
         <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>8</v>
@@ -17537,10 +17559,10 @@
         <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>6</v>
@@ -17560,10 +17582,10 @@
         <v>32</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>10</v>
@@ -17597,10 +17619,10 @@
         <v>38</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>8</v>
@@ -17634,10 +17656,10 @@
         <v>44</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>8</v>
@@ -17659,10 +17681,10 @@
         <v>44</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>7</v>
@@ -17693,10 +17715,10 @@
         <v>50</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>9</v>
@@ -17716,10 +17738,10 @@
         <v>53</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -17739,10 +17761,10 @@
         <v>56</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -17764,10 +17786,10 @@
         <v>56</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>9</v>
@@ -17778,10 +17800,10 @@
         <v>56</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>9</v>
@@ -17792,10 +17814,10 @@
         <v>56</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>7</v>
@@ -17806,10 +17828,10 @@
         <v>56</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>6</v>
@@ -17826,10 +17848,10 @@
         <v>60</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>9</v>
@@ -17863,10 +17885,10 @@
         <v>66</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>7</v>
@@ -17886,10 +17908,10 @@
         <v>69</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>9</v>
@@ -17909,10 +17931,10 @@
         <v>72</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>7</v>
@@ -17932,10 +17954,10 @@
         <v>75</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -17969,10 +17991,10 @@
         <v>81</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>9</v>
@@ -17992,10 +18014,10 @@
         <v>85</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>10</v>
@@ -18017,10 +18039,10 @@
         <v>85</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>9</v>
@@ -18031,10 +18053,10 @@
         <v>85</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>6</v>
@@ -18045,10 +18067,10 @@
         <v>85</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>6</v>
@@ -18059,10 +18081,10 @@
         <v>85</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>6</v>
@@ -18073,10 +18095,10 @@
         <v>85</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>5</v>
@@ -18093,15 +18115,15 @@
         <v>88</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="I34" s="18" t="n">
+      <c r="I34" s="15" t="n">
         <v>10</v>
       </c>
     </row>
@@ -18116,10 +18138,10 @@
         <v>91</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>10</v>
@@ -18139,16 +18161,16 @@
         <v>94</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>8</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H36" s="1" t="n">
         <v>8</v>
@@ -18163,10 +18185,10 @@
         <v>94</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>8</v>
@@ -18177,10 +18199,10 @@
         <v>94</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>5</v>
@@ -18249,22 +18271,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>116</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18278,10 +18300,10 @@
         <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>8</v>
@@ -18315,10 +18337,10 @@
         <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>8</v>
@@ -18340,10 +18362,10 @@
         <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>7</v>
@@ -18360,10 +18382,10 @@
         <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>2</v>
@@ -18383,10 +18405,10 @@
         <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>10</v>
@@ -18408,10 +18430,10 @@
         <v>32</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>9</v>
@@ -18422,10 +18444,10 @@
         <v>32</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>7</v>
@@ -18436,10 +18458,10 @@
         <v>32</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>6</v>
@@ -18450,10 +18472,10 @@
         <v>32</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>4</v>
@@ -18484,10 +18506,10 @@
         <v>38</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>8</v>
@@ -18521,10 +18543,10 @@
         <v>44</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -18558,10 +18580,10 @@
         <v>50</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>10</v>
@@ -18581,10 +18603,10 @@
         <v>53</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>9</v>
@@ -18606,10 +18628,10 @@
         <v>53</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>8</v>
@@ -18620,10 +18642,10 @@
         <v>53</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>3</v>
@@ -18640,10 +18662,10 @@
         <v>56</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>10</v>
@@ -18665,10 +18687,10 @@
         <v>56</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>8</v>
@@ -18679,10 +18701,10 @@
         <v>56</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>8</v>
@@ -18699,10 +18721,10 @@
         <v>60</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>9</v>
@@ -18736,10 +18758,10 @@
         <v>66</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>9</v>
@@ -18759,10 +18781,10 @@
         <v>69</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>10</v>
@@ -18784,10 +18806,10 @@
         <v>69</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>6</v>
@@ -18804,10 +18826,10 @@
         <v>72</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>8</v>
@@ -18827,10 +18849,10 @@
         <v>75</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>9</v>
@@ -18864,10 +18886,10 @@
         <v>81</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>8</v>
@@ -18887,10 +18909,10 @@
         <v>85</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>10</v>
@@ -18910,10 +18932,10 @@
         <v>88</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>9</v>
@@ -18933,10 +18955,10 @@
         <v>91</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>10</v>
@@ -18956,10 +18978,10 @@
         <v>94</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>8</v>
@@ -18984,7 +19006,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H38" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="I38" s="1" t="n">
         <f aca="false">COUNTIF(I2:I37,"&gt;0")</f>
